--- a/04_extract_results/ai_review_batches/batch_001.xlsx
+++ b/04_extract_results/ai_review_batches/batch_001.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H151"/>
+  <dimension ref="A1:N151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,25 +446,55 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>previous_sentence</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>sentence</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>next_sentence</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ai_relevant</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>relevance_level</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>sentence_type</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>rule_matched_pathways</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>matched_keywords</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ethanol_specific</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>oxygenate_related</t>
         </is>
@@ -486,27 +516,51 @@
           <t>S0001</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>*OHoverAgCuNWduringCO RR.Todeterminethe*OHadsorption Basedontheaboveresults,thereactionmechanismsofCO RRfor 1 2 2 site,theadsorptionanddissociationenergiesofH OonCuNW,AgCu thedistinctiveselectivitytowardsethyleneandethanoloverAgCuNW 2 NWandAgCuNWwerecalculated17.AsshowninFig.5a,comparedto andAgCuNWcanbeclearlyevidenced.Theethylenepathwayfollows 1 1 AgCuNWandCuNW,theH OadsorptionenergyoverAgCuNWis the symmetric C-C coupling, arising from the high *CO coverage 2 1 more negative with more electrons directly transferred from H O generatedoverAgnanoparticlesandthereducedenergybarrierfor 2 molecule to AgCu NW (Supplementary Fig. 50).</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>Furthermore, H O *COCOformationoverAgCuNW.Whiletheethanolpathwayfollows 1 2 tendstomorepreferablydissociateonthesingleAgatomicsiteover theasymmetricC-Ccoupling,triggeredbythein-situgeneratedHOAgCuNWwiththelowestH Odissociationtransitionstate(TS)energy Ag-Cu-Cu sites (Fig. 5e), which reduces the energy barrier for the 1 2 1 barrier(Fig.5bandSupplementaryFigs.51–53).Thein-situformation formationof*CHOspeciesandthuspromotesasymmetric*CO-*CHO ofHO-AgCuNWduringCO RRnotonlypromotedthereleaseofH+ coupling,boostingCO reductiontoethanoloverAgCuNW. 1 2 2 1 forthesubsequenthydrogenationreaction,butalsolargelyreduced theGibbsfreeenergyfor*COhydrogenationto*CHO(Fig.5c),which Discussion facilitated the asymmetric *CO-*CHO coupling over the adjacent Insummary,twowell-definedmodelCu-basedcatalystsweredevelpairedCuatoms(HO-Ag-Cu-Cu)topreferablyreduceCO toethanol opedbymodifyingCunanowireswithAgnanoparticles(AgCuNW) 1 2 (Fig. 5d, e,and SupplementaryFigs. 54–57).On the other hand, for andsingleAgatoms(AgCuNW),respectively,andtheirunderlying 1 AgCuNW,asshowninSupplementaryFigs.58–60,theenergybarrier C-C coupling mechanisms of CO RR to ethylene and ethanol were 2 forhydrogenationof*CO to*COOHcanbegreatlyreducedfrom0.83 successfullyelucidated.OperandoXASandquasiin-situXPSrevealed 2 NatureCommunications|( 2024)1 5:10247 7</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>P1;P2</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>P1:*COCO; P1:COCO; P2:*CO-*CHO; P2:*CHO</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -528,27 +582,51 @@
           <t>S0002</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
         <is>
           <t>Article https://doi.org/10.1038/s41467-024-54636-w Manipulating C-C coupling pathway in electrochemical CO reduction for selective 2 ethylene and ethanol production over single-atom alloy catalyst Received:28February2024 ShifuWang1,2,9,FuhuaLi3,4,9,JianZhao2,YaqiongZeng2,YifanLi 5,Zih-YiLin6, Tsung-JuLee6,ShuhuiLiu7,XinyiRen2,WeijueWang2,YusenChen2, Accepted:14November2024 Sung-FuHung 6,Ying-RuiLu 8,YiCui 5,XiaofengYang 2,XuningLi 2 , YanqiangHuang 1,2 &amp;BinLiu 3,4 Checkforupdates ManipulationC-CcouplingpathwayisofgreatimportanceforselectiveCO 2 electroreductionbutremainchallenging.Herein,twomodelCu-basedcatalysts,bymodifyingCunanowireswithAgnanoparticles(AgCuNW)andAg singleatoms(AgCuNW),respectively,arerationallydesignedforexploring 1 theC-CcouplingmechanismsinelectrochemicalCO reductionreaction 2 (CO RR).ComparedtoAgCuNW,theAgCuNWexhibitsamorethan10-fold 2 1 increaseofC selectivityinCO reductiontoethanol,withethanol-to-ethylene 2 2 ratioincreasedfrom0.41overAgCuNWto4.26overAgCuNW.Viaavarietyof 1 operando/in-situtechniquesandtheoreticalcalculation,theenhancedethanol selectivityoverAgCuNWisattributedtothepromotedH Odissociationover 1 2 theatomicallydispersedAgsites,whicheffectivelyaccelerated*COhydrogenationtoform*CHOintermediateandfacilitatedasymmetric*CO-*CHO couplingoverpairedCuatomsadjacenttosingleAgatoms.Resultsofthis workprovidedeepinsightintotheC-CcouplingpathwaystowardstargetC 2+ productandshedlightontherationaldesignofefficientCO RRcatalystswith 2 pairedactivesites.</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ElectrochemicalCO reduction reaction (CO RR) offersa promising attractive6–10.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>P2:*CO-*CHO; P2:*CHO; P2:CHO intermediate</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -570,27 +648,47 @@
           <t>S0003</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
         <is>
           <t>1.4 1.2 1.0 -1.1 -1.3 -1.5 -1.7 )Ve( ygrene noitamroof HOC-OC* sites without extra O-Cu bond sites with extra O-Cu bond trend fitted level Y=-0.54X+0.45 1.27 4 1.21 3 2 1 6 5 0.92 0.90 2 *CO adsorption (eV) 0.0 -0.5 -1.0 -1.5 -2.0 -2.5 -3.0 Reaction coordinates )Ve( G(cid:141) 0.5 0.0 -0.5 -1.0 5 H 2 -1.5 -0.5 0.0 0.5 1.0 ethanol pathway ethylene pathway n-propanol pathway )Ve( E(cid:141) OC* active sites on R-Hex-2Cu-O/G CO HCOOH 1 2 3 4 6 Beyond CO (cid:141)E (eV) *H 1.5 1.0 0.5 0.0 -0.5 -1.0 )Ve( ygrenE a b c *CCOH *HOCCOH *OCCOH *CHCOH *OCHCOH *OCCOCOH *CCH 2*CO *OCC(OH)COH *OCCH2COH *HOCCH2CH * O H H OCHCH2CHOH *OCCCOH *CHCH2CHOH *OCHC *OCHCH *OCHCH2 *CCH2 *CHCH2 ethylene 3*CO *OCCHCOH *OCCH2CHOH ethanol *CH2CH2CHOH 2*CO + 8 (H++e-) (cid:2)CH 3 CH 2 OH (g) + H 2 O *OCHCH3 *CH3CH2CHOH *OCH2CH3 n-propanol d e 0 V vs RHE -1.3 V vs RHE Reaction coordinates -0.07 Article https://doi.org/10.1038/s41467-022-32740-z R-Hex-2Cu-O/G 0.42 -0.09 0 V vs RHE 2*CO + 8 (H++e-) (cid:2)CHCH + 2HO 2 2(g) 2 3*CO + 12 (H++e-) (cid:2)CHCHCHOH + 2HO 3 2 2 (g) 2 -0.09 1.51 0.92 -1.18 *OCHCOH *OCCOH 0.72 0.42 2*CO *OCHC ethanol(g) 0.48 -0.03 -0.03 -0.71 -0.87 *OCHCH *OCHCH 2 3 *OCHCH 3 *OCHCH 2 Fig.5|DFTcalculationstounraveltheformationmechanismofmulti-carbon change(ΔG)valuesforkeybifurcatingintermediatesareannotatedineV.dAtomic alcohols.aLinearscalingrelationsbetween2*COadsorptionand*OCCOHforstructuresofthereactionintermediatesalongtheethanolpathway.ΔGforevery mationfreeenergiesonR-Hex-2Cu-O/G.Atomicconfigurationofrelevantactive stepat0VvsRHEareannotatedineV.Greenandredvaluesdenote,respectively, sitesaresummarizedinSupplementaryFig.35.bAnalysisofadsorptionenergyfor exergonicandendergonicprocess.SolidbluearrowsrefertothePCETsteps.color CO(ΔE )andH(ΔE )atvarioussitesontheR-Hex-2Cu-2O/G.Verticalandhorcodes:Cu,orange;C,brown(Hex-2Cu-O),navy(graphene)andgreen(reaction *CO *H izontalblacklinesrepresenttheequilibriumstates(i.e.,ΔG=0)for*H↔½H2,and intermediates);O,red(Hex-2Cu-O)andpurple(reactionintermediates);H,pink *CO↔CO,respectively.Atomicconfigurationofrelevantactivesitesaresummar- (Hex-2Cu-O)andblue(reactionintermediates).eEnergybarriersof*HOCCOH izedinSupplementaryFig.37.cReductionpathwaysidentifiedonR-Hex-2Cu-O/G formationonR-Hex-2Cu-O/Gat0Vand–1.3VvsRHE. at0VvsRHE.Thereferenceenergylevelissettobebaresurface.Freeenergy NatureCommunications|( 2022)1 3:5122 9</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>P1;P4;P5</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>P1:*OCCO; P1:OCCO; P1:COCO; P4:*CH2; P4:*CH3; P5:HCOO</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -612,19 +710,47 @@
           <t>S0004</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>It is noteworthy, riers of C–C coupling on p-sq, s-sq and cv-sq sites are 0.33eV, that, Cu(100) and Cu(751), which experimentally show more 0.72eV, and 0.39eV, respectively, much lower than 0.85eV and selective for ethylene and alcohols7, fall in their respective pro1.19eVon(111)and(221)facets(Fig.2g).Basedontheanalysis duct region, thus meaning the bond length of C–O in adsorbed above,threeactivesites,p-sq,s-sqandcv-sqsites,whichfavorfor *CH CHO may be a simple descriptor for the selectivity of 2 C 2+ products production have been identified on OD-Cu. ethylene and alcohols on different surface structures.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>Previous work proved that ethylene and ethanol are not genThe specific geometry of step-square site explains the differeratedfromthesametypesofactivesites,whichmeanstheC–C enceinselectivity.Figure3eshowsthatthegeneralcoordination couplingactivesitescanbefurthersubdivided16.Fromcalculated number (GCN) of s-sq is the lowest (5.50), thus showing the free energy profiles of the whole reaction pathway (Supplemenstrongest adsorption energy of acetaldehyde intermediate taryFigs.24–26),*CH CHOservesastheselectivitydetermining (*CH CHO),leadingtothehydrogenationpathwaydominances. 2 3 intermediate (SDI), which corresponds to previous calculations Meanwhile, p-sq and cv-sq can supply the fourfold sites to staon copper single crystal facets27,28.</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>The ethylene pathway probilize the newly formed *O after C–O cleavage.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -646,27 +772,55 @@
           <t>S0005</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>We note The observation of these peaks agrees well with a CO-coveragehere that irrespective of the electrolyte anionic species, carbonate determined C–C coupling during CORR13 and indicates a similar inter2 and bicarbonate ions will be present due to the CO/HO equilibrium. mediate for C–C coupling during CORR and CORR.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Concurrently, 2 2 2 Although a lower Faradaic efficiency of C products is obtained during the Raman peaks of *HCOO−/*HCOOH disappear, which suggests that 2+ CORR in CO-saturated 0.1 M NaClO (ref. 28), the onset potentials and CO or C–C coupling intermediates may affect the production of 2 2 4 potential-dependent trends for ethylene and ethanol formation are formic acid due to competition for surface sites. similar to those in 0.1 M KHCO (Supplementary Fig. 12).</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>At more cathodic potentials, CO coverage further increases, and 3 Initially, at open-circuit potential, Raman peaks at 400 cm−1, four new peaks can be detected at 1,182 cm−1, 1,318 cm−1, 1,453 cm−1 and 528 cm−1 and 620 cm−1 from a CuO phase are detected12,29.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>P5:HCOO</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -688,27 +842,55 @@
           <t>S0006</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>P 2 L Cu O.IntheRamanspectra(Fig.5BandSupplementaryFig.33D),the Cu/CuOwithadditionallyformedemptyorbitalscanfacilitateelectron 2 L 2 Cu /Cu Opowderloadedoncarbonpapersubstrateexhibitstypical transferfromhydrogentonucleophilicintermediates,suggestingtheCu L 2 characteristic peaks of adsorbed *CO intermediates, which are 3dorbitalsoverlapwiththeπorbitalsofCandfurtherreducedactivation deconvoluted into a low-frequencyband (LFB) at ∼2045cm−1 and a energyforCO hydrogenationonCu/CuO68.Asaresult,thenucleo2 2 high-frequencyband(HFB)at∼2097cm−1,whichverifiesthebonding philic addition reaction process of *CHCO–*CO coupling may effec2 stylesonterraceandstepsites,respectively53,54.Aredshiftoftheυ(CO) tivelyreactonthemixed-valenceboundaryregion33,whichreducesthe bandindicatestheenhancedinteractionbetweenthecatalystsurface formation energy of *CHCOCO on Cu/CuO (−0.148eV) toward 2 L 2 and *CO, resulting in a higher *CO coverage55.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>In addition, the fren-propanol(Fig.5E,SupplementaryFig.35,andSupplementaryTable6). quenciesofυ(CO)bandsarecorrelatedwiththecoordinationstatesof For the C–C coupling on Cu/CuO model (Fig. 5F, Supplementary L 2 Cusites.Therefore,thelow-coordinationstatesofCusitesinCu /Cu O Fig.36andSupplementaryTable7),the*CO–COHcouplingistherateL 2 willinduceapositiveshiftofthed-bandcenterofCuandboostthe determiningstepforCu/CuOcatalyst(1.46eV),indicatingthevitalrule L 2 hybridizationofthed-bandwiththe2π*orbitalofCO.TheHFBmodes of *CO coverage in the post-coupled proton-electron transfer (CPET) derivedfromthelow-coordinatedCusiteswillfavorthebreedingof reaction.Theenergybarriersofintermediatesgraduallydecreaseuntil theυ(C–C)band(~1960cm−1),whereablueshiftmaypredictthepro- *CHOisreached,whichcanbefurtherreducedto*CH Oor*Ofor 2 3 2 4 tonationprocessC–Cbonds29,30.Onthecontrary,theweaksignsofthe ethanol or CH , respectively.</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>The Cu/CuO model exhibits a more 2 4 L 2 υ(CO)andυ(C–C)bandsonCu /Cu Ocatalystalsoverifythepoor*CO stable adsorption for CH O* (−0.293eV) than Cu /CuO (−0.154eV), P 2 2 4 P 2 coverageandC–Ccoupling(SupplementaryFig.34B).Toverifythe implying facilitated thermodynamics for increasing the adsorption of originoftheoxidationstateofCu /Cu O,Ramanspectroscopywas keyintermediate.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>P2;P3</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>P2:*CHO; P3:CO-COH; P3:CO–COH</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -730,27 +912,55 @@
           <t>S0007</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>To date, Cu is the only electrocatalyst found able to 2 generate C (n ≥ 2) liquid products from the CO RR with appreciable reaction rates, due to the strong n 2 adsorption of the *CO intermediate on the Cu surface that promotes C-C bond formation via CO dimerization or CO-CHO coupling 5,12,15.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>Unfortunately, the formation of C-C bonds on Cu is very complicated and the pathway remains elusive 16, which have greatly limited the development of highly selective electrocatalyst to reduce CO to C (n ≥ 2) liquid products. 2 n Herein, we report a Sn-based tandem catalyst consisting of SnS nanosheets that are able to produce 2 formate intermediates and single Sn atoms anchored on a 3D carbon support via a local SnO3 cluster (Sn -O3G) that generate *OCO(OH) bicarbonate intermediates, followed by C-C coupling to 1 electrochemically reduce CO to ethanol.</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Based on this strategy, an ethanol selectivity of more than 70% 2 was achieved over a wide potential range from − 0.6 to -1.1 V versus the reversible hydrogen electrode (RHE).</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>P5:formate intermediate</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -772,27 +982,55 @@
           <t>S0008</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>The morphology of the catalysts was symmetric*CO-*COcouplinginCO RRtoproduceethylene.Onthe examined by transmission electron microscopy (HRTEM, JEOL JEM2 contrary, the in-situ formed *OH species via H O dissociation was 2100F operated at 200kV) and field-emission scanning electron 2 dominantly found over AgCu NW.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>Isotopic labelling experiments microscopy(FESEM,JSM-6700F)equippedwithanenergydispersive 1 indicated that the methyl C (*CH ) and methylene C (*CH OH) in X-rayspectroscopy(EDX,AztecX-Max80T).High-angleannulardark3 2 ethanol product were originated from the *CO and *HCHO interfield scanning transmission electron microscopy (HAADF-STEM) mediates,respectively.Theoreticalcalculationsfurtherdemonstrated characterizationwasconductedonaJEOLJEMARM200FSTEM/TEM thattheatomicallydispersedAgcouldnotonlypromotedissociation withaguaranteedresolutionof0.08nm.DetailedchemicalcomposiofH OtoreleaseH+,butalsoreducetheenergybarrierforthefortionswereanalyzedbyX-rayphotoelectronspectroscopy(XPS)onan 2 mation of *CHO over its neighboring Cu site, resulting in the sigESCALAB250photoelectronspectrometer(ThermoFisherScientific) nificantly promoted asymmetric *CO-*CHO coupling over paired Cu using a monochromatic Al Kα X-ray beam (1,486.6eV).</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>All binding atoms adjacent to the single Ag atom, greatly boosting electroenergieswerereferencedtotheC1speak(284.8eV).TheconcentrachemicalCO reductiontoethanol. tionofAginAgCuNWandAgCuNWwerequantifiedbyinductively 2 1 coupledplasmaopticalemissionspectroscopy(ICP-OES).Forex-situ Methods XASmeasurements,acertainamountofpowdersampleswereplaced Chemicalsandmaterials intoahollowcircularmold(madeofpolytetrafluoroethylene)witha Copper(II)chloridedihydrate(CuCl ·2H O,99.99%,CAS:10125-13-0), diameterof1cm.Thefilledsamplewasthenfixedandvacuumedto 2 2 glucose(C H O ,99.5%,CAS:50-99-7),hexadecylamine(HAD,98%, prevent oxidation during the transfer and measurement processes. 6 12 6 CAS:143-27-1),hexane(98%,CAS:110-94-3)andsilvernitrate(AgNO , And the sample was secured on an XAS sample stage, which was 3 99.99%, CAS: 7761-88-8) were purchased from Aladdin.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>P2:*CO-*CHO; P2:*CHO</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -814,27 +1052,51 @@
           <t>S0009</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Importantly, it achieves CO –to–ethanol conversion under high current 2 operation with partial current density of 326.4mAcm−2 at −0.87V vs reversible hydrogen electrodeto rankhighlysignificantlyamongstreported Cu–basedcatalysts.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>Basedon in situ spectra studies we show that significantly boosted production results from tailored introduction of Ag to optimize the coordinated number and oxide state of surface Cu sites, in which the *CO adsorption is steered as both atop and bridge configuration to trigger asymmetric C–C coupling for stablization of EtOH intermediates. 1SchoolofChemicalEngineeringandAdvancedMaterials,TheUniversityofAdelaide,Adelaide,SA5005,Australia.2StateKeyLaboratoryofPhysical ChemistryofSolidSurfaces,CollegeofChemistryandChemicalEngineering,XiamenUniversity,Xiamen361005,China.3InstituteofFunctionalNano&amp;Soft Materials(FUNSOM),JiangsuKeyLaboratoryforCarbon-BasedFunctionalMaterials&amp;Devices,JointInternationalResearchLaboratoryofCarbon-Based FunctionalMaterialsandDevices,SoochowUniversity,Suzhou215123,China.4Theseauthorscontributedequally:PengtangWang,HaoYang. ✉ email:hxq006@xmu.edu.cn;s.qiao@adelaide.edu.au NATURECOMMUNICATIONS| (2022) 13:3754 |https://doi.org/10.1038/s41467-022-31427-9|www.nature.com/naturecommunications 1 ;,:)(0987654321</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>P5:OCHO</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -856,27 +1118,55 @@
           <t>S0010</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>However, it is difficult to *CO,whichaffectsthereactionpathwaystowardethyleneandethanol. measure local CO concentration in the catalyst layer directly.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>To Thus,in-situATR-SEIRASwasemployedtofurtherevaluatetheimpact 2 investigate the localCO concentration ofdifferentinterfacialwettofinterfacialwettabilityontheadsorptionofintermediates(Fig.3d,e). 2 ability,controlsampleswerepreparedwithdifferentgas–liquid–solid There is a stretching band at ~2070cm−1 on all electrodes, correcontact, enabling in situ measurements with fluorescence electrospondingtothestretchingbandofthelinear-bondCO(CO )ontheCu L chemical spectroscopy (FES) at 100mAcm−2 chronopotentiometry surface43,44.Asforhydrophobic-treatedCuelectrodes,theCO bands L (Fig.3b).ThelocalCO concentrationofallsamplesdecreasestoanew becomemoreclearlydefinedatmoderateoverpotentials(−0.6to1.2V 2 steadystateduringelectrolysis.Asforthethree-phasecontactelecvs.RHE),indicatingalarger*COcoverage.Furthermore,CO bandsare L trode,increasinghydrophobicitycanshortentherelaxationtimeof preferentially observed on hydrophobic-treated Cu surfaces under thelocalCO concentrationandincreaseequilibriumconcentration, more negative potentials, with a wider voltage range of *CO 2 whichcanfacileCO masstransport.ThelocalCO concentrationwill coverage14,45.Theenhanced*COadsorptioncanbeattributedtothe 2 2 return back to the initial equilibrium value after electroreduction highproduction rateofthe accumulationofmore*COona hydro- (SupplementaryFig.30).TherecoveryoflocalCO concentrationon phobicCusurfaceunderahighlocalconcentrationofCO 31.Thedif2 2 the highly hydrophobic interface is faster due to the improved gas ferencein*COcoverageoverawidevoltagerangederivedfromthe diffusion.Theseresultsdemonstratethattheinterfacialcontactstate wettabilityofthecatalystlayerisoneofthekeyfactorsfortheethylene affectstheCO masstransportfromthebulkphasetothecatalyst,thus andethanolpathways. 2 affectingthelocalCO concentrationnearbythecatalyst. 2 The hydrophobic treatment also can promote CO diffusion in Effectofcontrollablewettabilityon*HcoverageviaH Omass 2 COreductionreactions.Thus,itcanbeexcludedthatthelimitedCO transport 2 masstransportatthehydrophilicCuelectrodeisentirelyduetothe As another key intermediate, the *H intermediate on the surface is neutralization of CO with the electrolyte (Fig. 3c, Supplementary convertedfromthebulksolution,whichisaffectedbyH Otransport. 2 2 Fig. 31).</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Like in the CO RR, the direct coupling between two *CO InordertoelucidatetheeffectofH Otransportontheethyleneand 2 2 speciesintheCORRiswidelyacceptedasthemajorC–Ccoupling ethanol reaction pathways, the hydrogen evolution reaction (HER) mechanism.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>P1:*COCO; P1:COCO</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -898,19 +1188,47 @@
           <t>S0011</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" t="n">
+        <v>7</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>CO reduction to produce ethylene over AgCu NW (Supplementary 2 Operando Ramanmeasurements observed in-situ generation of Figs.61,62).</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>*OHoverAgCuNWduringCO RR.Todeterminethe*OHadsorption Basedontheaboveresults,thereactionmechanismsofCO RRfor 1 2 2 site,theadsorptionanddissociationenergiesofH OonCuNW,AgCu thedistinctiveselectivitytowardsethyleneandethanoloverAgCuNW 2 NWandAgCuNWwerecalculated17.AsshowninFig.5a,comparedto andAgCuNWcanbeclearlyevidenced.Theethylenepathwayfollows 1 1 AgCuNWandCuNW,theH OadsorptionenergyoverAgCuNWis the symmetric C-C coupling, arising from the high *CO coverage 2 1 more negative with more electrons directly transferred from H O generatedoverAgnanoparticlesandthereducedenergybarrierfor 2 molecule to AgCu NW (Supplementary Fig. 50).</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Furthermore, H O *COCOformationoverAgCuNW.Whiletheethanolpathwayfollows 1 2 tendstomorepreferablydissociateonthesingleAgatomicsiteover theasymmetricC-Ccoupling,triggeredbythein-situgeneratedHOAgCuNWwiththelowestH Odissociationtransitionstate(TS)energy Ag-Cu-Cu sites (Fig. 5e), which reduces the energy barrier for the 1 2 1 barrier(Fig.5bandSupplementaryFigs.51–53).Thein-situformation formationof*CHOspeciesandthuspromotesasymmetric*CO-*CHO ofHO-AgCuNWduringCO RRnotonlypromotedthereleaseofH+ coupling,boostingCO reductiontoethanoloverAgCuNW. 1 2 2 1 forthesubsequenthydrogenationreaction,butalsolargelyreduced theGibbsfreeenergyfor*COhydrogenationto*CHO(Fig.5c),which Discussion facilitated the asymmetric *CO-*CHO coupling over the adjacent Insummary,twowell-definedmodelCu-basedcatalystsweredevelpairedCuatoms(HO-Ag-Cu-Cu)topreferablyreduceCO toethanol opedbymodifyingCunanowireswithAgnanoparticles(AgCuNW) 1 2 (Fig. 5d, e,and SupplementaryFigs. 54–57).On the other hand, for andsingleAgatoms(AgCuNW),respectively,andtheirunderlying 1 AgCuNW,asshowninSupplementaryFigs.58–60,theenergybarrier C-C coupling mechanisms of CO RR to ethylene and ethanol were 2 forhydrogenationof*CO to*COOHcanbegreatlyreducedfrom0.83 successfullyelucidated.OperandoXASandquasiin-situXPSrevealed 2 NatureCommunications|( 2024)1 5:10247 7</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -932,19 +1250,43 @@
           <t>S0012</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Here, we report a strategy in which we modify the surface of bimetallic silver-copper catalyst with aromatic heterocycles such as thiadiazole and triazole derivatives to increase the conversion of CO into hydro2 carbon molecules.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>By combining operando Raman and X-ray absorption spectroscopy with electrocatalytic measurements and analysis of the reaction products, we identified that the electron withdrawing nature of functional groups orients the reaction pathway towards the production of C species (ethanol and ethylene) and enhances the reaction rate on the 2+ surfaceofthecatalystbyadjustingtheelectronicstateofsurfacecopperatoms.Asaresult, we achieve a high Faradaic efficiency for the C 2+ formation of ≈80% and full-cell energy efficiency of 20.3% with a specific current density of 261.4mAcm−2 for C 2+ products. 1InstitutEuropéendesMembranes,IEM,UMR5635,UniversitéMontpellier,ENSCM,CNRS,Montpellier34000,France.2CollegeofBioresourcesand MaterialsEngineering,ShaanxiUniversityofScience&amp;Technology,710021Xi’an,People’sRepublicofChina.3InstitutCharlesGerhardt,ICGM,UMR5253, UniversityofMontpellier,ENSCM,CNRS,34095MontpellierCedex5,France.4SchoolofScienceandEngineering,TheChineseUniversityofHongKong, 518172Shenzhen,Guangdong,People’sRepublicofChina.5DepartamentodeCienciadelosMaterialeseIngenieríaMetalúrgicayQuímicaInorgánica, FacultaddeCiencias,UniversidaddeCádiz,CampusRíoSanPedroS/N,PuertoReal,11510Cádiz,Spain.6InstitutoUniversitariodeInvestigaciónde MicroscopíaElectrónicayMateriales(IMEYMAT),FacultaddeCiencias,UniversidaddeCádiz,CampusRíoSanPedroS/N,PuertoReal,11510Cádiz,Spain. 7InstitutUniversitairedeFrance(IUF),1rueDescartes,75231ParisCedex05,France. ✉ email:damien.voiry@umontpellier.fr NATURECOMMUNICATIONS| (2021) 12:7210 |https://doi.org/10.1038/s41467-021-27456-5|www.nature.com/naturecommunications 1 ;,:)(0987654321</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -966,19 +1308,47 @@
           <t>S0013</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Of the three pH?—iscrucialforprovidinginsightattheatomic-levelandbroaden branchingintermediatesOCHCH*isthemoststableandCHCOH* our understanding when addressing the trends of C Oxy/HC the least (Supplementary Fig. 5a).</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>Despite the poorer thermo2 selectivity. dynamicstabilityofCHCOH*,itsformationexhibitsthelowestΔG a In this work, we investigate the reaction mechanism of COR of 0.65eV at U =0V; whereas the other two steps have to RHE towards major C Oxy/HC products (e.g. ethylene, ethanol, and overcomeafreeenergybarrieratleast0.21eVhigher.Nevertheless, 2 aceticacid)fromreactionandactivationenergiescalculatedusing these differences in ΔG become smaller as the overpotential a density functional theory (DFT).</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Pathways trifurcating from a increases,duetothesmallercharge-transfercoefficient(β~0.35)for common intermediate, CHCO*, are shown to be responsible for CHCO-H than for CHC-HO (β ~0.45) and OCCH-H (β ~0.5) generating specific C Oxy/HC products.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1000,27 +1370,55 @@
           <t>S0014</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>C-C coupling pathway for ethanol synthesis via the CO RR, with a low activation energy, high selectivity 2 and good stability.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>These properties can be attributed to the dual active centers of Sn and O in Sn -O3G, 1 which are able to adsorb *CHO and *CO(OH) intermediates, respectively, thereby promoting the subsequent C-C coupling of these intermediates to form ethanol.</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>It is anticipated that this work will lead to new applications for single-atom catalysts 17,18 with polar active centers in multi-step chemical reactions.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>P2:*CHO</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1042,19 +1440,47 @@
           <t>S0015</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RHE) (Fig. 3c), while a mixture of SnS nanosheets with 3D 2 carbon (without the single Sn atoms, Extended data Fig. 44) failed to produce ethanol.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>From these ndings, we propose that the formation of ethanol over the SnS /Sn -O3G may result from C-C coupling 2 1 between the two intermediates associated with formate and CO.</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>To verify our hypothesis, we intentionally introduced a small amount of HCOOH into the reaction system (in a Na SO electrolyte instead of KHCO ) during the CO RR over the Sn -O3G.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1076,27 +1502,51 @@
           <t>S0016</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
         <is>
           <t>atom of Sn -O3 and the C of the support, the Sn -O3G catalyst is distinguished by the dual active sites of 1 1 Sn and O that are able to adsorb different C-based intermediates, providing a novel platform for C-C bond formation during the CO RR to produce ethanol. 2 In summary, we have developed a Cu-free, Sn-based tandem catalyst to produce ethanol from the CO RR, 2 in which the dual active centers of Sn and O atoms on Sn -O3G serve to adsorb different C-based 1 intermediates, which effectively lowers the C-C coupling energy between *CO(OH) and *CHO.</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Our tandem catalyst enables a formal-bicarbonate coupling pathway, which not only provides a novel platform for C-C bond formation during ethanol synthesis and overcomes the restrictions of Cu-based catalysts, but also offers a unique strategy for manipulating CO reduction pathways toward desired products. 2 References 1.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>P2:*CHO</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1118,19 +1568,47 @@
           <t>S0017</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>The distortion of Cu(200) may be confirmingtheaffinityfor*COadsorbatesonCu+ sites,asstatedin causedbythepotentialsurfacedefectowingtothecounterdiffusion previous literature31,32.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>Subsequently, the adsorption energy of oflatticeOfromtheCu O/Cuinterfacewithlowenergybarriers34.The 2 CH CHO (a branching intermediate for ethanol or ethylene) and distortedCu(200)caninducealow-coordinatedCuandreducethe 2 CH CO intermediates were calculated to assess the potential capabarriersofintermediatesadsorption35.EnergydispersiveX-rayspectra 2 citiesfor ethanol andC products(Fig.1E,F).</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Both ofthemexhibit (EDS)mappinganalysisshowsthepresenceofresidualchlorinewitha 3 strong adsorption on the surface of Cu /Cu O model.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1152,27 +1630,55 @@
           <t>S0018</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>However, due to the high energy barrier to C-C bond formation, which competes with the formation of C-H or C-O bonds 12,13,14, the generation of multi-carbon liquid products via the CO RR is still very dicult.</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>To date, Cu is the only electrocatalyst found able to 2 generate C (n ≥ 2) liquid products from the CO RR with appreciable reaction rates, due to the strong n 2 adsorption of the *CO intermediate on the Cu surface that promotes C-C bond formation via CO dimerization or CO-CHO coupling 5,12,15.</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Unfortunately, the formation of C-C bonds on Cu is very complicated and the pathway remains elusive 16, which have greatly limited the development of highly selective electrocatalyst to reduce CO to C (n ≥ 2) liquid products. 2 n Herein, we report a Sn-based tandem catalyst consisting of SnS nanosheets that are able to produce 2 formate intermediates and single Sn atoms anchored on a 3D carbon support via a local SnO3 cluster (Sn -O3G) that generate *OCO(OH) bicarbonate intermediates, followed by C-C coupling to 1 electrochemically reduce CO to ethanol.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>P1;P2</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>P1:CO dimerization; P2:CO-CHO</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1194,19 +1700,47 @@
           <t>S0019</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" t="n">
+        <v>7</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Therefore, 3 2 2 Fig. 3f schematically summarizes the CO RR process to form ethanol taking place on the SnS /Sn -O3G. 2 2 1 The comprehensive discussion for the ethanol formation process on the SnS /Sn -O3G tandem catalyst 2 1 is provided from additional structural characterization and kinetics simulation (Extended data Figs. 49– 53 and Tables 9–17), indicating that diffusion of HCOOH generated from the SnS component to the 2 single atomic Sn sites on Sn -O3G is the rate-determining step for ethanol formation. 1 Based on the above experimental results, we built the active site model of the catalyst.</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>Extensive DFT calculations were performed using the computational hydrogen electrode (CHE) model 22,23,24,25 to map the CO RR pathway and energetics during the formation of ethanol.</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>The results show that, during the CO 2 2 reduction process, the proton-coupled electron transfer (PCET, H+/e−) and dehydration of the Sn - 1 O3(OH)G pre-catalytic sites is exergonic and the resulting Sn -O3G is of radical nature (going from 1 species 0 to 1 in Fig. 4, Extended data Figs. 54 and 55).</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1228,19 +1762,47 @@
           <t>S0020</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" t="n">
+        <v>5</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>According to the simultaneouslytuningkinetic-controlled*COand*H. results of in-situ ATR-SEIRAS spectra (Fig. 3d, e) and in-situ Raman ThelocalCO /HOratioderivedfromwettabilitymayaffectthe 2 2 spectra (Supplementary Fig. 35), higher hydrophobicity indicates coverage of *CO and *H, resulting in the reaction pathways toward higher *CO coverage, thus the corresponding *H coverage is lower. ethylene or ethanol.</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>CFD simulation is adopted to understand the Further, the surface coverage of intermediate (*CO, *H) is directly effectofwettabilityontheinterfacialcontactstateandthelocalCO / 2 proportionaltotheconcentrationofreactants(CO ,H O)5,42.ThereH O ratio, which can reveal the mechanism of wettability variation 2 2 2 fore,the*Hcoveragecanbededucedindirectlythroughwaterconinfluenceontheethyleneandethanolpathways(Fig.4g–j).Asshownin tent.Theconfocallaserscanningmicroscopymeasurements(CLSM) SEMimages,Cunano-islandsareuniformlygrownontheporoussurwere employed toobserve the variation of availablewater near the face of carbon paper with an average size of around 1μm (Suppleinterface(detailsinthe“Methods”section)(Fig.4d–f)48.Todetermine mentaryFigs.2and3).Therefore,thestructureoftheCuelectrodecan the relevance of absorbed water with different wettability, crossbesimplifiedascatalystislandswithpores.ToenabletheCFDsimusectionalimagesalongthez-axisarechosenforcomparison.Thegreen lation,asimplifiedmodelwasconstructed(Fig.4g).Thesquaresinthe fluorescent regions represent the electrolyte phase, while the dark modelareusedtorepresentthecatalystswithvariouscontactangles. regionsrepresentthegasphaseorsolidelectrode.Thedecaytailing Thegapsbetweenthesquaresrepresenttheporesbetweenthereal effect of fluorescence intensity atthe liquid phase boundaryreprecatalystislands(Fig.4g).Thesimulationresultsrevealtheformationof sents the decreasing of available water (since the H during CO RR acontinuousliquidlayeronthehydrophiliccatalyst(Cu)surfaceand 2 source from H O, which can represent *H coverage), which can be CO needsdiffusethroughthethinliquidlayertoreachthecatalystfor 2 2 valued by decay distance.</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>The linear sweep plots of fluorescence reduction,whichcausessomehinderduringgastransport(Fig.4h).In intensityalongthez-axisatthewhitearrowsfromthecross-sectional comparison,thewholesurfaceofhighhydrophobicity(CA:156o)catimages were obtained.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1262,27 +1824,55 @@
           <t>S0021</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Electrochemical reduction of CO (CORR) to chemicals is a promising coverage and selectivity towards C products exists13.</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>Recently, pos2 2 2+ approach to store intermittent renewable energy as valuable fuels and sible C–C coupling intermediates *OCCO or *OCCOH were detected feedstocks1,2.</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>In particular, the synthesis of multi-carbon (C ) products, by infrared spectroscopy during the electrochemical reduction of 2+ such as ethylene and ethanol, is highly attractive because of their verCO (COR)14,15.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>P1:*OCCO; P1:OCCO</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1304,27 +1894,55 @@
           <t>S0022</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>In particular, the synthesis of multi-carbon (C ) products, by infrared spectroscopy during the electrochemical reduction of 2+ such as ethylene and ethanol, is highly attractive because of their verCO (COR)14,15.</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>However, while CO coupling has been repeatedly consatility in the chemical and energy industries3, and processes involving firmed, observing and tracking potential-dependent CO dimerization C–C bond formation are of great relevance from the point of view of and intermediates during the subsequent gradual reduction process fundamental research2,4. towards final products has not yet been achieved.</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Copper-based materials are the most selective catalysts for elecAmong the CORR reaction intermediates7,8, *OCHCH is consid2 2 trochemically reducing CO to C products2.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>P1:CO dimerization</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1346,27 +1964,55 @@
           <t>S0023</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Article https://doi.org/10.1038/s41467-024-54636-w Mechanistically,theCO -to-C pathway(eg.,ethylene,ethanol)is summarized in the Supplementary Methods.</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>One-dimensional Cu 2 2+ conventionallyconsideredtoproceedviaacomplexC-Ccoupling nanowires with an average diameter of 45±3nm were imaged by mechanism involving various intermediates such as *COCO, scanningelectronmicroscopy(SEM)andtransmissionelectronmicro- *COCHO, *COCOH, *CH CO, and *OCHCH , etc1,15–25.</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Therefore, scopy(TEM)(Fig.1bandSupplementaryFigs.1,2).AsshowninFig.1c, 2 2 regulating the key intermediates involved in the CO RR over theAgCuNWexhibitstypicalcharacteristicsofsupportedcatalyst,with 2 catalytic sites and optimizing their binding energies become criAg nanoparticles distributed as islands on the surface of the Cu NW tical to adjust the C-C coupling pathways towards targeted C (SupplementaryFigs.3,4),andobviousgrainboundariesbetweenAg 2+ products.Nevertheless,manipulationofC-Ccouplingpathwaysis nanoparticles and Cu NW can be clearly observed (Supplementary still highly challenging due to the complexity of the catalytic Fig.4b).Incontrast,AgCuNWdisplayssimilarmicrostructuralfeatures 1 system, the unclear reaction intermediates and the limited to Cu NW (Fig. 1d and Supplementary Figs. 5, 6).</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>P1;P5</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>P1:*COCO; P1:COCO; P5:OCHO</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1388,19 +2034,47 @@
           <t>S0024</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" t="n">
+        <v>8</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>We adopted the selectivity determining method linearscalingrelationwith*CO.Next,CO RRproceedspreferentially 2 proposedbyRossmeisletal45todecidetheproductselectivityonRtowardC HOHformationthroughtheexergonicprotonationonCto 2 5 Hex-2Cu-O/G.TheresultsinFig.5bshowthatallactivesitesfromtheRfrom*OCHCOH,whereastheprotonationonOtoform*HOCCOHis Hex-2Cu-O/G surface (Supplementary Fig. 37) fell in the CO RR disfavoredowingtotheextraenergyneededtocleavetheO–Cubond. 2 dominantzone.Thecalculatedselectivityonthetwomodelsisingood Lastly,theelectrochemicalCO RRofHex-2Cu-Owasfurthertestedina 2 agreementwiththeexperimentalobservationofstableC andalcohol flow-cell using the aqueous 1M KOH electrolyte.</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>Similar trend of 2+ productionwithsuppressedH yieldonHex-2Cu-O(Fig.2a). ethanol, propanol, and ethylene was observed with a noticeable 2 After C–C coupling, the spatial-confinement effect can reserve amountofaceticacid(SupplementaryFig.41a).Atthecurrentdensity oxygeninthehydroxylgrouptoincreasealcoholselectivityandinhibit of250mAcm−2,thetotalFEofoxygenates(includingethanol,propathe competing hydrocarbon production.</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>We acquired the complete nol,andaceticacid)sumsupto38.6%andthatofC productsreaches 2+ reactionpathwaystowardthemainproductsobservedinexperiments, 55.4%.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1422,19 +2096,43 @@
           <t>S0025</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" t="n">
+        <v>48</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RHE 2 3 for 2 hours, plotted in selectivity regarding produced number of moles.</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>CO was continuously purged to the solution at 10 2 sccm during eCO2RR. a) Faradaic efficiency of all detected products. b) Faradaic efficiency ratio between *CO-originated products depending on the involvement of C-C coupling during formation process as a function of Ag contents. c) Faradaic efficiency of H and CH (CH , CH , CH , CH , and C H ) as a function of Ag content. d) Faradaic efficiencies of CO as a 2 x y 4 2 4 2 6 3 6 3 8 2 function of Ag content. e)-g) Faradaic efficiencies of *CO-originated products classified on C-O bond as a function of Ag content: e) other carbonyls (glyoxal, acetate, and hydroxy acetone; formate is not included), f) aldehydes (glycolaldehyde, acetaldehyde, and propionaldehyde), g) alcohols (ally alcohol, ethanol, and propanol). 7</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1456,27 +2154,55 @@
           <t>S0026</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" t="n">
+        <v>6</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>The partial geometric current density associated with ethanol formation also increased, from 0.002 to 0.9 mA/cm2.</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>These results demonstrate the importance of HCOOH in C-C coupling to form ethanol on O atoms coordinated Sn catalytic sites.</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>In contrast, unlike the result for the Sn -O3G catalyst, 1 the Sn -N4G catalyst (with 4 nitrogen atoms coordinated Sn center) failed to produce any C2 products in 1 CO RR with addition of HCOOH (Extended data Figs. 46 and 47), indicating the critical roles of both the 2 single atomic Sn center and the coordinated oxygen atoms in Sn -O3G for the C-C coupling reaction.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>P5:HCOO</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1498,19 +2224,47 @@
           <t>S0027</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" t="n">
+        <v>4</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>To Thus,in-situATR-SEIRASwasemployedtofurtherevaluatetheimpact 2 investigate the localCO concentration ofdifferentinterfacialwettofinterfacialwettabilityontheadsorptionofintermediates(Fig.3d,e). 2 ability,controlsampleswerepreparedwithdifferentgas–liquid–solid There is a stretching band at ~2070cm−1 on all electrodes, correcontact, enabling in situ measurements with fluorescence electrospondingtothestretchingbandofthelinear-bondCO(CO )ontheCu L chemical spectroscopy (FES) at 100mAcm−2 chronopotentiometry surface43,44.Asforhydrophobic-treatedCuelectrodes,theCO bands L (Fig.3b).ThelocalCO concentrationofallsamplesdecreasestoanew becomemoreclearlydefinedatmoderateoverpotentials(−0.6to1.2V 2 steadystateduringelectrolysis.Asforthethree-phasecontactelecvs.RHE),indicatingalarger*COcoverage.Furthermore,CO bandsare L trode,increasinghydrophobicitycanshortentherelaxationtimeof preferentially observed on hydrophobic-treated Cu surfaces under thelocalCO concentrationandincreaseequilibriumconcentration, more negative potentials, with a wider voltage range of *CO 2 whichcanfacileCO masstransport.ThelocalCO concentrationwill coverage14,45.Theenhanced*COadsorptioncanbeattributedtothe 2 2 return back to the initial equilibrium value after electroreduction highproduction rateofthe accumulationofmore*COona hydro- (SupplementaryFig.30).TherecoveryoflocalCO concentrationon phobicCusurfaceunderahighlocalconcentrationofCO 31.Thedif2 2 the highly hydrophobic interface is faster due to the improved gas ferencein*COcoverageoverawidevoltagerangederivedfromthe diffusion.Theseresultsdemonstratethattheinterfacialcontactstate wettabilityofthecatalystlayerisoneofthekeyfactorsfortheethylene affectstheCO masstransportfromthebulkphasetothecatalyst,thus andethanolpathways. 2 affectingthelocalCO concentrationnearbythecatalyst. 2 The hydrophobic treatment also can promote CO diffusion in Effectofcontrollablewettabilityon*HcoverageviaH Omass 2 COreductionreactions.Thus,itcanbeexcludedthatthelimitedCO transport 2 masstransportatthehydrophilicCuelectrodeisentirelyduetothe As another key intermediate, the *H intermediate on the surface is neutralization of CO with the electrolyte (Fig. 3c, Supplementary convertedfromthebulksolution,whichisaffectedbyH Otransport. 2 2 Fig. 31).</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>Like in the CO RR, the direct coupling between two *CO InordertoelucidatetheeffectofH Otransportontheethyleneand 2 2 speciesintheCORRiswidelyacceptedasthemajorC–Ccoupling ethanol reaction pathways, the hydrogen evolution reaction (HER) mechanism.</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Moreover, *CO coverage is determined by the local performance of Cu catalysts with different wettability for various concentration of CO near the catalyst.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1532,27 +2286,55 @@
           <t>S0028</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" t="n">
+        <v>7</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Figure 3e and Extended data Fig. 48 show that the methyl C 1 (*CH ) in ethanol comes from HCOOH, while the C in CO goes to the methylene C (*CH OH).</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>Therefore, 3 2 2 Fig. 3f schematically summarizes the CO RR process to form ethanol taking place on the SnS /Sn -O3G. 2 2 1 The comprehensive discussion for the ethanol formation process on the SnS /Sn -O3G tandem catalyst 2 1 is provided from additional structural characterization and kinetics simulation (Extended data Figs. 49– 53 and Tables 9–17), indicating that diffusion of HCOOH generated from the SnS component to the 2 single atomic Sn sites on Sn -O3G is the rate-determining step for ethanol formation. 1 Based on the above experimental results, we built the active site model of the catalyst.</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Extensive DFT calculations were performed using the computational hydrogen electrode (CHE) model 22,23,24,25 to map the CO RR pathway and energetics during the formation of ethanol.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>P5:HCOO</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1574,19 +2356,47 @@
           <t>S0029</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" t="n">
+        <v>5</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>*H and *CO occupy most of the Cu coverage)onthesurface.Theseresultssuggestthatthevariationof 2 surfacesites,resultingindirectcompetitionbetween*Hand*COfor the interface contact state derived from the interfacial wettability surfacesites47.Whenthesurfacemaintainsahigh*COcoverage,the affects both CO and H O transport, which may be a solution for 2 2 corresponding *H coverage will decrease12,18,46,47.</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>According to the simultaneouslytuningkinetic-controlled*COand*H. results of in-situ ATR-SEIRAS spectra (Fig. 3d, e) and in-situ Raman ThelocalCO /HOratioderivedfromwettabilitymayaffectthe 2 2 spectra (Supplementary Fig. 35), higher hydrophobicity indicates coverage of *CO and *H, resulting in the reaction pathways toward higher *CO coverage, thus the corresponding *H coverage is lower. ethylene or ethanol.</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>CFD simulation is adopted to understand the Further, the surface coverage of intermediate (*CO, *H) is directly effectofwettabilityontheinterfacialcontactstateandthelocalCO / 2 proportionaltotheconcentrationofreactants(CO ,H O)5,42.ThereH O ratio, which can reveal the mechanism of wettability variation 2 2 2 fore,the*Hcoveragecanbededucedindirectlythroughwaterconinfluenceontheethyleneandethanolpathways(Fig.4g–j).Asshownin tent.Theconfocallaserscanningmicroscopymeasurements(CLSM) SEMimages,Cunano-islandsareuniformlygrownontheporoussurwere employed toobserve the variation of availablewater near the face of carbon paper with an average size of around 1μm (Suppleinterface(detailsinthe“Methods”section)(Fig.4d–f)48.Todetermine mentaryFigs.2and3).Therefore,thestructureoftheCuelectrodecan the relevance of absorbed water with different wettability, crossbesimplifiedascatalystislandswithpores.ToenabletheCFDsimusectionalimagesalongthez-axisarechosenforcomparison.Thegreen lation,asimplifiedmodelwasconstructed(Fig.4g).Thesquaresinthe fluorescent regions represent the electrolyte phase, while the dark modelareusedtorepresentthecatalystswithvariouscontactangles. regionsrepresentthegasphaseorsolidelectrode.Thedecaytailing Thegapsbetweenthesquaresrepresenttheporesbetweenthereal effect of fluorescence intensity atthe liquid phase boundaryreprecatalystislands(Fig.4g).Thesimulationresultsrevealtheformationof sents the decreasing of available water (since the H during CO RR acontinuousliquidlayeronthehydrophiliccatalyst(Cu)surfaceand 2 source from H O, which can represent *H coverage), which can be CO needsdiffusethroughthethinliquidlayertoreachthecatalystfor 2 2 valued by decay distance.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1608,19 +2418,47 @@
           <t>S0030</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Several couglycol only on polycrystalline copper16–18, suggesting an exclusive pling pathways have been proposed7,8, suggesting adsorbed CO (*CO) ethanol-selective route via *OCHCH.</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>Recently, a methyl carbonyl 2 as the building block of multi-carbon products5,9,10 via dimerization intermediate, *OCCH, has been proposed as an alternative intermedi3 (OC–CO)7 or coupling (OC–CHO or OC–COH)8 steps.</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Experimentally, ate for ethanol and propanol19,20.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1642,27 +2480,55 @@
           <t>S0031</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" t="n">
+        <v>5</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>These defects are probably formed under reaction conditions and were used to fit the recorded potential-dependent Raman spectra. generate distinct surface sites with strong CO binding.</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>C–O stretching bands with intermediate frequencies (2,075 cm−1 and On the basis of these mechanistic insights, we aimed to correlate 2,090 cm−1) become the main contribution at −0.76 V , from which specific active sites and reaction intermediates with ethylene and RHE the *OCCO intermediate is identified and ethylene is produced, in line ethanol production during CORR.</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Recent experimental studies have 2 with the observation of a 2,060 cm−1 CO precursor reacting towards highlighted the relevance of defects and polarized Cu sites in enabling C–C coupling as reported in a previous SERS study6.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>P1:*OCCO; P1:OCCO</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1684,19 +2550,47 @@
           <t>S0032</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" t="n">
+        <v>8</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>A water ties (R2 = 0.82 (ref. 51); Supplementary Fig. 26 and Supplementary immersion objective with a long working distance (Leica MicrosysTable 19).</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>Besides, in situ Raman spectroscopy during CO, CO and tems, ×63, numerical aperture of 0.9) was chosen to perform the in situ 2 glyoxal reduction to ethanol confirms the existence of a shared reacexperiments in an electrolyte.</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>The objective with a long working distion intermediate, which is reasonably OCHCH (Supplementary tance was needed to avoid diffusion hindrance during the Raman 2 Fig. 28).</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1718,19 +2612,43 @@
           <t>S0033</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>ElectrochemicalCO reduction reaction (CO RR) offersa promising attractive6–10.</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>Unfortunately, the catalytic performance of electro2 2 strategy to achieve carbon neutrality by converting CO into valuechemicalCO reductiontoC productsisstillfarfromsatisfactory 2 2 2+ added carbon-containing fuels or chemicals using renewable withlowselectivityandsluggishreactionkinetics11,12. electricity1–5.ComparedtoC products,directconversionofCO to The slow carbon-carbon (C-C) coupling reaction is the fun1 2 multi-carbon (C ) products (e.g., ethylene, ethanol, etc.) is more damental issue for poor conversion of CO to C products13,14. 2+ 2 2+ 1DepartmentofChemicalPhysics,UniversityofScienceandTechnologyofChina,Hefei230026,P.R.China.2StateKeyLaboratoryofCatalysis,Dalian InstituteofChemicalPhysics,ChineseAcademyofSciences,Dalian116023,P.R.China.3DepartmentofMaterialsScienceandEngineering,CityUniversityof HongKong,Kowloon,HongKongSAR999077,China.4DepartmentofChemistry,HongKongInstituteofCleanEnergy(HKICE)&amp;CenterofSuper-Diamond andAdvancedFilms(COSDAF),CityUniversityofHongKong,Kowloon,HongKongSAR999077,China.5VacuumInterconnectedNanotechWorkstation, SuzhouInstituteofNanoTechandNanoBionics,ChineseAcademyofSciences,Suzhou215123,P.R.China.6DepartmentofAppliedChemistryandCenterfor EmergentFunctionalMatterScience,NationalYangMingChiaoTungUniversity,Hsinchu300,Taiwan.7SchoolofComputerandCommunicationEngineering,DalianJiaotongUniversity,Dalian116028,P.R.China.8NationalSynchrotronRadiationResearchCenter,Hsinchu300,Taiwan.9Theseauthors contributedequally:ShifuWang,FuhuaLi. e-mail:lixn@dicp.ac.cn;yqhuang@dicp.ac.cn;bliu48@cityu.edu.hk NatureCommunications|( 2024)1 5:10247 1 ;,:)(0987654321 ;,:)(0987654321</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1752,19 +2670,47 @@
           <t>S0034</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" t="n">
+        <v>8</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Consequently, the affinity of the Cu catalyst 0.01mM,Fig.6f)fromthe1HNMRspectrum,suggestingthattheCA 2 5 towardoxygenin*OC H willhaveaneffectontheinteractionintensity was continuously enriched in the Helmholtz plane.</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>This result sug2 3 ofCuwithadsorbed*OC H intermediate,i.e.,thestrengthofCu–O gested that the CA enriched in the Helmholtz plane, which was 2 3 (*OC H ) bond, and correspondingly changed the stability of C–O achievedbytheuniqueinsidetoon-surfacediffusionapproach,canbe 2 3 bondof*OC H intermediate.Accordingly,thisdeterminedthecleaconsistently maintained by the innovative asymmetric pulsed elec2 3 vageversuspreservationofC–Obond,resultinginthesynthesisof trolysisstrategy,furtherfacilitatedtheefficientandcontinuouselechydrocarbonversusoxygenatedproducts.TheinteractionofCuwith trosynthesisofvalue-addedC HOHproduct. 2 5 adsorbed *OC H intermediate and C–O internal bond strength of 2 3 *OC H onCu(100)andCu(100)-CAwereinvestigatedbythecrystal CO emissionandTEAofCO RRprocess 2 3 2 2 orbitalHamiltonpopulations(COHP).TheCOHPresultsandtheinteAfterverifyingthattheuniqueinsidetoon-surfacediffusionapproach grated overlap populations up to Fermi level (ICOHP) of C–O and canachieveanefficientandstableC HOHelectrosynthesis,wefurther 2 5 Cu–O bonds on Cu(100) and Cu(100)-CA were shown in Fig. 5e, f. validatedthepotentialofthisapproachforthescale-upproductionof According to the ICOHP theory, more negative ICOHP value repreC HOHinalarge-area(25cm2)membraneelectrodeassembly(MEA) 2 5 sentedstrongerbondstrength53,54.WithCA,thestrengthofC–Obond electrolyzer,whereahighFE andCO conversionrateof45.2% C2H5OH 2 wasstrong,whiletheCu–Ointeractionwasweak.Inbrief,theadsorand12%aswellasanenergyefficiency(EE)of16.6%wereachieved bedCAmoleculeweakenedtheinteractionbetweenCuandOatoms, underanindustrialcurrentof5A(SupplementaryFig.26,27).Also,we stabilizingtheC–Obondwithinthe*OC H andallowingOatomtobe investigatedCO emissionreductionandperformedTEAbasedonthe 2 3 2 retained,thuspromotingtheformationofoxygen-containingC HOH. tested electrochemical performance data to evaluate the environ2 5 TheelectroreductionpathwayfromCO toC HOHandcorrespondmental impact and economicfeasibility of this industrialCO RR-to2 2 5 2 ingchangeinselectivitybyCAmoleculewereshowninFig.5g.Further, C HOH conversion55–58.</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Here, distillation was employed for the 2 5 theΔGofeachstepfrom*OC H toC H andC HOHonCu(100)and separationofC HOHproducedbyCO RR,whichwasduetothefact 2 3 2 4 2 5 2 5 2 Cu(100)-CA were calculated and shown in Fig. 5h, i, corresponding thatthedistillationwascommonlycommercialwayofseparationand modelstructureofreactionintermediateswerealsoshowninFig.5j purification for alcohols.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1786,19 +2732,47 @@
           <t>S0035</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" t="n">
+        <v>4</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Moreover, we found that the reaction barall exhibit the same tendency like (322) facet.</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>It is noteworthy, riers of C–C coupling on p-sq, s-sq and cv-sq sites are 0.33eV, that, Cu(100) and Cu(751), which experimentally show more 0.72eV, and 0.39eV, respectively, much lower than 0.85eV and selective for ethylene and alcohols7, fall in their respective pro1.19eVon(111)and(221)facets(Fig.2g).Basedontheanalysis duct region, thus meaning the bond length of C–O in adsorbed above,threeactivesites,p-sq,s-sqandcv-sqsites,whichfavorfor *CH CHO may be a simple descriptor for the selectivity of 2 C 2+ products production have been identified on OD-Cu. ethylene and alcohols on different surface structures.</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Previous work proved that ethylene and ethanol are not genThe specific geometry of step-square site explains the differeratedfromthesametypesofactivesites,whichmeanstheC–C enceinselectivity.Figure3eshowsthatthegeneralcoordination couplingactivesitescanbefurthersubdivided16.Fromcalculated number (GCN) of s-sq is the lowest (5.50), thus showing the free energy profiles of the whole reaction pathway (Supplemenstrongest adsorption energy of acetaldehyde intermediate taryFigs.24–26),*CH CHOservesastheselectivitydetermining (*CH CHO),leadingtothehydrogenationpathwaydominances. 2 3 intermediate (SDI), which corresponds to previous calculations Meanwhile, p-sq and cv-sq can supply the fourfold sites to staon copper single crystal facets27,28.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1820,27 +2794,55 @@
           <t>S0036</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" t="n">
+        <v>7</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Combining with time-independent spectral analysis (SupoxidationstateofCu+speciesduringCO electroreduction,allowing 2 plementaryFig.33A,B),apparentpeaksaredeterminedat1064and forthesynergisticeffectofCuandCu+species. 1558cm−1, which correspond well to the symmetric and asymmetric ThereactionbarriersforthehydrogenationprocessofC inter2+ vibrationsofthe*OCCOHintermediate,respectively49,50.Inaddition, mediatesonthemodelsofCu/CuOwithandwithoutCl,respectively, 2 thestretchingvibrationat1335and1716cm−1areincloseproximityto werecalculatedbyDFT.Firstly,byanalyzingtheBaderchargeandbond thestretchingof*OCH CH and*CHO,respectively,whichserveasthe length of Cu/CuO (Fig. 5C, D), it is observed that the lower Bader 2 3 L 2 important intermediates for the subsequent C–C coupling in the chargevalue(0.477|e|)comparedtoCu /CuO(1.01|e|)indicatesthat P 2 productionofC alcohols51,52.Theseconclusionsareconsistentwith thepopulatedelectronicorbitalsoflow-coordinatedCusiteswilleasily 2+ theresultsobtainedfromtheproductanalysisofCu /Cu OandCu / bindtointermediatesandreducetherate-determiningenergybarrier67.</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>P 2 L Cu O.IntheRamanspectra(Fig.5BandSupplementaryFig.33D),the Cu/CuOwithadditionallyformedemptyorbitalscanfacilitateelectron 2 L 2 Cu /Cu Opowderloadedoncarbonpapersubstrateexhibitstypical transferfromhydrogentonucleophilicintermediates,suggestingtheCu L 2 characteristic peaks of adsorbed *CO intermediates, which are 3dorbitalsoverlapwiththeπorbitalsofCandfurtherreducedactivation deconvoluted into a low-frequencyband (LFB) at ∼2045cm−1 and a energyforCO hydrogenationonCu/CuO68.Asaresult,thenucleo2 2 high-frequencyband(HFB)at∼2097cm−1,whichverifiesthebonding philic addition reaction process of *CHCO–*CO coupling may effec2 stylesonterraceandstepsites,respectively53,54.Aredshiftoftheυ(CO) tivelyreactonthemixed-valenceboundaryregion33,whichreducesthe bandindicatestheenhancedinteractionbetweenthecatalystsurface formation energy of *CHCOCO on Cu/CuO (−0.148eV) toward 2 L 2 and *CO, resulting in a higher *CO coverage55.</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>In addition, the fren-propanol(Fig.5E,SupplementaryFig.35,andSupplementaryTable6). quenciesofυ(CO)bandsarecorrelatedwiththecoordinationstatesof For the C–C coupling on Cu/CuO model (Fig. 5F, Supplementary L 2 Cusites.Therefore,thelow-coordinationstatesofCusitesinCu /Cu O Fig.36andSupplementaryTable7),the*CO–COHcouplingistherateL 2 willinduceapositiveshiftofthed-bandcenterofCuandboostthe determiningstepforCu/CuOcatalyst(1.46eV),indicatingthevitalrule L 2 hybridizationofthed-bandwiththe2π*orbitalofCO.TheHFBmodes of *CO coverage in the post-coupled proton-electron transfer (CPET) derivedfromthelow-coordinatedCusiteswillfavorthebreedingof reaction.Theenergybarriersofintermediatesgraduallydecreaseuntil theυ(C–C)band(~1960cm−1),whereablueshiftmaypredictthepro- *CHOisreached,whichcanbefurtherreducedto*CH Oor*Ofor 2 3 2 4 tonationprocessC–Cbonds29,30.Onthecontrary,theweaksignsofthe ethanol or CH , respectively.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>P1:COCO</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1862,19 +2864,43 @@
           <t>S0037</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" t="n">
+        <v>4</v>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
         <is>
           <t>C-C coupling pathway for ethanol synthesis via the CO RR, with a low activation energy, high selectivity 2 and good stability.</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>These properties can be attributed to the dual active centers of Sn and O in Sn -O3G, 1 which are able to adsorb *CHO and *CO(OH) intermediates, respectively, thereby promoting the subsequent C-C coupling of these intermediates to form ethanol.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1896,19 +2922,47 @@
           <t>S0038</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" t="n">
+        <v>4</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Water shows 2 a broad O–H bending band at about 1,600 cm−1 (refs. 14,15) (SuppleCu active sites selective for CO RR to ethylene 2 mentary Table 13), limiting the identification of vibrations from other and ethanol species in this regime.</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>In agreement with our assignment, the peak at The potential-dependent formation of C–C coupling intermediates about 1,602 cm−1 still appears after the DO/HO isotope exchange. explains the selectivity trend towards C products observed during 2 2 2+ Besides, the DO/HO exchange negligibly affected the peaks at about CORR.</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>In correspondence with an increase in the CO coverage from 2 2 2 Nature Energy | Volume 9 | December 2024 | 1485–1496 1488 ).u.a( ytisnetnI –0.36 V versus RHE –0.76 V versus RHE –0.85 V versus RHE 1,070 cm–1 1,390 cm–1 1,610 cm–1 1,450 cm–1 1,550 cm–1 1,182 cm–1 1,318 cm–1 1,453 cm–1 1,595 cm–1 N = 4–5 N = 7–8 Cu–Cu Cu–Cu N = 6–7 N = 8–9 Cu–Cu Cu–Cu OCHCH OCCO– 2 CO 2– 3 HCOOH O s COCO2– OCHCH 3 Raman shift (cm–1) Fig. 3 | DFT-optimized CORR reaction intermediates and their vibrational highlighted in the panels by vertical dashed lines.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1930,19 +2984,47 @@
           <t>S0039</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" t="n">
+        <v>8</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Faradaic efficiency for both products in Supplementary Fig. 26 and XPS measurements were performed with a commercial hemispherSupplementary Table 19). ical analyser (Phoibos 150, MCD-9 Detector, SPECS, E = 15 eV) and a pass Thus, although a methyl carbonyl intermediate (OCCH) was monochromatic X-ray source (SPECS) with an Al anode (E = 1,486.7 eV 3 Kα recently suggested as the ethanol precursor during CHI and acetaldeas X-ray energy) at a power of P = 300 W.</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>All spectra were aligned by 3 hyde/CO reduction20, we here identify *CHCO reduction to *OCHCH fixing the Cu 2p of Cu0 and Cu+ to 932.67 eV as a reference. 2 3/2 as the selectivity switch (selectivity-determing step 2, SDS2) to ethanol, acetaldehyde, 1-propanol and allyl alcohol (Supplementary In situ Raman experiments Note 1 and Supplementary Figs. 28 and 29), as confirmed by the The in situ Raman spectra were obtained using a Renishaw (InVia strong correlation between acetaldehyde and ethanol selectiviReflex) confocal Raman microscope with a 785 nm laser.</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>A water ties (R2 = 0.82 (ref. 51); Supplementary Fig. 26 and Supplementary immersion objective with a long working distance (Leica MicrosysTable 19).</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1964,19 +3046,43 @@
           <t>S0040</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" t="n">
+        <v>16</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>The microstructure of Co -Sub-CuS remained intact after CO ER (Supplementary Figs. 0.050 2 55-56).</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>Deciphering Ethanol Reaction Pathways EtOH and C H follow similar CO ER pathways, both undergoing protonation to the shared 2 4 2 intermediate *CHCO, where the bonding configuration of its protonated form *CHCHO plays a</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1998,27 +3104,51 @@
           <t>S0041</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" t="n">
+        <v>6</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>In contrast, unlike the result for the Sn -O3G catalyst, 1 the Sn -N4G catalyst (with 4 nitrogen atoms coordinated Sn center) failed to produce any C2 products in 1 CO RR with addition of HCOOH (Extended data Figs. 46 and 47), indicating the critical roles of both the 2 single atomic Sn center and the coordinated oxygen atoms in Sn -O3G for the C-C coupling reaction.</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>We 1 also investigated the CO RR products generated by the Sn -O3G catalyst using gaseous CO and HCOOH 2 1 as the reactants and found no C2 products, indicating the critical role of the adsorbed *CO(OH) intermediate (see below) formed via CO reduction on the Sn -O3G site in the formation of ethanol. 2 1 Page 6/14</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>P5:HCOO</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2040,19 +3170,47 @@
           <t>S0042</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" t="n">
+        <v>8</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>atom of Sn -O3 and the C of the support, the Sn -O3G catalyst is distinguished by the dual active sites of 1 1 Sn and O that are able to adsorb different C-based intermediates, providing a novel platform for C-C bond formation during the CO RR to produce ethanol. 2 In summary, we have developed a Cu-free, Sn-based tandem catalyst to produce ethanol from the CO RR, 2 in which the dual active centers of Sn and O atoms on Sn -O3G serve to adsorb different C-based 1 intermediates, which effectively lowers the C-C coupling energy between *CO(OH) and *CHO.</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>Our tandem catalyst enables a formal-bicarbonate coupling pathway, which not only provides a novel platform for C-C bond formation during ethanol synthesis and overcomes the restrictions of Cu-based catalysts, but also offers a unique strategy for manipulating CO reduction pathways toward desired products. 2 References 1.</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Hasselmann, K. et al.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2074,27 +3232,55 @@
           <t>S0043</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" t="n">
+        <v>8</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>These undercoordinated sites are mainly selective to as well.</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
         <is>
           <t>For the steady-state experiment, each potential was applied ethylene via the traditional route, *CO–CO or *CO–COH couplings, for at least 10 min before collecting the spectra to ensure steady-state which are C product precursors.</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>However, defects characterized by conditions at the surface of the catalyst. 2+ a highly compressed and distorted coordination environment and deep s-band states are instead generated at higher overpotentials and CORR testing 2 stabilize the adsorption of OCHCH via the terminal oxygen, opening Electrocatalytic measurements were performed with a Biologic SP-240 2 an alternative selective route towards ethanol on copper.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>P3:CO-COH; P3:CO–COH</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2116,27 +3302,55 @@
           <t>S0044</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" t="n">
+        <v>8</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Article https://doi.org/10.1038/s41560-024-01633-4 The hypothesis of OCCO(H) as a common C precursor for CO Methods 2+ 2 reduction is reinforced by the strong correlation between ethanol Electrode preparations and ethylene Faradaic efficiency on copper (R2 = 0.90, values taken A commercial polycrystalline copper foil (Advent Research Materials, from ref. 51; see Supplementary Fig. 26 and Supplementary Table 19). 99.995%) was used in all experiments.</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
         <is>
           <t>Before each experiment, the copIn line with recent advances20, additional parallel pathways, such as per foil was electropolished at 3 V versus a titanium foil for 3 min in a CO–CH coupling (grey arrows, Fig. 7), may also open, yet our DFT HPO/HSO solution consisting of 130 ml HPO (VWR, 85 wt%), 20 ml x 3 4 2 4 3 4 simulations disprove any major role of these on distorted sites.</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>In fact, HSO (VWR, 95%) and 60 ml ultrapure water.</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
         <is>
           <t>P6</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>P6:parallel pathway</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2158,19 +3372,47 @@
           <t>S0045</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" t="n">
+        <v>8</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>*OCHCH (ref. 7; characterized by a double C–C bond, of 1° to decrease the bulk contribution of the Cu foil. 2 see Supplementary Table 18) can either reduce to acetaldehyde and The size and morphology of the samples were determined by SEM ethanol or couple with a CO/COH species to form allyl alcohol and, with a ThermoFisher Apreo microscope and a Hitachi S-4800 system, at later reduction stages, 1-propanol51 (see the correlation between including a cold field emission gun.</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
         <is>
           <t>Faradaic efficiency for both products in Supplementary Fig. 26 and XPS measurements were performed with a commercial hemispherSupplementary Table 19). ical analyser (Phoibos 150, MCD-9 Detector, SPECS, E = 15 eV) and a pass Thus, although a methyl carbonyl intermediate (OCCH) was monochromatic X-ray source (SPECS) with an Al anode (E = 1,486.7 eV 3 Kα recently suggested as the ethanol precursor during CHI and acetaldeas X-ray energy) at a power of P = 300 W.</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>All spectra were aligned by 3 hyde/CO reduction20, we here identify *CHCO reduction to *OCHCH fixing the Cu 2p of Cu0 and Cu+ to 932.67 eV as a reference. 2 3/2 as the selectivity switch (selectivity-determing step 2, SDS2) to ethanol, acetaldehyde, 1-propanol and allyl alcohol (Supplementary In situ Raman experiments Note 1 and Supplementary Figs. 28 and 29), as confirmed by the The in situ Raman spectra were obtained using a Renishaw (InVia strong correlation between acetaldehyde and ethanol selectiviReflex) confocal Raman microscope with a 785 nm laser.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2192,19 +3434,47 @@
           <t>S0046</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" t="n">
+        <v>3</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Here, we present a subsurface Co-doped CuS (Co-Sub-CuS) 2 catalyst, which exhibits directed selectivity toward ethanol.</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>We elucidate the role of subsurface doping in enhancing the oxophilicity of surface Cu sites, thereby facilitating the conversion of key intermediates (*CHCHO*) via the formation of surface-O bonds, Sguiding subsequent protonation S towards ethanol.</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Moreover, the surface sulfur vacancies cEreated by subsurface Co-doping help R regulate the optimal distance between dual sites, faciliPtating asymmetric C-C coupling.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2226,19 +3496,47 @@
           <t>S0047</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" t="n">
+        <v>4</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Thus, FE increased thecarbonylC productsbyafactorofthree(Figure4f,S7f). ethanol 2+ 1.5times by the addition of 5at% of Ag to CuONCs.</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>Overall, introducing Ag increases the FE of the desired C 2 2+ Additionally,theproductionof1-propanolisdoubledinthe liquid products (Figure4e, S7e) for 5-Ag/CuO by 15% in 2 Ag/CuOsampleswithFEof5–6%at@0.9V compared comparisontoCuONCsat@1.0V .Thisisassignedtothe 2 RHE 2 RHE to3%fortheCuONCs(Figure4b).Thisincreaseinalcohol enhanced production of ethanol, 1-propanol, allyl alcohol, 2 yieldhasbeenpreviouslylinkedtoCOspilloverfromAgto andcarbonylC products(Figure4a,b,f,S9c).Weaddition2+ Cu, since the weaker binding between Ag and the *CO ally performed long-term CORR measurements for 12h at 2 intermediate is considered to facilitate CO production as @1.0V totrackthestabilityofthecatalyticperformance RHE compared to the moderate binding energy between Cu and (FigureS12) and found a good stability for all catalysts.</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>For the *CO intermediate leading to the formation of hydrothe Ag/CuO samples, the amount of C liquid products 2 2+ carbons.[4,10] Also in our case, the Ag/CuO samples show remainsstableovertimewithadecreaseofthealdehydesand 2 higherFEsforCOatlowoverpotentials,withalmost40%FE Angew.Chem.Int.Ed.2021,60,7426–7435 T2021TheAuthors.AngewandteChemieInternationalEditionpublishedbyWiley-VCHGmbH www.angewandte.org 7429 15213773, 2021, 13, Downloaded from https://onlinelibrary.wiley.com/doi/10.1002/anie.202017070 by CochraneAustria, Wiley Online Library on [23/05/2026].</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2260,19 +3558,43 @@
           <t>S0048</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" t="n">
+        <v>6</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>RHE acetate formation with increasing OH − concentration6,8,16.</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>In BesidesthethreeTSsfortheinitialprotonationofCHCO*,we fact, the ethanol/ethylene molecular ratios (with acetate also note that the relative rate of the CHCOH pathway is 6 NATURECOMMUNICATIONS| (2022) 13:1399 |https://doi.org/10.1038/s41467-022-29140-8|www.nature.com/naturecommunications</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2294,27 +3616,55 @@
           <t>S0049</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" t="n">
+        <v>6</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>These results demonstrate the importance of HCOOH in C-C coupling to form ethanol on O atoms coordinated Sn catalytic sites.</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
         <is>
           <t>In contrast, unlike the result for the Sn -O3G catalyst, 1 the Sn -N4G catalyst (with 4 nitrogen atoms coordinated Sn center) failed to produce any C2 products in 1 CO RR with addition of HCOOH (Extended data Figs. 46 and 47), indicating the critical roles of both the 2 single atomic Sn center and the coordinated oxygen atoms in Sn -O3G for the C-C coupling reaction.</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>We 1 also investigated the CO RR products generated by the Sn -O3G catalyst using gaseous CO and HCOOH 2 1 as the reactants and found no C2 products, indicating the critical role of the adsorbed *CO(OH) intermediate (see below) formed via CO reduction on the Sn -O3G site in the formation of ethanol. 2 1 Page 6/14</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>P5:HCOO</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2336,19 +3686,43 @@
           <t>S0050</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" t="n">
+        <v>7</v>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
         <is>
           <t>To elucidate the mechanism of ethanol formation through the CO RR, isotopically-labeled reactants 2 (12CO , 13CO , H12COOH and H13COOH) were used to trace the pathway of the C atoms in the nal C2 2 2 product formed on the Sn -O3G catalyst.</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Figure 3e and Extended data Fig. 48 show that the methyl C 1 (*CH ) in ethanol comes from HCOOH, while the C in CO goes to the methylene C (*CH OH).</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2370,19 +3744,47 @@
           <t>S0051</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>In fact, glyoxal some consensus has been reached, the dependence of these paths on and glycolaldehyde reduce to acetaldehyde, ethanol and ethylene the particular material history is yet to be confirmed5,6.</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
         <is>
           <t>Several couglycol only on polycrystalline copper16–18, suggesting an exclusive pling pathways have been proposed7,8, suggesting adsorbed CO (*CO) ethanol-selective route via *OCHCH.</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Recently, a methyl carbonyl 2 as the building block of multi-carbon products5,9,10 via dimerization intermediate, *OCCH, has been proposed as an alternative intermedi3 (OC–CO)7 or coupling (OC–CHO or OC–COH)8 steps.</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2404,19 +3806,47 @@
           <t>S0052</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" t="n">
+        <v>4</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Instead, these signals were also result from (a set of) very similar adsorbates. not observed for ethanol reduction (Supplementary Fig. 21).</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
         <is>
           <t>Thus, we In addition, we carried out 13Cor D-labelling SERS experiments reasonably confirmed the detection of a common intermediate along at −0.95 V (Fig. 4a). 13C/12C exchange led to obvious redshifts of the CO, CO and glyoxal reduction route to ethanol, which is *OCHCH.</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>RHE 2 2 the 1,455 cm−1 and 1,602 cm−1 peaks, in addition to the CO stretching Overall, the presence of CO molecules on the Cu surface during CORR 2 (2,100 cm−1), Cu–CO stretching (358 cm−1) and CO rotation (275 cm−1) is linked to and probably causes the formation of *CO–CO or *CO–COH bands, proving that these peaks are related to the CORR process.</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2438,19 +3868,43 @@
           <t>S0053</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D54" t="n">
+        <v>5</v>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
         <is>
           <t>0.5 0.4 0.3 0.2 0.1 0 0 0.1 0.2 0.3 0.4 0.5 square-like sites are responsible for C–C coupling, low coordiThe ratio of three theoretically identified active sites, p-sq, s-sq, nated sites are conducive to further protonation for alcohols. andcv-sqsites,decreasedwithincreasingannealingtemperatureas Very recent study35 found that square, four-atom Cu islands are well.</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>From our theoretical models, the OD-Cu surface before the active sites for generating ethanol.</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2472,19 +3926,47 @@
           <t>S0054</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D55" t="n">
+        <v>7</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>In addition, the fren-propanol(Fig.5E,SupplementaryFig.35,andSupplementaryTable6). quenciesofυ(CO)bandsarecorrelatedwiththecoordinationstatesof For the C–C coupling on Cu/CuO model (Fig. 5F, Supplementary L 2 Cusites.Therefore,thelow-coordinationstatesofCusitesinCu /Cu O Fig.36andSupplementaryTable7),the*CO–COHcouplingistherateL 2 willinduceapositiveshiftofthed-bandcenterofCuandboostthe determiningstepforCu/CuOcatalyst(1.46eV),indicatingthevitalrule L 2 hybridizationofthed-bandwiththe2π*orbitalofCO.TheHFBmodes of *CO coverage in the post-coupled proton-electron transfer (CPET) derivedfromthelow-coordinatedCusiteswillfavorthebreedingof reaction.Theenergybarriersofintermediatesgraduallydecreaseuntil theυ(C–C)band(~1960cm−1),whereablueshiftmaypredictthepro- *CHOisreached,whichcanbefurtherreducedto*CH Oor*Ofor 2 3 2 4 tonationprocessC–Cbonds29,30.Onthecontrary,theweaksignsofthe ethanol or CH , respectively.</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>The Cu/CuO model exhibits a more 2 4 L 2 υ(CO)andυ(C–C)bandsonCu /Cu Ocatalystalsoverifythepoor*CO stable adsorption for CH O* (−0.293eV) than Cu /CuO (−0.154eV), P 2 2 4 P 2 coverageandC–Ccoupling(SupplementaryFig.34B).Toverifythe implying facilitated thermodynamics for increasing the adsorption of originoftheoxidationstateofCu /Cu O,Ramanspectroscopywas keyintermediate.</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>L 2 conducted in the shift range of 200–1600cm−1, and the results are presentedinSupplementaryFigs.33Aand34A.InthecaseofCl–Cu O Discussion 2 samples, characteristic signals were observed at 224, 425, 522, and Thementionedtheoreticalandexperimentalstudiesprovidetangible 626cm−1,whichwereattributedtothe2Γ− ,4Γ− ,Γ+ ,andΓ− +Γ+ proofthattheenhancedrectifyinginterfaceoflow-coordinatedCu/CuO 12 12 25 12 25 2 phonon modes, respectively56,57.</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2506,19 +3988,47 @@
           <t>S0055</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Recently, pos2 2 2+ approach to store intermittent renewable energy as valuable fuels and sible C–C coupling intermediates *OCCO or *OCCOH were detected feedstocks1,2.</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
         <is>
           <t>In particular, the synthesis of multi-carbon (C ) products, by infrared spectroscopy during the electrochemical reduction of 2+ such as ethylene and ethanol, is highly attractive because of their verCO (COR)14,15.</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>However, while CO coupling has been repeatedly consatility in the chemical and energy industries3, and processes involving firmed, observing and tracking potential-dependent CO dimerization C–C bond formation are of great relevance from the point of view of and intermediates during the subsequent gradual reduction process fundamental research2,4. towards final products has not yet been achieved.</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2540,19 +4050,47 @@
           <t>S0056</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D57" t="n">
+        <v>8</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>For the steady-state experiment, each potential was applied ethylene via the traditional route, *CO–CO or *CO–COH couplings, for at least 10 min before collecting the spectra to ensure steady-state which are C product precursors.</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
         <is>
           <t>However, defects characterized by conditions at the surface of the catalyst. 2+ a highly compressed and distorted coordination environment and deep s-band states are instead generated at higher overpotentials and CORR testing 2 stabilize the adsorption of OCHCH via the terminal oxygen, opening Electrocatalytic measurements were performed with a Biologic SP-240 2 an alternative selective route towards ethanol on copper.</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>By combining potentiostat in an H-type cell equipped with an anion exchange memthe potential-dependent evolution of CO adsorption and C–C coupling brane (Selemion AMV, AGC).</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2574,27 +4112,51 @@
           <t>S0057</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D58" t="n">
+        <v>8</v>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
         <is>
           <t>Article https://doi.org/10.1038/s41560-024-01633-4 The hypothesis of OCCO(H) as a common C precursor for CO Methods 2+ 2 reduction is reinforced by the strong correlation between ethanol Electrode preparations and ethylene Faradaic efficiency on copper (R2 = 0.90, values taken A commercial polycrystalline copper foil (Advent Research Materials, from ref. 51; see Supplementary Fig. 26 and Supplementary Table 19). 99.995%) was used in all experiments.</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Before each experiment, the copIn line with recent advances20, additional parallel pathways, such as per foil was electropolished at 3 V versus a titanium foil for 3 min in a CO–CH coupling (grey arrows, Fig. 7), may also open, yet our DFT HPO/HSO solution consisting of 130 ml HPO (VWR, 85 wt%), 20 ml x 3 4 2 4 3 4 simulations disprove any major role of these on distorted sites.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>P1:OCCO</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2616,19 +4178,47 @@
           <t>S0058</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D59" t="n">
+        <v>8</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Besides, in situ Raman spectroscopy during CO, CO and tems, ×63, numerical aperture of 0.9) was chosen to perform the in situ 2 glyoxal reduction to ethanol confirms the existence of a shared reacexperiments in an electrolyte.</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
         <is>
           <t>The objective with a long working distion intermediate, which is reasonably OCHCH (Supplementary tance was needed to avoid diffusion hindrance during the Raman 2 Fig. 28).</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>The reduction of OCHCH to OCHCH is thermodynamically measurements13.</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2650,19 +4240,43 @@
           <t>S0059</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D60" t="n">
+        <v>2</v>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
         <is>
           <t>Article https://doi.org/10.1038/s41467-024-54636-w Mechanistically,theCO -to-C pathway(eg.,ethylene,ethanol)is summarized in the Supplementary Methods.</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>One-dimensional Cu 2 2+ conventionallyconsideredtoproceedviaacomplexC-Ccoupling nanowires with an average diameter of 45±3nm were imaged by mechanism involving various intermediates such as *COCO, scanningelectronmicroscopy(SEM)andtransmissionelectronmicro- *COCHO, *COCOH, *CH CO, and *OCHCH , etc1,15–25.</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2684,27 +4298,55 @@
           <t>S0060</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D61" t="n">
+        <v>8</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Article https://doi.org/10.1038/s41467-024-54636-w dynamicoxidationstateevolutionofCuandAgoverAgCuNWand Characterization AgCuNWduringCO RR.FollowingacombinationofoperandoRaman ThecrystalstructureofCuNW,AgCuNWandAgCuNWwerechar1 2 1 spectroscopyandoperandoATR-SEIRASmeasurements,ahigher*CO acterizedbyX-raydiffraction(XRD,BrukerAXSD8Advance)withCu coverage was observed over AgCu NW surface, which would favor Kα radiation (λ=1.5406Å).</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
         <is>
           <t>The morphology of the catalysts was symmetric*CO-*COcouplinginCO RRtoproduceethylene.Onthe examined by transmission electron microscopy (HRTEM, JEOL JEM2 contrary, the in-situ formed *OH species via H O dissociation was 2100F operated at 200kV) and field-emission scanning electron 2 dominantly found over AgCu NW.</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Isotopic labelling experiments microscopy(FESEM,JSM-6700F)equippedwithanenergydispersive 1 indicated that the methyl C (*CH ) and methylene C (*CH OH) in X-rayspectroscopy(EDX,AztecX-Max80T).High-angleannulardark3 2 ethanol product were originated from the *CO and *HCHO interfield scanning transmission electron microscopy (HAADF-STEM) mediates,respectively.Theoreticalcalculationsfurtherdemonstrated characterizationwasconductedonaJEOLJEMARM200FSTEM/TEM thattheatomicallydispersedAgcouldnotonlypromotedissociation withaguaranteedresolutionof0.08nm.DetailedchemicalcomposiofH OtoreleaseH+,butalsoreducetheenergybarrierforthefortionswereanalyzedbyX-rayphotoelectronspectroscopy(XPS)onan 2 mation of *CHO over its neighboring Cu site, resulting in the sigESCALAB250photoelectronspectrometer(ThermoFisherScientific) nificantly promoted asymmetric *CO-*CHO coupling over paired Cu using a monochromatic Al Kα X-ray beam (1,486.6eV).</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>P1:*COCO; P1:COCO</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2726,19 +4368,47 @@
           <t>S0061</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D62" t="n">
+        <v>8</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Isotopic labelling experiments microscopy(FESEM,JSM-6700F)equippedwithanenergydispersive 1 indicated that the methyl C (*CH ) and methylene C (*CH OH) in X-rayspectroscopy(EDX,AztecX-Max80T).High-angleannulardark3 2 ethanol product were originated from the *CO and *HCHO interfield scanning transmission electron microscopy (HAADF-STEM) mediates,respectively.Theoreticalcalculationsfurtherdemonstrated characterizationwasconductedonaJEOLJEMARM200FSTEM/TEM thattheatomicallydispersedAgcouldnotonlypromotedissociation withaguaranteedresolutionof0.08nm.DetailedchemicalcomposiofH OtoreleaseH+,butalsoreducetheenergybarrierforthefortionswereanalyzedbyX-rayphotoelectronspectroscopy(XPS)onan 2 mation of *CHO over its neighboring Cu site, resulting in the sigESCALAB250photoelectronspectrometer(ThermoFisherScientific) nificantly promoted asymmetric *CO-*CHO coupling over paired Cu using a monochromatic Al Kα X-ray beam (1,486.6eV).</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
         <is>
           <t>All binding atoms adjacent to the single Ag atom, greatly boosting electroenergieswerereferencedtotheC1speak(284.8eV).TheconcentrachemicalCO reductiontoethanol. tionofAginAgCuNWandAgCuNWwerequantifiedbyinductively 2 1 coupledplasmaopticalemissionspectroscopy(ICP-OES).Forex-situ Methods XASmeasurements,acertainamountofpowdersampleswereplaced Chemicalsandmaterials intoahollowcircularmold(madeofpolytetrafluoroethylene)witha Copper(II)chloridedihydrate(CuCl ·2H O,99.99%,CAS:10125-13-0), diameterof1cm.Thefilledsamplewasthenfixedandvacuumedto 2 2 glucose(C H O ,99.5%,CAS:50-99-7),hexadecylamine(HAD,98%, prevent oxidation during the transfer and measurement processes. 6 12 6 CAS:143-27-1),hexane(98%,CAS:110-94-3)andsilvernitrate(AgNO , And the sample was secured on an XAS sample stage, which was 3 99.99%, CAS: 7761-88-8) were purchased from Aladdin.</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Isopropyl positioned at a 45° angle to the X-ray during the measurement, alcohol(C H O,99.9%,CAS:67-63-0),potassiumbicarbonate(KHCO , allowingforcollectionoffluorescencesignals. 3 8 3 99.95%,CAS:298-14-6),potassiumhydroxide(KOH,99.99%,CAS:131058-3),ethanol(CH CH OH,å99.9%,CAS:64-17-5),andformaldehyde Quasiin-situXPSmeasurements 3 2 (HCHO,20wt.%inH O,99atom%13C,CAS:3228-27-1)werepurchased Quasi in-situ X-ray photoelectron spectroscopy characterizations 2 from Sigma-Aldrich.</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2760,19 +4430,47 @@
           <t>S0062</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D63" t="n">
+        <v>8</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>This result sug2 3 ofCuwithadsorbed*OC H intermediate,i.e.,thestrengthofCu–O gested that the CA enriched in the Helmholtz plane, which was 2 3 (*OC H ) bond, and correspondingly changed the stability of C–O achievedbytheuniqueinsidetoon-surfacediffusionapproach,canbe 2 3 bondof*OC H intermediate.Accordingly,thisdeterminedthecleaconsistently maintained by the innovative asymmetric pulsed elec2 3 vageversuspreservationofC–Obond,resultinginthesynthesisof trolysisstrategy,furtherfacilitatedtheefficientandcontinuouselechydrocarbonversusoxygenatedproducts.TheinteractionofCuwith trosynthesisofvalue-addedC HOHproduct. 2 5 adsorbed *OC H intermediate and C–O internal bond strength of 2 3 *OC H onCu(100)andCu(100)-CAwereinvestigatedbythecrystal CO emissionandTEAofCO RRprocess 2 3 2 2 orbitalHamiltonpopulations(COHP).TheCOHPresultsandtheinteAfterverifyingthattheuniqueinsidetoon-surfacediffusionapproach grated overlap populations up to Fermi level (ICOHP) of C–O and canachieveanefficientandstableC HOHelectrosynthesis,wefurther 2 5 Cu–O bonds on Cu(100) and Cu(100)-CA were shown in Fig. 5e, f. validatedthepotentialofthisapproachforthescale-upproductionof According to the ICOHP theory, more negative ICOHP value repreC HOHinalarge-area(25cm2)membraneelectrodeassembly(MEA) 2 5 sentedstrongerbondstrength53,54.WithCA,thestrengthofC–Obond electrolyzer,whereahighFE andCO conversionrateof45.2% C2H5OH 2 wasstrong,whiletheCu–Ointeractionwasweak.Inbrief,theadsorand12%aswellasanenergyefficiency(EE)of16.6%wereachieved bedCAmoleculeweakenedtheinteractionbetweenCuandOatoms, underanindustrialcurrentof5A(SupplementaryFig.26,27).Also,we stabilizingtheC–Obondwithinthe*OC H andallowingOatomtobe investigatedCO emissionreductionandperformedTEAbasedonthe 2 3 2 retained,thuspromotingtheformationofoxygen-containingC HOH. tested electrochemical performance data to evaluate the environ2 5 TheelectroreductionpathwayfromCO toC HOHandcorrespondmental impact and economicfeasibility of this industrialCO RR-to2 2 5 2 ingchangeinselectivitybyCAmoleculewereshowninFig.5g.Further, C HOH conversion55–58.</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
         <is>
           <t>Here, distillation was employed for the 2 5 theΔGofeachstepfrom*OC H toC H andC HOHonCu(100)and separationofC HOHproducedbyCO RR,whichwasduetothefact 2 3 2 4 2 5 2 5 2 Cu(100)-CA were calculated and shown in Fig. 5h, i, corresponding thatthedistillationwascommonlycommercialwayofseparationand modelstructureofreactionintermediateswerealsoshowninFig.5j purification for alcohols.</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Calculations suggested that one ton (t) of andSupplementaryFig.21–23.TheΔGofC H formation(−0.43eV)on C HOHproducedbyCO electrolysisusingrenewablewindenergyas 2 4 2 5 2 bareCu(100)waslowerthantheformationof*OC H (0.14eV),verthedrivingforceemitted1.2tofCO accordingly,whichsubstantially 2 4 2 ifyingthecleavageofC–ObondwasmorefavorablethanCu–Obond, lower than that of conventional coal-to-CHOH and biomass-to2 5 resultingintheformationofC H insteadofC HOH.Onthesurfaceof C HOHapproacheswithemissionvaluesof7.6and3.9t /t , 2 4 2 5 2 5 CO2 C2H5OH Cu(100)-CA, the ΔG of C H formation exhibited major uphill to respectively(Fig.6g,SupplementaryNote1,SupplementaryTable2)59. 2 4 −0.24eV, whereas the ΔG of *OC H formation was downhill to Additionally, under current TEA analysis, the system of CO 2 4 2 NatureCommunications|( 2025)1 6:8390 8</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2794,19 +4492,47 @@
           <t>S0063</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D64" t="n">
+        <v>2</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>And how does such a step correlate with potential and enabled through formation of a surface–O bond.</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
         <is>
           <t>Of the three pH?—iscrucialforprovidinginsightattheatomic-levelandbroaden branchingintermediatesOCHCH*isthemoststableandCHCOH* our understanding when addressing the trends of C Oxy/HC the least (Supplementary Fig. 5a).</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Despite the poorer thermo2 selectivity. dynamicstabilityofCHCOH*,itsformationexhibitsthelowestΔG a In this work, we investigate the reaction mechanism of COR of 0.65eV at U =0V; whereas the other two steps have to RHE towards major C Oxy/HC products (e.g. ethylene, ethanol, and overcomeafreeenergybarrieratleast0.21eVhigher.Nevertheless, 2 aceticacid)fromreactionandactivationenergiescalculatedusing these differences in ΔG become smaller as the overpotential a density functional theory (DFT).</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2828,19 +4554,47 @@
           <t>S0064</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D65" t="n">
+        <v>4</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>As shownin Fig. 3I, both coordinationnumberthanthatofCu /Cu O(SupplementaryFig.14 Cu OandCu /Cu OhavetheKvaluescenteredaround6.3Å−1,while P 2 2 L 2 and Supplementary Table 4), indicating the preferred nucleophilic thevaluefromCu /Cu Oislocatedat7.1,closerto7.9Å−1observed L 2 addition reaction process on Cu /Cu O.</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
         <is>
           <t>Due to the difference in fromtheCufoil.Theseanalysesconfirmthatthelow-coordinatedCu / L 2 L electrondensity,theCu+regionbecomesnucleophilic,whiletheCu0 Cu O possesses an electron-rich region and abundant defect sites, 2 regionprefersanelectrophilicadditionreactionprocess(Fig.2I).In whichreceivenucleophilicadditionreactionofC–CorC –Ccoupling 2 conclusion, the faster electron exchange at enhanced rectifying in the mixed-valence boundary region to generate ethanol and interfaceregions,resultingfromtheasymmetricelectronaggregation, n-propanol. willboostthenucleophilicorelectrophilicadditionreactionprocess for C–C or C –C coupling.</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Generally, the enhanced adsorption of PerformanceofCERintheflowcell 2 negativelycharged*COmayfocusontheelectrophilicCusites,while ThecathodicelectrochemicalexperimentsofCO reductionreaction 2 theC endof*C H O,withahighpositivecharge,prefersbondingwith were implemented in flow cells using 1M KOH as electrolyte under 2 2 2 nucleophilicCu O. ambientconditions(SupplementaryFig.19).Allworkingpotentialsare 2 Toanalyzetheoriginsofenhancedrectifyinginterfaces,electro convertedintothereversiblehydrogenelectrode(RHE)scalewithiR paramagnetic resonance (EPR), XPS, and X-ray absorption spectrocorrectionof85%.Thelinearsweepvoltammetry(LSV)curvesinFig.4A scopywereutilizedtocharacterizetherefinedstructureofCu /Cu O. show that the Cu /Cu O catalyst provides higher conductivity and L 2 L 2 AsshowninFig.3A,theO1sXPSspectrumisdeconvolutedintofour activity for CER, with a total current density (j ) of −200 at the total peakssituatedat529.7,530.3,530.8,and531.7eV,correspondingto appliedpotentialof−0.66V.ThesplendidkineticpropertyofCu/Cu O L 2 the lattice oxygen (Cu–O), oxygen vacancies (Vo), C–O bond and revealsasmallercharge-transferresistanceandhighercatalyticactivity adsorbedoxygenonCu /Cu Osamples,respectively38.TheratioofVo/ (tafelslopeof232mVdec−1andelectrochemicallyactivesurfaceareaof L 2 Cu–O demonstrates a descendant trend with Ar+ etching, implying 6.1mFcm−2)forCER(SupplementaryFigs.20and21).Remarkably,Cu / L surfaceandsubsurfaceoxygendeficiencyintheoxide-derivedCu.The Cu O shows excellent selectivity of C alcohols with a maximum 2 2+ shiftofbondingenergyofCu–Otowardahigherlevelalsoindicates faradicefficiency(FE)of64.15±1.92%(ethanolof~56%andn-propanol thedisappearanceofVowithinthedepthofCu /Cu O.Acharacteristic of ~8%), whereas Cu /CuO only reaches a maximum FE and L 2 P 2 ethylene sign of Vo is observed at g=2.004 (Fig. 3B)39, which supports the FE of ~38.4% and 11.4%, respectively (Fig. 4B, C and alcohols NatureCommunications|( 2024)1 5:5172 4</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2862,19 +4616,47 @@
           <t>S0065</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D66" t="n">
+        <v>3</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Article https://doi.org/10.1038/s41560-024-01633-4 500 1,000 1,500 2,000 2,500 3,000 range of 1,000–2,000 cm−1 (Supplementary Figs. 10 and 11).</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
         <is>
           <t>We note The observation of these peaks agrees well with a CO-coveragehere that irrespective of the electrolyte anionic species, carbonate determined C–C coupling during CORR13 and indicates a similar inter2 and bicarbonate ions will be present due to the CO/HO equilibrium. mediate for C–C coupling during CORR and CORR.</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Concurrently, 2 2 2 Although a lower Faradaic efficiency of C products is obtained during the Raman peaks of *HCOO−/*HCOOH disappear, which suggests that 2+ CORR in CO-saturated 0.1 M NaClO (ref. 28), the onset potentials and CO or C–C coupling intermediates may affect the production of 2 2 4 potential-dependent trends for ethylene and ethanol formation are formic acid due to competition for surface sites. similar to those in 0.1 M KHCO (Supplementary Fig. 12).</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2896,27 +4678,55 @@
           <t>S0066</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D67" t="n">
+        <v>4</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Alternatively, such frequencies can be As ethanol and acetaldehyde are the main C products for gly2 assigned to an OCCO− dimer adsorbed on surface oxygen (O), known oxal reduction on polycrystalline copper and are proposed to share s as deprotonated glyoxylate OCOCO2− (ref. 36), which also shows the the same *OCHCH intermediate16–18, we performed in situ Raman s 2 1,070 cm−1 band detected at −0.76 V (Supplementary Table 6). experiments of glyoxal and ethanol reduction (Supplementary Figs. 20 RHE Among other additional possible intermediates (*OCCHO, *OHCand 21).</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
         <is>
           <t>As shown in Fig. 4c, similar bands at about 1,290 cm−1, 1,420 cm−1 COH, *OCCHOH, *CHO and *CH; Supplementary Tables 7–11), we attriband 1,605 cm−1 are observed during glyoxal reduction.</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>We attribute ute the 1,182 cm−1, 1,318 cm−1, 1,453 cm−1 and 1,595 cm−1 signals detected the variations in relative intensities and positions to the substantially at −0.85 V and below to the CCO symmetric stretching, CCO antisymdifferent chemical environment in the absence of predominantly RHE metric stretching, C–C stretching and C–O (or C=C) stretching of co-adsorbed CO, as is the case in CORR.</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t>P2:*CHO</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2938,19 +4748,47 @@
           <t>S0067</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D68" t="n">
+        <v>3</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>We elucidate the role of subsurface doping in enhancing the oxophilicity of surface Cu sites, thereby facilitating the conversion of key intermediates (*CHCHO*) via the formation of surface-O bonds, Sguiding subsequent protonation S towards ethanol.</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
         <is>
           <t>Moreover, the surface sulfur vacancies cEreated by subsurface Co-doping help R regulate the optimal distance between dual sites, faciliPtating asymmetric C-C coupling.</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Theoretical N calculations combined with in-situ isotopic spectroscopy validate these views, and the branching I pathway for converting *CHCO to *CHC E HO* is captured.</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2972,19 +4810,47 @@
           <t>S0068</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D69" t="n">
+        <v>2</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Despite the poorer thermo2 selectivity. dynamicstabilityofCHCOH*,itsformationexhibitsthelowestΔG a In this work, we investigate the reaction mechanism of COR of 0.65eV at U =0V; whereas the other two steps have to RHE towards major C Oxy/HC products (e.g. ethylene, ethanol, and overcomeafreeenergybarrieratleast0.21eVhigher.Nevertheless, 2 aceticacid)fromreactionandactivationenergiescalculatedusing these differences in ΔG become smaller as the overpotential a density functional theory (DFT).</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
         <is>
           <t>Pathways trifurcating from a increases,duetothesmallercharge-transfercoefficient(β~0.35)for common intermediate, CHCO*, are shown to be responsible for CHCO-H than for CHC-HO (β ~0.45) and OCCH-H (β ~0.5) generating specific C Oxy/HC products.</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>We observe that it is (SupplementaryFig.5b).Oncethethreespeciesaregeneratedonthe 2 kineticallyunfeasibletoformethylenethroughtheOCHCH*and surface, the subsequent reaction steps are shown to be facile at CH CO* pathway.</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3006,19 +4872,47 @@
           <t>S0069</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>However, the production efficiency for ethanol (EtOH), a significant chemical feedstock, is impractically low because of limited selectivity, especially under high current operation.Herewereportanewsilver–modifiedcopper–oxidecatalyst(dCu O/Ag )that 2 2.3% exhibitsasignificantFaradaicefficiencyof40.8%andenergyefficiencyof22.3%forboosted EtOH production.</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
         <is>
           <t>Importantly, it achieves CO –to–ethanol conversion under high current 2 operation with partial current density of 326.4mAcm−2 at −0.87V vs reversible hydrogen electrodeto rankhighlysignificantlyamongstreported Cu–basedcatalysts.</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Basedon in situ spectra studies we show that significantly boosted production results from tailored introduction of Ag to optimize the coordinated number and oxide state of surface Cu sites, in which the *CO adsorption is steered as both atop and bridge configuration to trigger asymmetric C–C coupling for stablization of EtOH intermediates. 1SchoolofChemicalEngineeringandAdvancedMaterials,TheUniversityofAdelaide,Adelaide,SA5005,Australia.2StateKeyLaboratoryofPhysical ChemistryofSolidSurfaces,CollegeofChemistryandChemicalEngineering,XiamenUniversity,Xiamen361005,China.3InstituteofFunctionalNano&amp;Soft Materials(FUNSOM),JiangsuKeyLaboratoryforCarbon-BasedFunctionalMaterials&amp;Devices,JointInternationalResearchLaboratoryofCarbon-Based FunctionalMaterialsandDevices,SoochowUniversity,Suzhou215123,China.4Theseauthorscontributedequally:PengtangWang,HaoYang. ✉ email:hxq006@xmu.edu.cn;s.qiao@adelaide.edu.au NATURECOMMUNICATIONS| (2022) 13:3754 |https://doi.org/10.1038/s41467-022-31427-9|www.nature.com/naturecommunications 1 ;,:)(0987654321</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3040,27 +4934,55 @@
           <t>S0070</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D71" t="n">
+        <v>7</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>To elucidate the mechanism of ethanol formation through the CO RR, isotopically-labeled reactants 2 (12CO , 13CO , H12COOH and H13COOH) were used to trace the pathway of the C atoms in the nal C2 2 2 product formed on the Sn -O3G catalyst.</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
         <is>
           <t>Figure 3e and Extended data Fig. 48 show that the methyl C 1 (*CH ) in ethanol comes from HCOOH, while the C in CO goes to the methylene C (*CH OH).</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Therefore, 3 2 2 Fig. 3f schematically summarizes the CO RR process to form ethanol taking place on the SnS /Sn -O3G. 2 2 1 The comprehensive discussion for the ethanol formation process on the SnS /Sn -O3G tandem catalyst 2 1 is provided from additional structural characterization and kinetics simulation (Extended data Figs. 49– 53 and Tables 9–17), indicating that diffusion of HCOOH generated from the SnS component to the 2 single atomic Sn sites on Sn -O3G is the rate-determining step for ethanol formation. 1 Based on the above experimental results, we built the active site model of the catalyst.</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t>P5:HCOO</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3082,19 +5004,47 @@
           <t>S0071</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D72" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Recently, a methyl carbonyl 2 as the building block of multi-carbon products5,9,10 via dimerization intermediate, *OCCH, has been proposed as an alternative intermedi3 (OC–CO)7 or coupling (OC–CHO or OC–COH)8 steps.</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
         <is>
           <t>Experimentally, ate for ethanol and propanol19,20.</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>In general, the reaction pathways for *CO has been detected on Cu surfaces using in situ Raman and infrared ethylene and ethanol formation are defined by logical intuition based spectroscopy during CORR6,11,12, and a direct correlation between CO on experimental and computational results7,8,16,21.</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3116,19 +5066,47 @@
           <t>S0072</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D73" t="n">
+        <v>3</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Concurrently, 2 2 2 Although a lower Faradaic efficiency of C products is obtained during the Raman peaks of *HCOO−/*HCOOH disappear, which suggests that 2+ CORR in CO-saturated 0.1 M NaClO (ref. 28), the onset potentials and CO or C–C coupling intermediates may affect the production of 2 2 4 potential-dependent trends for ethylene and ethanol formation are formic acid due to competition for surface sites. similar to those in 0.1 M KHCO (Supplementary Fig. 12).</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
         <is>
           <t>At more cathodic potentials, CO coverage further increases, and 3 Initially, at open-circuit potential, Raman peaks at 400 cm−1, four new peaks can be detected at 1,182 cm−1, 1,318 cm−1, 1,453 cm−1 and 528 cm−1 and 620 cm−1 from a CuO phase are detected12,29.</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>At a poten1,595 cm−1 from −0.85 V , which show a regular shift with the potential, x RHE tial of −0.36 V , the CuO is reduced to metallic Cu on the surface, and indicating the existence of new adsorbates.</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3150,27 +5128,55 @@
           <t>S0073</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D74" t="n">
+        <v>4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Our data show similar bands (Supplementary Fig. 18). 3 species form (see 1,070 cm−1, 1,390 cm−1 and 1,610 cm−1 signals in Fig. 3; We further prove the appearance of C–C coupling intermediates by Supplementary Tables 1–3).</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
         <is>
           <t>Consistent with previous reports14,15, the observing analogous signals on a different Cu foil with distinct surface signals appearing at 1,450 cm−1 and 1,550 cm−1 from −0.76 V can be morphology, yet with still good performance towards C products RHE 2+ attributed to *OCCO(H), with the C=O vibration mode (Fig. 3 and Sup- (Supplementary Fig. 19). plementary Tables 4 and 5).</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Alternatively, such frequencies can be As ethanol and acetaldehyde are the main C products for gly2 assigned to an OCCO− dimer adsorbed on surface oxygen (O), known oxal reduction on polycrystalline copper and are proposed to share s as deprotonated glyoxylate OCOCO2− (ref. 36), which also shows the the same *OCHCH intermediate16–18, we performed in situ Raman s 2 1,070 cm−1 band detected at −0.76 V (Supplementary Table 6). experiments of glyoxal and ethanol reduction (Supplementary Figs. 20 RHE Among other additional possible intermediates (*OCCHO, *OHCand 21).</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t>P1:*OCCO; P1:OCCO</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3192,27 +5198,55 @@
           <t>S0074</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D75" t="n">
+        <v>4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Thus, we In addition, we carried out 13Cor D-labelling SERS experiments reasonably confirmed the detection of a common intermediate along at −0.95 V (Fig. 4a). 13C/12C exchange led to obvious redshifts of the CO, CO and glyoxal reduction route to ethanol, which is *OCHCH.</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
         <is>
           <t>RHE 2 2 the 1,455 cm−1 and 1,602 cm−1 peaks, in addition to the CO stretching Overall, the presence of CO molecules on the Cu surface during CORR 2 (2,100 cm−1), Cu–CO stretching (358 cm−1) and CO rotation (275 cm−1) is linked to and probably causes the formation of *CO–CO or *CO–COH bands, proving that these peaks are related to the CORR process.</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Such at about −0.76 V , and then these species further reduce to, for exam2 RHE redshifts were also confirmed by DFT vibrational analysis of O12CH12CH ple, *OCHCH at −0.85 V and −0.95 V . 2 2 RHE RHE and O13CH13CH (Fig. 4b and Supplementary Table 12).</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t>P3:CO-COH; P3:CO–COH</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3234,19 +5268,47 @@
           <t>S0075</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D76" t="n">
+        <v>5</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Four Gaussian peak functions hint at the key role of structural defects in tuning the ethylene/ethanol centred at about 2,035 cm−1, 2,075 cm−1, 2,090 cm−1 and 2,100 cm−1 ratio.</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
         <is>
           <t>These defects are probably formed under reaction conditions and were used to fit the recorded potential-dependent Raman spectra. generate distinct surface sites with strong CO binding.</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>C–O stretching bands with intermediate frequencies (2,075 cm−1 and On the basis of these mechanistic insights, we aimed to correlate 2,090 cm−1) become the main contribution at −0.76 V , from which specific active sites and reaction intermediates with ethylene and RHE the *OCCO intermediate is identified and ethylene is produced, in line ethanol production during CORR.</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3268,19 +5330,47 @@
           <t>S0076</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D77" t="n">
+        <v>7</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Data are given as average ± s.d. ~1,450 cm–1 ~1,550 cm–1 – +H+ +H+ + e– +H+ + e– +5H+ + 5e– –H 2 O +H –H 2 O Ethylene SDS1 *COCO– *COCOH *CCO *CHCO + + e– Allyl alcohol Propionaldehyde or Acetaldehyd +2 e H+ + 2e– 1-Propanol +H+ + e– +H+ + e– *CH 2 CO Solution – Glyoxal Acetate Ethanol *OCHCH 3 +H+ + e– SDS2 *OCHCH 2 glycolaldehyde 1,182 cm–1 1,318 cm–1 1,453 cm–1 1,595 cm–1 Fig. 7 | Proposed reaction scheme for CO reduction to C products.</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
         <is>
           <t>Proposed Reaction steps confirmed by experimental studies are reported as solid lines, 2 2+ reaction scheme, including ethylene and ethanol, was extracted from the present and proposed steps are labelled as dashed lines.</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Grey arrows indicate potential experimental Raman data, our DFT data and additional mechanistic insights CO–CH coupling routes.</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3302,19 +5392,47 @@
           <t>S0077</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D78" t="n">
+        <v>8</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>The diffraction pattern was 2 *OCHCH by strongly binding the terminal oxygen in a monodentate recorded through the grazing incidence mode with an incidence angle 2 configuration.</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
         <is>
           <t>*OCHCH (ref. 7; characterized by a double C–C bond, of 1° to decrease the bulk contribution of the Cu foil. 2 see Supplementary Table 18) can either reduce to acetaldehyde and The size and morphology of the samples were determined by SEM ethanol or couple with a CO/COH species to form allyl alcohol and, with a ThermoFisher Apreo microscope and a Hitachi S-4800 system, at later reduction stages, 1-propanol51 (see the correlation between including a cold field emission gun.</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Faradaic efficiency for both products in Supplementary Fig. 26 and XPS measurements were performed with a commercial hemispherSupplementary Table 19). ical analyser (Phoibos 150, MCD-9 Detector, SPECS, E = 15 eV) and a pass Thus, although a methyl carbonyl intermediate (OCCH) was monochromatic X-ray source (SPECS) with an Al anode (E = 1,486.7 eV 3 Kα recently suggested as the ethanol precursor during CHI and acetaldeas X-ray energy) at a power of P = 300 W.</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3336,19 +5454,47 @@
           <t>S0078</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D79" t="n">
+        <v>4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Previous work proved that ethylene and ethanol are not genThe specific geometry of step-square site explains the differeratedfromthesametypesofactivesites,whichmeanstheC–C enceinselectivity.Figure3eshowsthatthegeneralcoordination couplingactivesitescanbefurthersubdivided16.Fromcalculated number (GCN) of s-sq is the lowest (5.50), thus showing the free energy profiles of the whole reaction pathway (Supplemenstrongest adsorption energy of acetaldehyde intermediate taryFigs.24–26),*CH CHOservesastheselectivitydetermining (*CH CHO),leadingtothehydrogenationpathwaydominances. 2 3 intermediate (SDI), which corresponds to previous calculations Meanwhile, p-sq and cv-sq can supply the fourfold sites to staon copper single crystal facets27,28.</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
         <is>
           <t>The ethylene pathway probilize the newly formed *O after C–O cleavage.</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>While on s-sq ceeds with cleavage of C–O bond while alcohols are formed by site, *O can only adsorb in adjacent triple site, resulting in the further protonation.</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3370,19 +5516,47 @@
           <t>S0079</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D80" t="n">
+        <v>6</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Figure 4 depicts the DSCs for ethylene, ethanol, and accurately predicts such an inverse Volcano-like characteristic. aceticacidasafunctionofpotentialandpH.AtpH7,Cu(100)is The observed discrepancy in absolute magnitudes could be foundtobeextremelyselectivetowardsethylene,andtheethylene attributedtotheabsenceofundercoordinatedsitesonCu(100)in productionisinsensitivetoanyoftheenergystatesinarangeof oursimulation,whereasundercoordinatedsitespresentindefectU from approximately −0.4V to −0.8V; only when U RHE RHE or grain-boundary-rich pcCu or OD-Cu have been suggested as decreases further, the difference between CHCO-HTS and C Oxy-specific active sites in previous studies6,13,33.</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
         <is>
           <t>We will OCCH-HTS becomes smaller and the CH CO pathway starts to 2 2 unravel the atomistic origin of C Oxy-specific activity on these compete with the CHCOH pathway (Fig. 4a).</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>The formation of 2 sites in the last section.</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3404,19 +5578,43 @@
           <t>S0080</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D81" t="n">
+        <v>4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Due to the difference in fromtheCufoil.Theseanalysesconfirmthatthelow-coordinatedCu / L 2 L electrondensity,theCu+regionbecomesnucleophilic,whiletheCu0 Cu O possesses an electron-rich region and abundant defect sites, 2 regionprefersanelectrophilicadditionreactionprocess(Fig.2I).In whichreceivenucleophilicadditionreactionofC–CorC –Ccoupling 2 conclusion, the faster electron exchange at enhanced rectifying in the mixed-valence boundary region to generate ethanol and interfaceregions,resultingfromtheasymmetricelectronaggregation, n-propanol. willboostthenucleophilicorelectrophilicadditionreactionprocess for C–C or C –C coupling.</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
         <is>
           <t>Generally, the enhanced adsorption of PerformanceofCERintheflowcell 2 negativelycharged*COmayfocusontheelectrophilicCusites,while ThecathodicelectrochemicalexperimentsofCO reductionreaction 2 theC endof*C H O,withahighpositivecharge,prefersbondingwith were implemented in flow cells using 1M KOH as electrolyte under 2 2 2 nucleophilicCu O. ambientconditions(SupplementaryFig.19).Allworkingpotentialsare 2 Toanalyzetheoriginsofenhancedrectifyinginterfaces,electro convertedintothereversiblehydrogenelectrode(RHE)scalewithiR paramagnetic resonance (EPR), XPS, and X-ray absorption spectrocorrectionof85%.Thelinearsweepvoltammetry(LSV)curvesinFig.4A scopywereutilizedtocharacterizetherefinedstructureofCu /Cu O. show that the Cu /Cu O catalyst provides higher conductivity and L 2 L 2 AsshowninFig.3A,theO1sXPSspectrumisdeconvolutedintofour activity for CER, with a total current density (j ) of −200 at the total peakssituatedat529.7,530.3,530.8,and531.7eV,correspondingto appliedpotentialof−0.66V.ThesplendidkineticpropertyofCu/Cu O L 2 the lattice oxygen (Cu–O), oxygen vacancies (Vo), C–O bond and revealsasmallercharge-transferresistanceandhighercatalyticactivity adsorbedoxygenonCu /Cu Osamples,respectively38.TheratioofVo/ (tafelslopeof232mVdec−1andelectrochemicallyactivesurfaceareaof L 2 Cu–O demonstrates a descendant trend with Ar+ etching, implying 6.1mFcm−2)forCER(SupplementaryFigs.20and21).Remarkably,Cu / L surfaceandsubsurfaceoxygendeficiencyintheoxide-derivedCu.The Cu O shows excellent selectivity of C alcohols with a maximum 2 2+ shiftofbondingenergyofCu–Otowardahigherlevelalsoindicates faradicefficiency(FE)of64.15±1.92%(ethanolof~56%andn-propanol thedisappearanceofVowithinthedepthofCu /Cu O.Acharacteristic of ~8%), whereas Cu /CuO only reaches a maximum FE and L 2 P 2 ethylene sign of Vo is observed at g=2.004 (Fig. 3B)39, which supports the FE of ~38.4% and 11.4%, respectively (Fig. 4B, C and alcohols NatureCommunications|( 2024)1 5:5172 4</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3438,19 +5636,47 @@
           <t>S0081</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D82" t="n">
+        <v>5</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>C–O stretching bands with intermediate frequencies (2,075 cm−1 and On the basis of these mechanistic insights, we aimed to correlate 2,090 cm−1) become the main contribution at −0.76 V , from which specific active sites and reaction intermediates with ethylene and RHE the *OCCO intermediate is identified and ethylene is produced, in line ethanol production during CORR.</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
         <is>
           <t>Recent experimental studies have 2 with the observation of a 2,060 cm−1 CO precursor reacting towards highlighted the relevance of defects and polarized Cu sites in enabling C–C coupling as reported in a previous SERS study6.</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>At −0.95 V , the CORR25,26,45,46, while flat atomically ordered surfaces mainly yield H RHE 2 2 C–O stretching bands at 2,090 cm−1 and 2,100 cm−1, assigned to atop (ref. 24).</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3472,27 +5698,55 @@
           <t>S0082</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D83" t="n">
+        <v>8</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>This is achieved betweentheCuclusterandadjacentsingleCucenteraffordsanextra 2 through the significantly enhanced *CO adsorption on the underO–Cu bond to stabilize the *OCCOH intermediate by breaking the coordinated sites.</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
         <is>
           <t>We adopted the selectivity determining method linearscalingrelationwith*CO.Next,CO RRproceedspreferentially 2 proposedbyRossmeisletal45todecidetheproductselectivityonRtowardC HOHformationthroughtheexergonicprotonationonCto 2 5 Hex-2Cu-O/G.TheresultsinFig.5bshowthatallactivesitesfromtheRfrom*OCHCOH,whereastheprotonationonOtoform*HOCCOHis Hex-2Cu-O/G surface (Supplementary Fig. 37) fell in the CO RR disfavoredowingtotheextraenergyneededtocleavetheO–Cubond. 2 dominantzone.Thecalculatedselectivityonthetwomodelsisingood Lastly,theelectrochemicalCO RRofHex-2Cu-Owasfurthertestedina 2 agreementwiththeexperimentalobservationofstableC andalcohol flow-cell using the aqueous 1M KOH electrolyte.</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Similar trend of 2+ productionwithsuppressedH yieldonHex-2Cu-O(Fig.2a). ethanol, propanol, and ethylene was observed with a noticeable 2 After C–C coupling, the spatial-confinement effect can reserve amountofaceticacid(SupplementaryFig.41a).Atthecurrentdensity oxygeninthehydroxylgrouptoincreasealcoholselectivityandinhibit of250mAcm−2,thetotalFEofoxygenates(includingethanol,propathe competing hydrocarbon production.</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="L83" t="inlineStr">
         <is>
           <t>P1:OCCO</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3514,19 +5768,47 @@
           <t>S0083</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="D84" t="n">
+        <v>3</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Unfortunately, the formation of C-C bonds on Cu is very complicated and the pathway remains elusive 16, which have greatly limited the development of highly selective electrocatalyst to reduce CO to C (n ≥ 2) liquid products. 2 n Herein, we report a Sn-based tandem catalyst consisting of SnS nanosheets that are able to produce 2 formate intermediates and single Sn atoms anchored on a 3D carbon support via a local SnO3 cluster (Sn -O3G) that generate *OCO(OH) bicarbonate intermediates, followed by C-C coupling to 1 electrochemically reduce CO to ethanol.</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
         <is>
           <t>Based on this strategy, an ethanol selectivity of more than 70% 2 was achieved over a wide potential range from − 0.6 to -1.1 V versus the reversible hydrogen electrode (RHE).</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>This catalyst was found to maintain 97% of its initial activity after 100 hours of continuous reaction at a geometric current density as high as 17.8 mA·cm− 2.</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3548,19 +5830,47 @@
           <t>S0084</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D85" t="n">
+        <v>6</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Interestingly, a 2 2 mechanically-mixed combination of SnS nanosheets and Sn -O3G was found to produce ethanol with 2 1 an FE of approximately 15% at -0.9 V (vs.</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
         <is>
           <t>RHE) (Fig. 3c), while a mixture of SnS nanosheets with 3D 2 carbon (without the single Sn atoms, Extended data Fig. 44) failed to produce ethanol.</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>From these ndings, we propose that the formation of ethanol over the SnS /Sn -O3G may result from C-C coupling 2 1 between the two intermediates associated with formate and CO.</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3582,27 +5892,55 @@
           <t>S0085</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D86" t="n">
+        <v>6</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>From these ndings, we propose that the formation of ethanol over the SnS /Sn -O3G may result from C-C coupling 2 1 between the two intermediates associated with formate and CO.</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
         <is>
           <t>To verify our hypothesis, we intentionally introduced a small amount of HCOOH into the reaction system (in a Na SO electrolyte instead of KHCO ) during the CO RR over the Sn -O3G.</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>As shown in Fig. 3d, 2 4 3 2 1 compared to the case without HCOOH (Fig. 3b), the cathodic current exhibits a clear decrease in the N - 2 saturated Na SO electrolyte upon HCOOH addition (Extended data Fig. 45).</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="L86" t="inlineStr">
         <is>
           <t>P5:HCOO</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3624,19 +5962,47 @@
           <t>S0086</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D87" t="n">
+        <v>6</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>RHE), adding HCOOH (50 µL) to the CO -saturated electrolyte decreased the FE 2 CO (inset in Fig. 3b) from 50% to approximately 40%, while increasing FE nearly 40-fold, from close to ethanol 0.2–7.4%.</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
         <is>
           <t>The partial geometric current density associated with ethanol formation also increased, from 0.002 to 0.9 mA/cm2.</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>These results demonstrate the importance of HCOOH in C-C coupling to form ethanol on O atoms coordinated Sn catalytic sites.</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3658,19 +6024,47 @@
           <t>S0087</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D88" t="n">
+        <v>4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Thus, the coverage of key electrolyteswascompared(Fig.4a,b).TheHERperformanceshould intermediate*COcanbeimprovedbydirectlyusingCOasreactant. notbeaffectedbytheexternalgasdiffusionbutisdeterminedbyH O 2 WhentheCucatalysthasasimilarcontactangle,thepromotionof availability and transport26.</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
         <is>
           <t>Therefore, stronger hydrophilicity can ethanol production is more obvious than that of ethylene during benefittheHERduetomoreefficientH Otransport. 2 CORR.</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>In comparison, a similar phenomenon can be observed on Unfortunately,thepeakof*HonCucannotbeobservedbyin-situ CuAg catalyst, which can generate more CO during performing Ramanspectra(SupplementaryFig.35)orin-situATR-SEIRASspectra CO RR(SupplementaryFig.32).Therefore,increasing*COcoverage (Fig. 3d, e) due to the extremely weak adsorption of *H on Cu.</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3692,19 +6086,47 @@
           <t>S0088</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D89" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>However, while CO coupling has been repeatedly consatility in the chemical and energy industries3, and processes involving firmed, observing and tracking potential-dependent CO dimerization C–C bond formation are of great relevance from the point of view of and intermediates during the subsequent gradual reduction process fundamental research2,4. towards final products has not yet been achieved.</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
         <is>
           <t>Copper-based materials are the most selective catalysts for elecAmong the CORR reaction intermediates7,8, *OCHCH is consid2 2 trochemically reducing CO to C products2.</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>A myriad of studies have ered the last common precursor in the ethylene and ethanol routes, 2 2+ focused on understanding the C–C coupling mechanism, and although although experimental confirmation is still missing2,7.</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3726,19 +6148,47 @@
           <t>S0089</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="D90" t="n">
+        <v>7</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>If formed, the CO–CO(H) 2 2+ Ethylene and ethanol formations are pH-independent on the RHE species is characterized by either a single or double C–C bond7 scale5.</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
         <is>
           <t>Thus, according to the state of the art2,7, CO–CO dimeriza- (Supplementary Table 18) and acts as a selectivity switch between tion, which involves a single electron transfer, is assumed to be the C and C products (C selectivity-determining step 1, SDS1). 1 2+ 2+ Nature Energy | Volume 9 | December 2024 | 1485–1496 1491 )Ve( E∆ HCHCO* 2 )Ve( E∆ O* pota a b –2.4 –2.7 0 1 2 3 4 5 6 0 1 2 3 4 5 6 ∑(∆d/d)N –1 (%) ∑(∆d/d)N –1 (%) Cu–Cu Cu–Cu c d 40 Ethylene 20 0 10 0 Ethanol Ethylene 20 Distorted domains Undercoordinated High strain sites Deep s sates 0 0 5 10 15 20 25 )%( ycneiciffe ciadaraF Ethanol Methane Faradaic efficiency of CO (%) Fig. 6 | Morphological descriptors for COR to C products. a,b, Correlation Faradaic efficiency versus CO Faradaic efficiency.</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Data retrieved from Fig. 1f. 2 2+ of *OCHCH (ΔE ) (a) and *O atop (ΔE ) binding energies (b) versus d, Key reaction intermediates and properties of the active sites selective 2 *OCHCH2 *Oatop Σ(Δd/d)N −1.</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3760,19 +6210,47 @@
           <t>S0090</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="D91" t="n">
+        <v>3</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>ARTICLE IN PRESS Abstract The challenge in precisely controlling the adsorption configuration of oxygen-binding intermediates in the branching path following C-C coupling constrains the directed selectivity of electroreduction CO -to-ethanol.</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
         <is>
           <t>Here, we present a subsurface Co-doped CuS (Co-Sub-CuS) 2 catalyst, which exhibits directed selectivity toward ethanol.</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>We elucidate the role of subsurface doping in enhancing the oxophilicity of surface Cu sites, thereby facilitating the conversion of key intermediates (*CHCHO*) via the formation of surface-O bonds, Sguiding subsequent protonation S towards ethanol.</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3794,19 +6272,47 @@
           <t>S0091</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D92" t="n">
+        <v>4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>The latter has also been recently 2+ products),andS11(geometricandmasscurrentdensities). observed for AgCu foam catalysts as compared to pure Cu Theproductionofethanolat@1.0V increasessignififoams.[14] In contrast, the formation of acetaldehyde (FigRHE cantlywiththeamountofAg.CuONCs,3-,and5-Ag/CuO ureS9a) and propionaldehyde (FigureS9b) is significantly 2 2 reach 10%, 13%, and 17% FE for ethanol at @1.0V , increasedfor5-Ag/CuO,whichresultsinanenhancementof RHE 2 respectively (Figures4a, S7a).</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
         <is>
           <t>Thus, FE increased thecarbonylC productsbyafactorofthree(Figure4f,S7f). ethanol 2+ 1.5times by the addition of 5at% of Ag to CuONCs.</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Overall, introducing Ag increases the FE of the desired C 2 2+ Additionally,theproductionof1-propanolisdoubledinthe liquid products (Figure4e, S7e) for 5-Ag/CuO by 15% in 2 Ag/CuOsampleswithFEof5–6%at@0.9V compared comparisontoCuONCsat@1.0V .Thisisassignedtothe 2 RHE 2 RHE to3%fortheCuONCs(Figure4b).Thisincreaseinalcohol enhanced production of ethanol, 1-propanol, allyl alcohol, 2 yieldhasbeenpreviouslylinkedtoCOspilloverfromAgto andcarbonylC products(Figure4a,b,f,S9c).Weaddition2+ Cu, since the weaker binding between Ag and the *CO ally performed long-term CORR measurements for 12h at 2 intermediate is considered to facilitate CO production as @1.0V totrackthestabilityofthecatalyticperformance RHE compared to the moderate binding energy between Cu and (FigureS12) and found a good stability for all catalysts.</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3828,19 +6334,47 @@
           <t>S0092</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="D93" t="n">
+        <v>4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Overall, introducing Ag increases the FE of the desired C 2 2+ Additionally,theproductionof1-propanolisdoubledinthe liquid products (Figure4e, S7e) for 5-Ag/CuO by 15% in 2 Ag/CuOsampleswithFEof5–6%at@0.9V compared comparisontoCuONCsat@1.0V .Thisisassignedtothe 2 RHE 2 RHE to3%fortheCuONCs(Figure4b).Thisincreaseinalcohol enhanced production of ethanol, 1-propanol, allyl alcohol, 2 yieldhasbeenpreviouslylinkedtoCOspilloverfromAgto andcarbonylC products(Figure4a,b,f,S9c).Weaddition2+ Cu, since the weaker binding between Ag and the *CO ally performed long-term CORR measurements for 12h at 2 intermediate is considered to facilitate CO production as @1.0V totrackthestabilityofthecatalyticperformance RHE compared to the moderate binding energy between Cu and (FigureS12) and found a good stability for all catalysts.</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
         <is>
           <t>For the *CO intermediate leading to the formation of hydrothe Ag/CuO samples, the amount of C liquid products 2 2+ carbons.[4,10] Also in our case, the Ag/CuO samples show remainsstableovertimewithadecreaseofthealdehydesand 2 higherFEsforCOatlowoverpotentials,withalmost40%FE Angew.Chem.Int.Ed.2021,60,7426–7435 T2021TheAuthors.AngewandteChemieInternationalEditionpublishedbyWiley-VCHGmbH www.angewandte.org 7429 15213773, 2021, 13, Downloaded from https://onlinelibrary.wiley.com/doi/10.1002/anie.202017070 by CochraneAustria, Wiley Online Library on [23/05/2026].</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>See the Terms and Conditions (https://onlinelibrary.wiley.com/terms-and-conditions) on Wiley Online Library for rules of use; OA articles are governed by the applicable Creative Commons License</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3862,19 +6396,47 @@
           <t>S0093</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="D94" t="n">
+        <v>5</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>0.5 0.4 0.3 0.2 0.1 0 0 0.1 0.2 0.3 0.4 0.5 square-like sites are responsible for C–C coupling, low coordiThe ratio of three theoretically identified active sites, p-sq, s-sq, nated sites are conducive to further protonation for alcohols. andcv-sqsites,decreasedwithincreasingannealingtemperatureas Very recent study35 found that square, four-atom Cu islands are well.</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
         <is>
           <t>From our theoretical models, the OD-Cu surface before the active sites for generating ethanol.</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>This structure certainly annealing has the largest proportion, 11.54%, of these three active meets our design criteria for alcohols production.</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3896,19 +6458,47 @@
           <t>S0094</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="D95" t="n">
+        <v>8</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Similar trend of 2+ productionwithsuppressedH yieldonHex-2Cu-O(Fig.2a). ethanol, propanol, and ethylene was observed with a noticeable 2 After C–C coupling, the spatial-confinement effect can reserve amountofaceticacid(SupplementaryFig.41a).Atthecurrentdensity oxygeninthehydroxylgrouptoincreasealcoholselectivityandinhibit of250mAcm−2,thetotalFEofoxygenates(includingethanol,propathe competing hydrocarbon production.</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
         <is>
           <t>We acquired the complete nol,andaceticacid)sumsupto38.6%andthatofC productsreaches 2+ reactionpathwaystowardthemainproductsobservedinexperiments, 55.4%.</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Chronoamperometric i–t test at −0.66V (Supplementary NatureCommunications|( 2022)1 3:5122 8</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3930,19 +6520,47 @@
           <t>S0095</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="D96" t="n">
+        <v>6</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Our model Note 7).</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
         <is>
           <t>Figure 4 depicts the DSCs for ethylene, ethanol, and accurately predicts such an inverse Volcano-like characteristic. aceticacidasafunctionofpotentialandpH.AtpH7,Cu(100)is The observed discrepancy in absolute magnitudes could be foundtobeextremelyselectivetowardsethylene,andtheethylene attributedtotheabsenceofundercoordinatedsitesonCu(100)in productionisinsensitivetoanyoftheenergystatesinarangeof oursimulation,whereasundercoordinatedsitespresentindefectU from approximately −0.4V to −0.8V; only when U RHE RHE or grain-boundary-rich pcCu or OD-Cu have been suggested as decreases further, the difference between CHCO-HTS and C Oxy-specific active sites in previous studies6,13,33.</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>We will OCCH-HTS becomes smaller and the CH CO pathway starts to 2 2 unravel the atomistic origin of C Oxy-specific activity on these compete with the CHCOH pathway (Fig. 4a).</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3964,19 +6582,47 @@
           <t>S0096</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="D97" t="n">
+        <v>3</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>economic values compared to C1 products (CO, CH , and formate), and therefore provide a more 4 attractive direction to aim for4.</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
         <is>
           <t>Ethylene and ethanol are of great interest because they are economically and energetically valuable and are produced in substantial quantities globally (&gt; 30 MtC/yr)2.</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Literature has found that these two products share the same generation pathway after C-C coupling5,6, which is believed to be the rate-determining step (RDS) of C product formation7–9.</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3998,27 +6644,55 @@
           <t>S0097</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="D98" t="n">
+        <v>6</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Meanwhile, mass spectrometry (MS) spectra of liquid proobserved in the ATR-SEIRAS spectra at ~2332, ~1265, ~1183 and ducts from CO RR exhibit signals at m/z=45.03 and m/z=46.03, 2 ~1034cm−1aresummarizedinSupplementaryTable10.Comparedto which can be attributed to 12CH 12CH O+ and 13CH 12CH O+ or 3 2 3 2 AgCuNW,ablue-shiftin*CO peakonAgCuNWwasnoticedat 12CH 13CH O+,respectively(Fig.4i)61.Basedonalltheseresults,Fig.4g bridge 1 3 2 variousappliedpotentials,suggestingenhancedbindingstrengthof schematicallyproposesthepathwayofCO RRtoethanoloverAgCu 2 1 *CO on AgCu NW.</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
         <is>
           <t>Additional new peaks at around 1244cm−1 and NW, where methyl C (-CH ) and methylene C (-CH OH) in ethanol 1 3 2 1083cm−1 were observed on AgCu NW, which can be assigned to originatefrom*COand*HCHOintermediates,respectively. 1 adsorbed*CHOand*COCHOintermediates,respectively(Fig.4e)60.As showninFig.4f,thepeakintensityof*COCHOintermediatewasfound Theoreticalinsightsintothecatalyticmechanism tograduallyincreasewithincreasingappliedcathodicpotentialfrom Densityfunctionaltheory(DFT)calculationswereperformedtogain −0.4to−1.2VvsRHE,whilethepeakintensityof*CHOintermediate insightsintotheunderlyingreactionmechanismsforthedistinctive was correspondingly decreased, suggesting production of *COCHO selectivityofCO electroreductiontoethyleneandethanoloverAgCu 2 intermediatefromasymmetric*CO-*CHOcoupling.</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>NW and AgCu NW, respectively (Supplementary Figs 44, 45).</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
         <is>
           <t>P2;P5</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="L98" t="inlineStr">
         <is>
           <t>P2:*CO-*CHO; P2:*CHO; P2:CHO intermediate; P5:OCHO</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4040,19 +6714,43 @@
           <t>S0098</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="D99" t="n">
+        <v>7</v>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
         <is>
           <t>Article https://doi.org/10.1038/s41467-025-63009-w Fig.5|In-situcharacterizationandtheoreticalcalculations.In-situFT-IRspectra *OCH intermediateonCu(100)(left)andCu(100)-CA(right).gDiagramofCA2 3 ofcommercialCuunderCORRinelectrolyte(a)withoutCA,(b)withCA.a.u. dominatedCO-to-CHOHconversionmechanismoverCucatalyst.Gibbsfree 2 2 2 5 arbitraryunits.cSchematicofCO2RRmechanismandpathwayforvarioussingle-/ energydiagramof*OC2H3toC2H4orC2H5OHover(h)Cu(100),(i)Cu(100)-CA. multi-carbonproducts.dΔGdiagramofC–CcouplingonCu(100)andCu(100)-CA. jTheatomicstructureofC–CcouplingandC2H4/C2H5OHformationstateson eCOHPanalysisofC–Obondinginteractionin*OCH intermediateonCu(100) Cu(100)-CA.Colorcode:grey(C),white(H),red(O),orange(Cu). 2 3 (left)andCu(100)-CA(right).fCOHPanalysisofCu–Obondinginteractionin theabsorbancepeaksintherangeof1200to1600wavenumberswere AfterdecouplingtheroleofCAontheselectivityofCO RR,the 2 presentedduetothepresenceofCA,indicatingthattheCAatthesubinteractionofCAattheHelmholtzplanewithH OmoleculesandH O 2 2 nanoreactioninterfaceprofoundlyaffectedtheadsorptionstrength dissociationprocesswerefurtherreal-timeinvestigatedandanalyzed and further conversion of reaction intermediates and governed the byahighlysurfacesensitivein-situRamantechnique43,44.Atthe3000CO RR mechanism.</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
+          <t>Specifically, for the system without CA, the 3800cm−1positionoftheRamanspectra,theO–Hstretchingvibration 2 *OCCOH,*OC H intermediatescorrespondingtothesynthesisofC can be decomposed into three types according to Gaussian fitting 2 5 2+ productsandC HOHlocatedat1210and1350cm−1aswellasthe*CHO (SupplementaryFig.17)45,46.Revealedbyexistingfindings43,47,K+inthe 2 5 and*OCH intermediatesassociatedwiththeformationofCH at1480 electrolytewasmorelikelytobespecificallyadsorbedontheelectrode 3 4 and1410cm−1wereclearlydetected40–42.Differently,inthepresenceof surface.</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="N99" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4074,27 +6772,55 @@
           <t>S0099</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="D100" t="n">
+        <v>2</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Tofurtherdeterminethechemicalstatesandlocalcoordination Inthiswork,viaamodifiedgalvanicreplacementapproach,two environments of Cu and Ag in AgCu NW and AgCu NW, X-ray 1 modelCu-basedcatalystsdecoratedwithAgnanoparticles(AgCuNW) absorptionnear-edgestructure(XANES)andextendedX-rayabsorpand single Ag atoms (AgCu NW) were rationallydesigned and pretion fine structure (EXAFS) measurements were conducted.</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
         <is>
           <t>The Cu 1 pared for CO RR, which exhibited distinct selectivity in electroK-edgeXANESspectrashowthattheedgefeaturesofAgCuNWand 2 1 chemical CO reduction to ethylene (Faradaic efficiency: ca. 54.9%, AgCuNW(designatedas1s→4ptransition)areclosetothoseofthe 2 currentdensity:ca.156.0mAcm−2)andethanol(Faradaicefficiency:ca. referencecommercialCufoil(Fig.1g),indicatingthatCuinAgCuNW 1 56.3%,currentdensity:ca.172.8mAcm−2).Basedonisotopiclabelling andAgCuNWexistmainlyintheformofCu(0)48.Thecorresponding experimentstogetherwithvariousoperando/in-situcharacterizations EXAFSspectraofAgCuNWandAgCuNWalsoshowthedominantCu1 includingoperandoX-rayabsorptionspectroscopy(XAS),quasiin-situ Cucoordinationatca.2.21Å(SupplementaryFigs.12,13andSuppleX-ray photoelectron spectroscopy (XPS), operando Raman spectromentaryTable4)49.AsdisplayedinFig.1h,theabsorptionedgesofthe scopy and operando attenuated total reflectance surface enhanced AgK-edgeXANESforAgCuNWandAgCuNWareobservedshifted 1 infrared absorption spectroscopy (ATR-SEIRAS), the dynamicoxidatowards higher energies compared to that for Ag foil, indicating a tionstateevolutionofCuandAgwerediscerned,andthekeyreaction higher average valence state of Ag in AgCu NW and AgCu NW, 1 intermediatesinvolvedinC-CcouplingduringCO RR,suchas*COCO matchingwellwiththeXPSresults. 2 and*COCHO,werecapturedoverAgCuNWandAgCuNW.Further 1 coupledwithdensityfunctionaltheory(DFT)calculations,theatomCO RRperformance 2 icallydispersedAgwasidentifiedtoboostH Odissociationtorelease TheelectrochemicalCO RRperformanceofCuNW,AgCuNWand 2 2 1 H+andreducetheenergybarrierfortheformationof*CHOoverits AgCuNWwerefirstevaluatedinanH-typecellfilledwithCO -satu2 neighboringCusite,leadingtoboostedasymmetric*CO-*CHOcourated0.1MKHCO electrolyte(pH =6.8),andthegasandliquidpro3 plingoverpairedCuatomsadjacenttothesingleAgatom. ducts were quantified by gas chromatography (GC) and nuclear magneticresonance(NMR),respectively(SupplementaryFigs.14,15).</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Results Linearsweepvoltammetry(LSV)curvesshowninFig.2arevealthatthe Catalystsynthesisandcharacterization currentdensitiesofbothAgCuNWandAgCuNWoutperformCuNW 1 The model Cu-based catalysts of Cu nanowires decorated with Ag in the potential range from −0.6 to −1.4V vs.</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
         <is>
           <t>P1;P2;P5</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="L100" t="inlineStr">
         <is>
           <t>P1:*COCO; P1:COCO; P2:*CO-*CHO; P2:*CHO; P5:OCHO</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="M100" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
+      <c r="N100" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4116,27 +6842,55 @@
           <t>S0100</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="D101" t="n">
+        <v>8</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>(Cu )immobilizedontheCu-reduction-inducedvacancyonHex-2CuOurexperimentsobserveaselectivityincreaseforethylenepro9 O,anddenotedasR-Hex-2Cu-O.ThecurvedstructureofHex-2Cu-O duction starting from –1.3V on Hex-2Cu-O (Supplementary Fig. 7), formsaconfinedspacebetweentheCu clusterandtheadjacentsingle whichisrationalizedbycalculationssuggestingthattheaccelerated 9 Cucenter,whichare~3.84Åapart(SupplementaryFig.34).Thismodel reactionkinetics is led by the decreased activationbarrier with the isreasonableconsideringthesimilarsizeoftheCuclustertothatofthe changeofelectrodepotential.Figure5eshowsthatat0VvsRHEthe hexaphyrinmolecule(Fig.3d).Furthermore,toincludetheimpactof formation of *HOCCOH is kinetically unfavored on R-Hex-2Cu-O/G carbon-basedconductingagentKetjenBlack(KB)intheexperiment,a with an activation energy barrier of 1.51eV (MEP shown in Supple5×5×1 graphene substrate was introduced to support the hybrid mentary Fig. 39).</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
         <is>
           <t>When applying a bias of –1.3V, the formation of structure (R-Hex-2Cu-O/G), which was used for all reaction *HOCCOHbecomesthermodynamicallydownhill(ΔE=–0.87eV)with mechanismstudy. aloweractivationenergybarrierof0.72eV,leadingtoanacceptable WefirstscrutinizedthekeyreactionintermediatesforC–Ccoureactionrateatroomtemperature46.Ourcalculationalsoconfirms*CO plingonR-Hex-2Cu-O/G,includingtwoCu-adsorbed*CObeforecoutrimerization to form n-propanol is facilitated by the spatialplingandthe*OCCOHdirectlyaftercoupling.Formostoftheactive confinementeffectonR-Hex-2Cu-O/G(SupplementaryFig.36b).The sitesexplored,alinearrelationshipexistsbetweenthetwoadsorption C pathwaytowardn-propanolisshowninFig.5candSupplementary 3 strengths(i.e.,ΔG andΔG )asshowninFig.5aandSuppleFig.40;theU is–0.98V,similartothatforethanolproduction, 2*CO *OCCOH limiting mentary Fig. 35.</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>However, some reaction sites significantly deviate and therefore agrees well with the experimental observation for a fromthislinearrelationship,withΔG decreasesfromthetrendnotableselectivitytowardn-propanol(Fig.2a).Nonetheless,itisworth *OCCOH fittedlevelsof1.27,1.21eVto0.92,0.90eV,respectively.ThesereactonotethatgiventhecomplexphasespacedemonstratedbyR-Hextionsitesarethosewithintheconfined-spacebetweentheCu cluster 2Cu-2O/Gthatwouldrequireas-of-yetunrealizedsimulationcapability 9 and the adjacent single Cu center (Supplementary Fig. 35), with an toconclusivelydepict,themechanismproposedhereispendingfor extrabondformedbetweentheadsorbed*OCCOHandadjacentCu furtherclarificationtounderstandthecausalfactorsfromelectronic center (Supplementary Fig. 36a).</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
+      <c r="L101" t="inlineStr">
         <is>
           <t>P1:*OCCO; P1:OCCO</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="M101" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
+      <c r="N101" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4158,27 +6912,55 @@
           <t>S0101</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="D102" t="n">
+        <v>8</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>DFT calculations of our previous study rangementsinfluencethereactionmechanism,itisusefulto showed that an expanded Cu lattice increases the binding correlate such changes with the formation and stability of energies for the intermediates of CORR (e.g., *CO on 2 different intermediates during CORR.</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
         <is>
           <t>The production of Cu).[9c] Additionally, Ag incorporation in Cu weakens the 2 CO increased at lower overpotentials with increasing Ag bindingenergies of the reduced aldehyde intermediates and content in the samples.[19] It has been suggested that *CO, inhibitstheirfurtherreductiontoethanoland1-propanolas which is a key intermediate for the C@C coupling mechademonstrated in a recent DFT study.[22] However, the nism,[19] might couple with *CH[20] to form the *CHCHO structural analysis of the catalysts showed that the surface x 2 intermediate, which plays a central role in the formation of partially consists of Cu/Ag areas, which also leads to the C liquid products.[21] The *CHCHO intermediate can be formationofethanoland1-propanolattheCusites,sincethey 2+ 2 hydrogenatedto*CHCHOandformacetaldehyde[Eq.(1)] are expected to have higher binding energies for the oxy3 orbefurtherhydrogenatedtoyieldethanol[Eq.(2)]. genated intermediates as compared to the Ag–Cu mixed Angew.Chem.Int.Ed.2021,60,7426–7435 T2021TheAuthors.AngewandteChemieInternationalEditionpublishedbyWiley-VCHGmbH www.angewandte.org 7433 15213773, 2021, 13, Downloaded from https://onlinelibrary.wiley.com/doi/10.1002/anie.202017070 by CochraneAustria, Wiley Online Library on [23/05/2026].</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>See the Terms and Conditions (https://onlinelibrary.wiley.com/terms-and-conditions) on Wiley Online Library for rules of use; OA articles are governed by the applicable Creative Commons License</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
+      <c r="L102" t="inlineStr">
         <is>
           <t>P2:CHO intermediate</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="M102" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
+      <c r="N102" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4200,27 +6982,55 @@
           <t>S0102</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="D103" t="n">
+        <v>8</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>The major difference between these two pathways is containingonlyonecoordinatedCuatom.Thisresultsinaconfined whetherCorOon*OCCOHisprotonated.TheprotonationonOto spacebetweentheagglomeratedCuclusterandunreducedsingleCu *HOCCOHisendergonicwithanuphillΔG=0.42eV,incontrasttothe centerinthevicinity.InthefollowingDFTinvestigationsbasedonthis exergonic protonation on C to *OCHCOH (ΔG=–0.09eV), which model(Fig.4f),wewillshowtheresultantuniquecoordinationenvirindicatesthatCO RRcanproceedpreferentiallytowardC HOHfor2 2 5 onment(i.e.,theconfinedspaceaffordinganextraO–Cubond)would mationonR-Hex-2Cu-O/G.Thereasonfortheunfavoredformationof significantlypromoteC–Ccouplingbybreakingthescalingrelation- *HOCCOHliesinthefactthattheprotonationonOisaccompaniedby ship between key intermediates and enhance alcohol selectivity by the cleavage of previously formed O–Cu bond (Supplementary reservingoxygeninthehydroxylgroup44.</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
         <is>
           <t>Fig.38).TheprotonationonCtoform*OCHCOH,followedbysubAlltheconstructedmodelsarelistedinSupplementaryFig.34. sequenthydrogenation,canbewellsupportedbythereactioninterAftergeometryoptimization,thestructureofHex-2Cu-Obendstoa mediatesdetectedbyATR-SEIRAS,especiallythestretchingoftheC–C curvedshape,coincidingwiththemolecularstructuredeterminedby coupling intermediate—*OCCOH and the C HOH precursor— 2 5 X-raycrystallography23,24.ThehybridstructureofCuclusterandpar- *OCH CH around1436and1360cm−1,respectively(Fig.4c),whichin 2 3 tially reduced Hex-2Cu-O is represented by a nine Cu atom cluster turnqualitativelyvalidatestheproposedethanolpathway(Fig.5d).</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>(Cu )immobilizedontheCu-reduction-inducedvacancyonHex-2CuOurexperimentsobserveaselectivityincreaseforethylenepro9 O,anddenotedasR-Hex-2Cu-O.ThecurvedstructureofHex-2Cu-O duction starting from –1.3V on Hex-2Cu-O (Supplementary Fig. 7), formsaconfinedspacebetweentheCu clusterandtheadjacentsingle whichisrationalizedbycalculationssuggestingthattheaccelerated 9 Cucenter,whichare~3.84Åapart(SupplementaryFig.34).Thismodel reactionkinetics is led by the decreased activationbarrier with the isreasonableconsideringthesimilarsizeoftheCuclustertothatofthe changeofelectrodepotential.Figure5eshowsthatat0VvsRHEthe hexaphyrinmolecule(Fig.3d).Furthermore,toincludetheimpactof formation of *HOCCOH is kinetically unfavored on R-Hex-2Cu-O/G carbon-basedconductingagentKetjenBlack(KB)intheexperiment,a with an activation energy barrier of 1.51eV (MEP shown in Supple5×5×1 graphene substrate was introduced to support the hybrid mentary Fig. 39).</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="L103" t="inlineStr">
         <is>
           <t>P1:*OCCO; P1:OCCO</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="M103" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
+      <c r="N103" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4242,27 +7052,55 @@
           <t>S0103</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="D104" t="n">
+        <v>6</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Ag is well electrokinetic study43.</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
         <is>
           <t>The subsequent C–C coupling process was knowntobeaweakCObindingmetal,sothefactthatCu–Aginterproposed to occur between COH and CO forming HOCCO 43. ad ad ad facialsitesbindlessstronglythannativeCu(OD)sitesshouldnotcome InvestigationsbasedontheoreticalcalculationreportedthatHOCCO ad asasurprise.Further,theCuandAgdomainsinCu(OD) 1−x Ag x catalysts was favored to go through a hydro-dehydroxylation path forming aretensofnanometersinsize,suggestingthattheinterfacialareais CHCO withthehydrogenationofα-C30,31.Thefurtherhydrogenation ad relativelyminorascomparedtothatofCudomains.Thisexplainsthe of CHCO was shown to form ethylene if either C atom is hydroad relativeconstantspecificethyleneproductionrateuponintroducing genated and to form oxygenates if the O is hydrogenated Ag toCu(OD),asthe CORR activity on Cu domains remainslargely respectively31.</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>While the C affinity of the surface could be used to unchanged(SupplementaryFig.7b).Itfollowsthattheenhancedrates predict the selectivity between oxygenates and ethylene, calculated andselectivitiesforC liquidproductsarecorrelatedwiththeCu–Ag surfacesfavoringoxygenatestendtohavebothlowCandOaffinities. 2+ NatureCommunications|( 2023)1 4:698 6</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="L104" t="inlineStr">
         <is>
           <t>P1:OCCO</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="M104" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
+      <c r="N104" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -4284,19 +7122,47 @@
           <t>S0104</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="D105" t="n">
+        <v>2</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Microkinetic ing experiments, we determine the key features of intermediate modelling26furthervalidatedtheenhancedactivityoftheCuZnalloy adsorptionandelectrocatalyticenvironmentthatleadtothemarked for CO R to C , with CuZn211 showing the highest theoretical 2 2+ Zn CO RperformancewithimprovedCO utilizationinacidicconditions. activity (Fig. 1f).</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
         <is>
           <t>Importantly, the most stable CuZn111 shows sig2 2 Zn nificantlyincreasedC activitycomparedtoCu111,whichenhanced 2+ Results C productionduringextendedCO R.TheHERactivitywasalsocal2+ 2 Mechanisticstudiesandcatalystdesign culatedon(111),(100),and(211)surfacesofCuandCuZn.Ingeneral,a To search for promising catalysts, we set out from a mechanistic worseHERactivitywasobtainedonalltheCuZnsurfacescompared analysisofCO -to-C conversionoverthesimplifiedreactionnetwork withthatonCuduetotheweakerH*binding(SupplementaryFig.7). 2 2+ (Supplementary Fig. 1) and calculated activity trends via density Overall,ourglobalenergyoptimizationschemeindicatedthatalloying functionaltheory(DFT).ThreemajorC–Ccouplingmechanismswere ZnwithCuenablesasymmetricsurfaceCO*bindingsonsurfacebinary considered: CO*–CO* (R5), CO*–CHO* (R6), and CO*–COH* (R7) sites to reduce the reaction energy for C–C coupling, therefore (SupplementaryTable5).Inadditiontoseveralimportantprotonation effectivelypromotingCO -to-C reduction. 2 2+ steps, six reaction pathways were enumerated (Supplementary Tables 5, 6).</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
+          <t>We then followed an energy-global-optimization Modelcatalystandco-sputteredcatalyststudies scheme24,25todeterminetheoptimallimitingenergyforagivencataToverifythecomputationalresults,wefabricatedaseriesofCu x Zn 1−x lyst(Fig.1a,Methods).</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
+      <c r="N105" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4318,27 +7184,55 @@
           <t>S0105</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="D106" t="n">
+        <v>4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Consistent with previous reports14,15, the observing analogous signals on a different Cu foil with distinct surface signals appearing at 1,450 cm−1 and 1,550 cm−1 from −0.76 V can be morphology, yet with still good performance towards C products RHE 2+ attributed to *OCCO(H), with the C=O vibration mode (Fig. 3 and Sup- (Supplementary Fig. 19). plementary Tables 4 and 5).</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
         <is>
           <t>Alternatively, such frequencies can be As ethanol and acetaldehyde are the main C products for gly2 assigned to an OCCO− dimer adsorbed on surface oxygen (O), known oxal reduction on polycrystalline copper and are proposed to share s as deprotonated glyoxylate OCOCO2− (ref. 36), which also shows the the same *OCHCH intermediate16–18, we performed in situ Raman s 2 1,070 cm−1 band detected at −0.76 V (Supplementary Table 6). experiments of glyoxal and ethanol reduction (Supplementary Figs. 20 RHE Among other additional possible intermediates (*OCCHO, *OHCand 21).</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>As shown in Fig. 4c, similar bands at about 1,290 cm−1, 1,420 cm−1 COH, *OCCHOH, *CHO and *CH; Supplementary Tables 7–11), we attriband 1,605 cm−1 are observed during glyoxal reduction.</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
+      <c r="L106" t="inlineStr">
         <is>
           <t>P1:OCCO; P1:COCO</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4360,27 +7254,55 @@
           <t>S0106</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
+      <c r="D107" t="n">
+        <v>3</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Both vibrational spectra30,31 and kinetic models32,33 coupling. reveal that *CO is the main intermediate on Cu surface under Further analysis found that these square sites have different reduction conditions.</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
         <is>
           <t>Considering that C 2+ pathway displays a localstructures.Therefore,weclassifiedthesesitesintofourtypes: pH independent on SHE scale, 2*CO dimerization is thus the planar-square (p-sq), step-square (s-sq), concave-square (cc-sq) most accepted form for C–C coupling on copper surface34. and convex-square (cv-sq). p-sq sites are the Σ3 grain boundary )Ve( ygrenE noitcaeR non-square sites square sites selected square sites 1.63eV 1.27eV Average E(*CO) (eV) 1.2 1 0.8 0.6 0.4 0.2 0 -0.2 )Ve( ygrenE noitcaeR d 1.2 1 0.8 0.6 0.4 0.2 0 (111) (100) (221) p-sq s-sq cc-sq cv-sq )Ve( reirraB noitcaeR 0.4 0.2 0 -0.2 -0.4 -0.6 -1.1 -1 -0.9 -0.8 -0.7 -0.6 -0.5 (111) (100) (221) p-sq s-sq cc-sq cv-sq )Ve( )OCOC*(E ARTICLE NATURECOMMUNICATIONS|https://doi.org/10.1038/s41467-020-20615-0 a b c non-square sites square sites selected square sites y=1.82x+1.48 planar-square step-square y=1.85x+1.14 concave-square convex-square Average E(*CO) (eV) e f g p-sq s-sq cc-sq cv-sq side view top view Fig.2IdentificationofC–Ccouplingactivesites.aReactionpathwayforC 2+productsinCO2R.bTheadsorptionenergyof*COCOasthefunctionofthe averageadsorptionenergyoftwoadsorbed*CO.cReactionenergy(2*CO→*COCO)asthefunctionoftheaverageE(*CO)onthesesites.dDFTperiodic slabmodelsoffoursquare-likesites.e*OCCOconfigurationsonthesefoursites(solventmoleculeshavebeenremovedtoshowtheadsorbate configurations).fReactionenergiesandgbarriers(2*CO→*COCO)ondifferentDFTslabmodelsunderappropriateelectrochemicalinterface.Colorcode: brown-Cu;yellow-Cuinsquare-likesites;gray-C;red-O.</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>NATURECOMMUNICATIONS| (2021) 12:395 |https://doi.org/10.1038/s41467-020-20615-0|www.nature.com/naturecommunications 3</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
+      <c r="L107" t="inlineStr">
         <is>
           <t>P1:*CO dimerization; P1:CO dimerization; P1:*OCCO; P1:OCCO; P1:*COCO; P1:COCO</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
+      <c r="M107" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
+      <c r="N107" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4402,27 +7324,55 @@
           <t>S0107</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
+      <c r="D108" t="n">
+        <v>7</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>These effects stabilize the Fig. 32)48.</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
         <is>
           <t>Combining with time-independent spectral analysis (SupoxidationstateofCu+speciesduringCO electroreduction,allowing 2 plementaryFig.33A,B),apparentpeaksaredeterminedat1064and forthesynergisticeffectofCuandCu+species. 1558cm−1, which correspond well to the symmetric and asymmetric ThereactionbarriersforthehydrogenationprocessofC inter2+ vibrationsofthe*OCCOHintermediate,respectively49,50.Inaddition, mediatesonthemodelsofCu/CuOwithandwithoutCl,respectively, 2 thestretchingvibrationat1335and1716cm−1areincloseproximityto werecalculatedbyDFT.Firstly,byanalyzingtheBaderchargeandbond thestretchingof*OCH CH and*CHO,respectively,whichserveasthe length of Cu/CuO (Fig. 5C, D), it is observed that the lower Bader 2 3 L 2 important intermediates for the subsequent C–C coupling in the chargevalue(0.477|e|)comparedtoCu /CuO(1.01|e|)indicatesthat P 2 productionofC alcohols51,52.Theseconclusionsareconsistentwith thepopulatedelectronicorbitalsoflow-coordinatedCusiteswilleasily 2+ theresultsobtainedfromtheproductanalysisofCu /Cu OandCu / bindtointermediatesandreducetherate-determiningenergybarrier67.</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>P 2 L Cu O.IntheRamanspectra(Fig.5BandSupplementaryFig.33D),the Cu/CuOwithadditionallyformedemptyorbitalscanfacilitateelectron 2 L 2 Cu /Cu Opowderloadedoncarbonpapersubstrateexhibitstypical transferfromhydrogentonucleophilicintermediates,suggestingtheCu L 2 characteristic peaks of adsorbed *CO intermediates, which are 3dorbitalsoverlapwiththeπorbitalsofCandfurtherreducedactivation deconvoluted into a low-frequencyband (LFB) at ∼2045cm−1 and a energyforCO hydrogenationonCu/CuO68.Asaresult,thenucleo2 2 high-frequencyband(HFB)at∼2097cm−1,whichverifiesthebonding philic addition reaction process of *CHCO–*CO coupling may effec2 stylesonterraceandstepsites,respectively53,54.Aredshiftoftheυ(CO) tivelyreactonthemixed-valenceboundaryregion33,whichreducesthe bandindicatestheenhancedinteractionbetweenthecatalystsurface formation energy of *CHCOCO on Cu/CuO (−0.148eV) toward 2 L 2 and *CO, resulting in a higher *CO coverage55.</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
         <is>
           <t>P1;P2;P3</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
+      <c r="L108" t="inlineStr">
         <is>
           <t>P1:*OCCO; P1:OCCO; P2:*CHO; P3:COH intermediate</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
+      <c r="M108" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
+      <c r="N108" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4444,19 +7394,47 @@
           <t>S0108</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
+      <c r="D109" t="n">
+        <v>2</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Further, the G -limiting RPD CO R,thesteppedCufacetsarereconstructedasCu(111)facets,which energyonCuZn (R1,SupplementaryTable5)waslowerthanthaton 2 Zn arelessactiveforC production,leadingtosubstantialperformance pureCu(R5,SupplementaryTable5),confirmingthepromotionofC 2+ 2+ deteriorationovertime. activityonCuZnsurfaces.</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
         <is>
           <t>Wetheorizethatalloyingstrategies,inwhichanenhancermetalis Wecalculatedtheactivationbarriersascriticalkineticparameters introducedintothelow-activitybutrelativelystableCu(111)facets,can forevaluatingtheactivityofC–Ccoupling.Figure1dshowsCO*–CO* createneighbouringbinarysiteshavingasymmetricsurfaceCObindcouplingonCu,CuZn ,andCuZn (211)facets.Thekineticenergyis Cu Zn ing energies to improve C–C coupling beyond the scaling-relationreducedby~0.16eVontheCuZn site.Wecomparedtheactivation Zn determinedactivitylimitationsonsingle-metalsurfaces.Wedevelop energiesforCO*–CO*,CO*–CHO*,andCO*–COH*couplingversusthe anactiveglobal-energy-optimizationdiagramtoidentifytheoptimal correspondinglimitingpotentialsoftherelevantpathsonlow-index routeforC–Ccouplingondifferentactivebinarysitesinelectrolytes Cu, CuZn and CuZn (111), (211), and (100) surfaces (Fig. 1e).</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
+          <t>Cu, Zn underreductionconditions.UsinginsituRamanspectroscopy,elecCuZn211 was identified as the most active site, with a small C–C Zn trochemicalhydrodynamicsimulations,andelectrochemicaloperatcoupling barrier and a low limiting potential (Fig. 1e).</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
+      <c r="N109" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4478,27 +7456,55 @@
           <t>S0109</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
+      <c r="D110" t="n">
+        <v>2</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>The Faradaic 2 intermediates14. efficiencies of C products show a typical volcano dependence on 2+ Here we provide direct spectroscopic evidence of potentialthe applied potential, with a maximum of 65% at about −1.0 V .</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
         <is>
           <t>The RHE dependent CO dimerization and subsequent reduction intermedionset potentials for ethylene and ethanol are about −0.8 V and RHE ates during CORR on a Cu surface by combining insights from in situ −0.9 V , with these products reaching a maximum value at −1.0 V 2 RHE RHE surface-enhanced Raman spectroscopy (SERS) and density functional and −1.05 V , respectively.</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>RHE theory (DFT)-based vibrational analysis.</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
+      <c r="L110" t="inlineStr">
         <is>
           <t>P1:CO dimerization</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4520,19 +7526,47 @@
           <t>S0110</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
+      <c r="D111" t="n">
+        <v>2</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>RHE theory (DFT)-based vibrational analysis.</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
         <is>
           <t>This allows us to identify crucial Cu sites and surface intermediates for either ethylene or ethanol, Potential-dependent intermediate evolution leading to the definition of an updated reaction scheme for CORR to To reveal molecular insights into C–C coupling intermediates and 2 C products. their potential dependence, we carried out in situ SERS measurements 2 (Supplementary Fig. 7).</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Figure 2a shows the in situ Raman spectra Electrode preparation and CO RR test acquired at the same position on the electrochemically treated Cu 2 The Cu electrodes were prepared by an electrochemical oxidation– foil electrode as a function of the applied potential in a CO-saturated 2 reduction process (see Methods for details).</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4554,19 +7588,47 @@
           <t>S0111</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
+      <c r="D112" t="n">
+        <v>6</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>These undercoordinated distorted sites 3 ethanol competition, the *O binding strength49.</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
         <is>
           <t>Crystalline sites with open the OCHCH-mediated ethanol route (Fig. 6d). 2 Nature Energy | Volume 9 | December 2024 | 1485–1496 1490 ).u.a( ytisnetnI )Am( tnerruC ).u.a( ytisnetnI 900 910 920 N = 4–5 Cu–Cu Raman shift (cm–1) ).u.a( ytisnetnI a b c 0.3 CuI Cu LMM –1.12 V Cu0 Envelope 0.2 –1.0 V –1.04 V 0.1 –0.8 V 0 –1.1 –1.0 –0.9 –0.8 Kinetic energy (eV) d e –0.95 V –0.85 V –0.76 V ×5 –0.56 V fo oitar ycneiciffe ciadaraF enelyhte/lonahte 1,000 cps Potential (V) 0.08 –0.8 V –1.0 V 0.04 0 –0.04 –0.08 –0.2 0 0.2 0.4 1,950 2,100 Potential (V) Raman shift (cm–1) Fig. 5 | Defect-driven mechanisms for CORR to ethylene and ethanol. a, Ratio The Raman data in c are from the same dataset as those in Fig. 2. d, DFT C–O 2 of the Faradaic efficiencies of ethanol and ethylene as a function of the applied stretching wavenumber as a function of the Cu–Cu coordination number, potential. b, Quasi in situ Cu LMM XAES spectra of electrochemically pre-treated decreasing from orange (N = 4–5) to dark brown (N = 7–8). e, Cyclic Cu–Cu Cu–Cu Cu foils after 1 h of CORR at −0.8 V and −1.0 V without air exposure. c, voltammograms of the electrochemically treated Cu foil after 1 h of CORR at 2 RHE RHE 2 Dependence of the C–O stretching band on the applied potential.</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>The Raman −0.8 V and −1.0 V .</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4588,19 +7650,47 @@
           <t>S0112</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
+      <c r="D113" t="n">
+        <v>18</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>S (i) Comparison of the *OC /(*OC +*OC ) ratio in in-situ FTIR spectra for different bridge bridge atop S catalysts at different applied potential.</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
         <is>
           <t>(j) Schematic illustration of the underexplored asymmetric E coupling process and ethanol path directed selectivity problem in CO electroreduction, and flow R 2 diagram illustrating the working principles of isotopic tracking of surface-adsorbed intermediates P based on 12C/13C and H/D isotopes in tandem with in-situ FTIR spectra.</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>(k) Schematic for boosted EtOH generation over Co -Sub-CuS.</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4622,27 +7712,51 @@
           <t>S0113</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
+      <c r="D114" t="n">
+        <v>19</v>
+      </c>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr">
         <is>
           <t>ARTICLE IN PRESS In-situ FTIR spectra of *OCCOH intermediates involved in C-C asymmetric coupling were verified using hydroxypropanone, a compound with a hydroxyl group adjacent to the carbonyl group (OCCOH).</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>The band detected at 1152 cm-1 on Co -Sub-CuS during CO ER at -0.8 V is 0.050 2 consistent with the C-OH of hydroxypropanone (Supplementary Fig. 59 and Fig. 3a).</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
         <is>
           <t>P1;P3</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
+      <c r="L114" t="inlineStr">
         <is>
           <t>P1:*OCCO; P1:OCCO; P3:COH intermediate</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
+      <c r="M114" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
+      <c r="N114" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4664,19 +7778,43 @@
           <t>S0114</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
+      <c r="D115" t="n">
+        <v>41</v>
+      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
         <is>
           <t>ARTICLE IN PRESS coupling process and ethanol path directed selectivity problem in CO electroreduction, and flow 2 diagram illustrating the working principles of isotopic tracking of surface-adsorbed intermediates based on 12C/13C and H/D isotopes in tandem with in-situ FTIR spectra.</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>(k) Schematic for boosted EtOH generation over Co -Sub-CuS.</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4698,19 +7836,47 @@
           <t>S0115</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
+      <c r="D116" t="n">
+        <v>6</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Elemental analysis further shows that the Cu clusters CuclustersduringCO RRwasalsowitnessedbyTime-lapseXAFSata remainedontheelectrodeaccountfor∼82%oftheoriginalCucon2 constantpotentialof−1.2V(SupplementaryFig.25).Injust8min,Cu tent, and that the N content isnotably reduced after soaking (Supcentersinthecomplexwerealreadypartiallyreduced,aswitnessedby plementaryTable5).InthesubsequentretestingofCO RR,theFEof 2 thecoexistenceofCu0andCu–N/OspeciesinboththeXANESandFTmulti-carbonproductsat−1.2Vdecreasesfrom66.2%fortheoriginal EXAFSspectra.After24min,thewholecatalystsystemwasstabilized, catalystto22.1%,inwhichethanolandn-propanolaccountforonly withsimilarCuoxidationandcoordinationstatestilltheendofthe 8.8%and8.2%,respectively.Meanwhile,thetotalefficiencyofC pro1 test.ItisthussurmisedthatmetallicCureducedfromorganometallic ducts(includingformate,COandmethanol)increasesfrom16.3%to precursorsmightimposeself-constraintonparticlegrowthduetothe 40.3%(SupplementaryFig.32).Thisresultissomehowsimilartothe ligand tethering effect and catalyst-support interaction, which have productdistributionobservedonOct-2Cu,whichformscopperclusbeen demonstrated in previous literature reports4,33,34, and further ters and fragmented ligands during electrolysis.</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
         <is>
           <t>Collectively, these confirmed here by plotting the potential-dependent Cu–Cu CNs observationshelptojustifytheroleofthepartiallyreducedHex-2Cu-O revealingtheslow-downofparticlegrowthwithincreasingbias(SupincontributingtobothC andalcoholproduction.Toreinforcethis 2+ plementaryFig.26).Collectively,ourcomprehensivecharacterizations pointofview,wefurthercastedthesolutefromthesoakingsolution aboveshouldhelptorationalizethegreatelectrocatalyticactivityand backontotheelectrode(SupplementaryFig.33)andobservedthatthe stabilityofHex-2Cu-OaswitnessedinFig.2d. alcoholproductionwaspartiallyrestored.Comparedtotheethanolsoakedelectrode,theregeneratedhybridcatalystcomprisingthecastMechanisticinsightsintothehighC 2+andalcoholproduction back organic phase and Cu clusters is able to augment the FEs of OurchoiceofHex-2Cu-O,Hex-2Cu-2Oand Oct-2CuastheCO RR oxygenates and hydrocarbons atall applied potentialsfrom −1.0to 2 catalysts offers a paradigm for illustrating the correlation of −1.4V(Fig.4a,b).Thesepost-mortemtreatmentsstronglysupportthe structure-property-performance.Forthetwobicentrichexaphyrin interplaybetweenCuclustersandpartiallyreducedHex-2Cu-Oligands complexes, although all copper ions are coordinated to three tosynergisticallypromoteC alcoholproduction. 2+ nitrogen and one oxygen, the geometry and symmetry of the In situ attenuated total reflection surface-enhanced infrared coordinationspheresarequitedifferent.Thesharedoxygenatom absorption spectroscopy (ATR-SEIRAS) was employed to probe the in Hex-2Cu-O and the intramolecular tension from the gabled intermediates associated with multi-carbon alcohol production on structure make the complex less thermodynamically stable, and Hex-2Cu-O (Fig. 4c).</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
+          <t>A prominent absorption band at 2095cm−1, thustheCuatomsaremoreactiveandcanbestrippedofftoform attributed to the C≡O stretching mode of *CO36, is observed atall metal clusters.</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
+      <c r="N116" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -4732,27 +7898,55 @@
           <t>S0116</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
+      <c r="D117" t="n">
+        <v>8</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>However, some reaction sites significantly deviate and therefore agrees well with the experimental observation for a fromthislinearrelationship,withΔG decreasesfromthetrendnotableselectivitytowardn-propanol(Fig.2a).Nonetheless,itisworth *OCCOH fittedlevelsof1.27,1.21eVto0.92,0.90eV,respectively.ThesereactonotethatgiventhecomplexphasespacedemonstratedbyR-Hextionsitesarethosewithintheconfined-spacebetweentheCu cluster 2Cu-2O/Gthatwouldrequireas-of-yetunrealizedsimulationcapability 9 and the adjacent single Cu center (Supplementary Fig. 35), with an toconclusivelydepict,themechanismproposedhereispendingfor extrabondformedbetweentheadsorbed*OCCOHandadjacentCu furtherclarificationtounderstandthecausalfactorsfromelectronic center (Supplementary Fig. 36a).</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
         <is>
           <t>The extra O–Cu bond boosts the structureandultimatelythecontributionsofstructuralevolutionto *OCCOH adsorption while not affecting the 2*CO adsorption, and theobservedkinetics. thereforebreakthescalingrelationbetweenthesetwocarbonaceous Inshort,ourcalculationsshowthehighlyunder-coordinatedCu intermediatestopromoteC–Ccoupling. clusterinthehybridinorganic/organicstructuresuppressesHERby Additionally,thehighlyunder-coordinatedCuclusteronR-Hexenhancing *CO adsorption, and thereby promotes C–C coupling to 2Cu-O/Gcaninhibitcompetitivehydrogenevolutionreaction(HER), form *OCCOH, which is the PDS.</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Furthermore, the confined space further contributing to its higher C selectivity.</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
+      <c r="L117" t="inlineStr">
         <is>
           <t>P1:*OCCO; P1:OCCO</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="M117" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
+      <c r="N117" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4774,19 +7968,47 @@
           <t>S0117</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
+      <c r="D118" t="n">
+        <v>7</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>L 2 conducted in the shift range of 200–1600cm−1, and the results are presentedinSupplementaryFigs.33Aand34A.InthecaseofCl–Cu O Discussion 2 samples, characteristic signals were observed at 224, 425, 522, and Thementionedtheoreticalandexperimentalstudiesprovidetangible 626cm−1,whichwereattributedtothe2Γ− ,4Γ− ,Γ+ ,andΓ− +Γ+ proofthattheenhancedrectifyinginterfaceoflow-coordinatedCu/CuO 12 12 25 12 25 2 phonon modes, respectively56,57.</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
         <is>
           <t>These Raman signals gradually disMott–Schottkycatalystplaysanessentialroleintheselectiveproduction appearwithin the potentialrange from −0.2 to −0.7V vs RHE, indiofC .Weemphasizeseveralelementsofthelow-coordinated 2+alcohols catingthecompletereductionofCu OtometallicCu.Incontrast,the Cu/CuOcatalystfortheupgradedCERperformance.Firstly,thefast 2 L 2 Cl–Cu O samples retain the characteristic Raman modes (2Γ− and electronexchangeandenhancedintermediateadsorptionatsynergistic 2 12 Γ− +Γ+ )evenatpotentialsgreaterthan−0.7V,suggestingthatthe rectifyinginterfaceregionsareduetothelowcoordinationandasym12 25 low-coordinatedCu /Cu OcanprotectCu+speciesagainstreduction metricelectronaggregationinsidetheCu/CuOcatalyst.Inaddition,the L 2 L 2 duetoacombinationofenvironmentalandstructuralfactors.Overall, excellent conductivity and charge difference of Cu+/Cu0 boost the Cu /Cu Ocatalystexhibitsastrongeradsorptioncapacityfor*COdue nucleophilicorelectrophilicadditionreactionprocessforC–CorC–C L 2 2 totherestrictedrotationandstretchingvibrationpeaksofadsorbed coupling.</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
+          <t>Secondly, the fast electron transfer from Cu to Cu+ at the *COandtheCu–CObondataround274and358cm−1,respectively58. enhancedrectifyinginterfacecaninducelatticeshrinkage,inhibitingthe Specifically,thecoverageof*COiscloselycorrelatedwiththeintensity lossofresidualoxygenatomsresponsibleforstabilizingthechemical ratioofν(Cu−CO)toν(*CO)59.Importantly,theintensityratioofν(Cu valenceofCu+whenworkingwithresidualClatoms.ThecleanCu/CuO 2 −CO)toν(*CO)ofCu /Cu OishigherinthecaseofCu /Cu Ocomregionsensuresmoothabsorptionanddesorption,aswellasthecouL 2 L 2 paredtoCu /Cu O,implyingagreaterCOcoverage,whichisfavorable plingbehavioroftheoxyhydrocarbonintermediates.Thirdly,abundant P 2 fortheoxidationstateofCu+.Thepeaksobservedat1015,1024,and defectsoriginatedfromoxygenvacanciesandresidualCl,asaresultof 1069cm−1canbeassignedtothevibrationsofν(C–O)ofHCO −,OCO electrochemically reconstructing Cl–CuO, supply rich free electrons 1 3 2 antisymmetric stretching from *COOH, and ν (C–O) of CO 2−, andlandingsitesforadsorbedintermediates.Theseresultsworktoge2 3 respectively60.</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
+      <c r="N118" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4808,27 +8030,55 @@
           <t>S0118</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
+      <c r="D119" t="n">
+        <v>3</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>This value is very close to the adsorption energy difpresented on Cu catalyst.</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
         <is>
           <t>The pathway for C 2+ products26–28 is ference, 0.31eV, of *COCO over Cu(111) and Cu(100), indicatillustratedinFig.2a.SolidexperimentalresearchesshowthatCO ing the decreased intercept is merely attributed to the additional 2 electroreduction to multi-carbon products isindependent on the stabilizing effect for *COCO intermediate at square-like sites. standard hydrogen electrode (SHE) scale and C–C coupling step ReflectedinreactionenergyofC–Ccouplingprocess(Fig.2c),the that does not involve proton transfer is considered as rateaverage reaction energy on square sites is 1.27eV, 0.36eV lower determiningstep(RDS)29,whichmeanstherateofC–Ccoupling thanthatonnon-squaresites.Therefore,square-likesitesarethe determines the whole activity for C 2+ products over OD-Cu most potential candidates to serve as active sites for C–C catalysts.</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Both vibrational spectra30,31 and kinetic models32,33 coupling. reveal that *CO is the main intermediate on Cu surface under Further analysis found that these square sites have different reduction conditions.</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr">
+      <c r="L119" t="inlineStr">
         <is>
           <t>P1:*COCO; P1:COCO</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
+      <c r="M119" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
+      <c r="N119" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4850,27 +8100,55 @@
           <t>S0119</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
+      <c r="D120" t="n">
+        <v>8</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Article https://doi.org/10.1038/s41467-022-32740-z DFTmodeling including C HOH, C H and C HOH.</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
         <is>
           <t>The reaction pathways are 2 5 2 4 3 7 In the existing reports of organometallics-derived copper catalysts, summarized in Fig. 5c; a more detailed thermodynamic profile metalliccopperhasbeenoftenperceivedastheonlymotifresponsible regarding all reaction intermediates is given in Supplementary forCO reduction42,43.However,inthecurrentcomparativestudyboth Tables6–8.FortheC pathways(blueandblack),the*COcouplingand 2 2 the characterization results and control experiments suggest there subsequentproton-coupledelectrontransfer(PCET)toform*OCCOH exists a synergy between the Cu clusters and partially reduced (2*CO+H++e− → *OCCOH) show the maximum uphill free energy O-containing hexaphyrin complexes in promoting C production, change (ΔG).</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>This step isthe potential-determine step (PDS) with a 2+ especially the alcohols.</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr">
+      <c r="L120" t="inlineStr">
         <is>
           <t>P1:*OCCO; P1:OCCO; P1:*COCO; P1:COCO</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
+      <c r="M120" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
+      <c r="N120" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4892,27 +8170,55 @@
           <t>S0120</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
+      <c r="D121" t="n">
+        <v>8</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Although the exact structure of this hybrid limiting potential(U )of–0.92V.Thesubsequentreductionof limiting complexisdifficulttocharacterizeexplicitly,westillbuildastructure *OCCOHonR-Hex-2Cu-O/Gproceedsintwomajorpathways(Fig.5c), model,basedonalltheexperimentalevidencegainedaboveaswellas including:(1)C H pathway(black)viatheformationofintermediate 2 4 thebestscientificguess,fortherestructuredHex-2Cu-Obyplacinga *HOCCOH, and (2) C HOH pathway (blue) via the formation of 2 5 Cu cluster adjacent to the partially reduced Hex-2Cu-O molecule *OCHCOH.</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
         <is>
           <t>The major difference between these two pathways is containingonlyonecoordinatedCuatom.Thisresultsinaconfined whetherCorOon*OCCOHisprotonated.TheprotonationonOto spacebetweentheagglomeratedCuclusterandunreducedsingleCu *HOCCOHisendergonicwithanuphillΔG=0.42eV,incontrasttothe centerinthevicinity.InthefollowingDFTinvestigationsbasedonthis exergonic protonation on C to *OCHCOH (ΔG=–0.09eV), which model(Fig.4f),wewillshowtheresultantuniquecoordinationenvirindicatesthatCO RRcanproceedpreferentiallytowardC HOHfor2 2 5 onment(i.e.,theconfinedspaceaffordinganextraO–Cubond)would mationonR-Hex-2Cu-O/G.Thereasonfortheunfavoredformationof significantlypromoteC–Ccouplingbybreakingthescalingrelation- *HOCCOHliesinthefactthattheprotonationonOisaccompaniedby ship between key intermediates and enhance alcohol selectivity by the cleavage of previously formed O–Cu bond (Supplementary reservingoxygeninthehydroxylgroup44.</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Fig.38).TheprotonationonCtoform*OCHCOH,followedbysubAlltheconstructedmodelsarelistedinSupplementaryFig.34. sequenthydrogenation,canbewellsupportedbythereactioninterAftergeometryoptimization,thestructureofHex-2Cu-Obendstoa mediatesdetectedbyATR-SEIRAS,especiallythestretchingoftheC–C curvedshape,coincidingwiththemolecularstructuredeterminedby coupling intermediate—*OCCOH and the C HOH precursor— 2 5 X-raycrystallography23,24.ThehybridstructureofCuclusterandpar- *OCH CH around1436and1360cm−1,respectively(Fig.4c),whichin 2 3 tially reduced Hex-2Cu-O is represented by a nine Cu atom cluster turnqualitativelyvalidatestheproposedethanolpathway(Fig.5d).</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
+      <c r="L121" t="inlineStr">
         <is>
           <t>P1:*OCCO; P1:OCCO</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
+      <c r="M121" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
+      <c r="N121" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4934,27 +8240,55 @@
           <t>S0121</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
+      <c r="D122" t="n">
+        <v>12</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Chen,C.etal.Theinsitustudyofsurfacespeciesandstructuresof G.Z.conceivedandsupervisedthestudy.Y.Z.conductedexperiments oxide-derivedcoppercatalystsforelectrochemicalCO reduction. andanalyzeddata.Y.C.performedandpreparedtheDFTcalculations 2 Chem.Sci.12,5938–5943(2021). section.X.W.andY.F.conductedsomeexperiments.Z.D.andM.C. 59.</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
         <is>
           <t>Zhan,C.etal.RevealingtheCOcoverage-drivenC–Ccoupling assistedtheelectrochemicalinsituFourierTransformInfrared(FTIR) mechanismforelectrochemicalCO reductiononCuOnanocubes spectroscopyandRamananalysis.G.Z.contributedsignificantlytothe 2 2 viaoperandoRamanspectroscopy.ACSCatal.11,7694–7701(2021). analysisandmanuscriptpreparation.Allauthorsparticipatedinthe 60.</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Shan,W.etal.Insitusurface-enhancedRamanspectroscopicevianalysiswithconstructivediscussions. denceontheoriginofselectivityinCO electrocatalyticreduction. 2 ACSNano14,11363–11372(2020).</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr">
+      <c r="L122" t="inlineStr">
         <is>
           <t>P1:COCO</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr">
+      <c r="M122" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
+      <c r="N122" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4976,27 +8310,55 @@
           <t>S0122</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
+      <c r="D123" t="n">
+        <v>7</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Simultaneously with the CO-related band, a band at residual Cl atoms61,62.</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
         <is>
           <t>(2) The presence of coordination defects and 1305cm−1 associated with *COH stretching grows, and *COOH disoxygen vacancies increases the adsorption of intermediates rather appears in the spectra. which indicates the performance of CO than forming proton bonds with O atoms of Cu–O to avoid the 2 reduction.Theabsenceofthebandsat1589cm−1inthetransmission reductionofCu+species63,64.(3)Strongelectronicinteractionsoccur spectrapoints out the possibility of the *OCCOH coupling reaction betweencarbonintermediatesandCu+species65,66.WhenCOformsa duringthereductionofCO onCu /Cu O(Fig.5A).However,inconhybridizationorbitalwiththeCud-states,the5σand2π*orbitalsof*CO 2 L 2 trast to Cu /Cu O catalyst, some new signals at 1706, 1543, and splitintobondingandanti-bondingorbitals.Inthisprocess,electrons L 2 1399cm−1correspondingtothestretchof*CHO,*OCCO,and*OCHO fromtheCud-bandaretransferredtothe2πorbitalsof*COthroughdintermediatesemergedinspectraofCu /Cu O,certifyingthecoupling 2πbackdonation,whileelectronsfromthe5σorbitalof*COdonateto P 2 mode of OC–CO and possible formate product (Supplementary the Cu d-band through 5σ-d donation30.</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>These effects stabilize the Fig. 32)48.</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
         <is>
           <t>P1;P2;P3;P5</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
+      <c r="L123" t="inlineStr">
         <is>
           <t>P1:*OCCO; P1:OCCO; P2:*CHO; P3:*COH; P5:*OCHO; P5:OCHO</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
+      <c r="M123" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
+      <c r="N123" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5018,27 +8380,55 @@
           <t>S0123</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr">
+      <c r="D124" t="n">
+        <v>8</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>ARTICLE NATURECOMMUNICATIONS|https://doi.org/10.1038/s41467-022-29035-8 Density functional theory calculations.</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
         <is>
           <t>Theoretical investigabondformationtoCH CH OH.Similarreactionprocessesbased 3 2 tions were conducted based on DFT calculations to further on *OCHO mechanism were considered for Cu –CuN , as well 3 3 understand the reaction mechanism of the Cu –CuN cluster asCuN andCu–CuN whichcontainedonlyoneactiveCusite, 2 3 3 3 withCH * adsorbed.AsupportedCu –CuN clustermodelwith as shownin Supplementary Fig. 29.Thecalculated overpotential 3 2 3 aCubondingwiththreeNatomsonN-dopedcarbonnanosheets (−0.501V) for Cu –CuN cluster was much lower than that of 2 3 was proposed to be the structure of active sites with an applied CuN (−1.685V), Cu–CuN (−1.368V) and Cu –CuN 3 3 3 3 potential of −1.1V vs.</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>RHE in Supplementary Fig. 28a.</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
+      <c r="L124" t="inlineStr">
         <is>
           <t>P5:*OCHO; P5:OCHO</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr">
+      <c r="M124" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
+      <c r="N124" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5060,27 +8450,55 @@
           <t>S0124</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr">
+      <c r="D125" t="n">
+        <v>7</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>The differential charge distribution analysis and Bader charges of 3 determined that the positive charge was higher on the Sn atom, such that bonding between Sn atom and HCOOH (externally added or in-situ produced over SnS ) was favored.</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
         <is>
           <t>With PCET, the carbonyl group in HCOOH* can easily dehydrate to 2 generate Sn-CHO in intermediate 4, with a free energy barrier of 0.52 eV.</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>This intermediate 4 features *CHO on Sn and *CO(OH) on the neighboring O (i.e., O2Sn-O-CO(OH) bicarbonate), which explains the activities of Sn and O atoms as the dual active centers in the Sn -O3G.</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
+      <c r="L125" t="inlineStr">
         <is>
           <t>P5:HCOO</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
+      <c r="M125" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
+      <c r="N125" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5102,19 +8520,43 @@
           <t>S0125</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr">
+      <c r="D126" t="n">
+        <v>4</v>
+      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr">
         <is>
           <t>Article https://doi.org/10.1038/s41467-023-36926-x Fig.2|ElectrochemicalandinsituRamananalysesfortheco-sputtered potentialsduringCO2R.eInsituRamanpeaksat250–470,1750–2300cm−1and Cu y Zn 1−y (y=0.95,0.9,0.85,0.8)andCucatalystsin0.75MKOHelectrolyte. 2700–3200cm−1.fC 2+ /C 1 FEs.Errorbarsrepresentthestandarddeviationbasedon aTheCH partialcurrentdensityneartheonsetpotentials.bTafelplotsforCH. threeindependentmeasurements.Allpotentialsarewithrespecttothereversible 2 4 2 4 InsituRamanpeaksforCOadsorptiononcCu0.9Zn0.1anddCuatvarious hydrogenelectrodes(RHE). consistentwiththeethyleneonsetpotentialintheelectrochemical promotetheC–Ccouplingkineticsinelectrolytes,consideringthe tests.TheC–Hstretching(2800–3000cm−1)islikelyattributedto factoflowgas-phaseCOsolubilityinaqueoussolutions. intermediatescontainingC–Hbondssuchas(1)C H O*29–theC To further improve the CO -to-C activity, we developed an 2 2 2+ 2 2+ intermediateafterC–Ccouplingandhydrogenation,or(2)CHO*or alloying–dealloying strategy to synthesize nanoporous Cu Zn 0.9 0.1 COH*30–thekeyintermediatesforC–CcouplingviatheCO*–CHO* catalysts on PTFE over a large area (Fig. 3a, b, and Supplementary and CO*–COH* pathways.</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
+          <t>The Raman signals of CO 2− and HCO − Figs.15,16).ThesputteredCuformscontinuousfilmlayersontopof 3 3 were observed in electrolytes at pH 7 and 13.5.</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
+      <c r="N126" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5136,27 +8578,55 @@
           <t>S0126</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
+      <c r="D127" t="n">
+        <v>4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>In agreement with our assignment, the peak at The potential-dependent formation of C–C coupling intermediates about 1,602 cm−1 still appears after the DO/HO isotope exchange. explains the selectivity trend towards C products observed during 2 2 2+ Besides, the DO/HO exchange negligibly affected the peaks at about CORR.</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
         <is>
           <t>In correspondence with an increase in the CO coverage from 2 2 2 Nature Energy | Volume 9 | December 2024 | 1485–1496 1488 ).u.a( ytisnetnI –0.36 V versus RHE –0.76 V versus RHE –0.85 V versus RHE 1,070 cm–1 1,390 cm–1 1,610 cm–1 1,450 cm–1 1,550 cm–1 1,182 cm–1 1,318 cm–1 1,453 cm–1 1,595 cm–1 N = 4–5 N = 7–8 Cu–Cu Cu–Cu N = 6–7 N = 8–9 Cu–Cu Cu–Cu OCHCH OCCO– 2 CO 2– 3 HCOOH O s COCO2– OCHCH 3 Raman shift (cm–1) Fig. 3 | DFT-optimized CORR reaction intermediates and their vibrational highlighted in the panels by vertical dashed lines.</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Raman spectra were achieved 2 fingerprints.</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
         <is>
           <t>P1;P5</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr">
+      <c r="L127" t="inlineStr">
         <is>
           <t>P1:OCCO; P1:COCO; P5:HCOO</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
+      <c r="M127" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
+      <c r="N127" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5178,27 +8648,51 @@
           <t>S0127</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
+      <c r="D128" t="n">
+        <v>6</v>
+      </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr">
         <is>
           <t>Article https://doi.org/10.1038/s41467-024-54636-w Fig.4|In-situcaptureofreactionintermediates.OperandoRamanspectra TheinsetinFig.4c,dandeshowstheDFT-optimizedstructures.(Cu:yellow,Ag: recordedinCO-saturated0.1MKHCO solutionatE=-0.6V~-1.4Vvs.RHEover gray,O:red,H:white,C:blackgray)fPotential-dependentATR-SEIRASpeak 2 3 (a)AgCuNWand(b)AgCuNW,respectively.cPotential-dependentRamanpeak intensityfor*COCHOintermediateoverAgCuNW(bluebar)and*COCOinter1 1 intensityratioofCu-COstretching(P2)toCu-COfrustratedrotation(P1)overAgCu mediateoverAgCuNW(blacksolidline).h13CNMRandiMSspectraofCO2RR NWandAg1CuNW,andpeakintensityof*OHspeciesversuspotentialoverAg1Cu productsoverAg1CuNW,using12CO+H12CHO(top),13CO+H12CHO(middle),or NW.d,eOperandoATR-SEIRASspectracollectedinCO-saturated0.1MKHCO 12CO+H13CHO(bottom)asthereactants,obtainedat−1.2Vvs.RHE.gSchematic 2 3 solutionatE=-0.4V~−1.6Vvs.RHEoverAgCuNWandAgCuNW,respectively. diagramshowingtheCORRpathwayoverAgCuNW. 1 2 1 intermediate,whoseintensityincreasedwithcathodicpotentialrising 17.47 and 58.05, respectively, attributing to -CH and -CH OH from 3 2 from −0.4 to −1.6V vs.</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>RHE.</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
         <is>
           <t>P1;P2;P5</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr">
+      <c r="L128" t="inlineStr">
         <is>
           <t>P1:*COCO; P1:COCO; P2:CHO intermediate; P5:OCHO</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr">
+      <c r="M128" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
+      <c r="N128" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5220,19 +8714,43 @@
           <t>S0128</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
+      <c r="D129" t="n">
+        <v>17</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>The selectivity of Co - 2 4 0.050 Sub-CuS for EtOH in CO ER suggests that subsurface Co doping may alter the bonding mode of 2 *CHCHO, thereby steering the reaction towards the selective production of EtOH.</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
         <is>
           <t>In-situ Fouriertransform infrared (FTIR) spectroscopy was employed to dynamically track the evolution of reaction intermediates, complemented by DFT calculations to explore potential bonding modes of intermediates in the CO -to-EtOH transformation pathway. 2 S S E R P N I E L C I T R A</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr">
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
+      <c r="N129" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5254,27 +8772,55 @@
           <t>S0129</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
+      <c r="D130" t="n">
+        <v>19</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>The 2 L C spectra recorded in a 12CO atmosphere with D O supported these views (Fig. 3d and 2 I T Supplementary Figure 60Rb, see details in Supplementary Note 1).</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
         <is>
           <t>Theoretical calculations of the A FTIR spectra of *OCCOH intermediates adsorbed on the surface of Co -Sub-CuS showed a 0.050 C=O stretching at 1151 cm-1, and a C-OH stretching at 1629 cm-1, which correspond to the experimental values of 1621 cm-1 and 1132 cm-1, respectively (Fig. 3e and Supplementary Fig. 61).</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>A peak at 1540 cm-1, indicative of *OCCO species, was detected on CuS and Co -Sur-CuS, a 0.050 key intermediate in traditional C-C symmetric coupling using surface-adsorbed *CO42,49,50.</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
         <is>
           <t>P1;P3</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
+      <c r="L130" t="inlineStr">
         <is>
           <t>P1:*OCCO; P1:OCCO; P3:COH intermediate</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
+      <c r="M130" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
+      <c r="N130" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5296,19 +8842,43 @@
           <t>S0130</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
+      <c r="D131" t="n">
+        <v>21</v>
+      </c>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr">
         <is>
           <t>ARTICLE IN PRESS *CO , resulting in asymmetric OC-COH coupling, which is further supported by in-situ Raman bridge spectroscopy (Fig. 3g-i and Supplementary Figs. 64-67, see details in Supplementary Note 3).</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
+          <t>Subsequently, the shared intermediate *CHCO transformed into *CHCHO* via surface-O bonds by hydrogenated carbon atoms, followed by the next protonation step through the adsorption of O atoms.</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
+      <c r="N131" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5330,27 +8900,55 @@
           <t>S0131</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
+      <c r="D132" t="n">
+        <v>33</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>The anti-bonding and bonding interactions were analyzed based on the projected crystal orbital Hamilton population (-pCOHP) method.</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
         <is>
           <t>Changes in reaction energy for the competing pathways leading to C products were calculated. 2 We calculated the activation barriers for asymmetric coupling of *CO and *COH to form *OCCOH using the dimer method implemented in the CP2K code with the Quickstep module58.</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>The molecularly optimized Double-Zeta-Valence-Polarization (DZVP-MOLOPT) basis sets and Goedecker-Teter-Hutter (GTH) pseudopotentials were used for core electrons in combination with Perdew-Burke-Ernzerhof (PBE) exchange correlation functional59.</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
         <is>
           <t>P1;P3</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr">
+      <c r="L132" t="inlineStr">
         <is>
           <t>P1:*OCCO; P1:OCCO; P3:*COH</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr">
+      <c r="M132" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
+      <c r="N132" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5372,19 +8970,47 @@
           <t>S0132</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
+      <c r="D133" t="n">
+        <v>4</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Experimental observations suggest that *CO intermediates undergo C-C coupling process, followed by protonation of the α-C to generate the shared initial intermediate *CHCO7,9,15,16.</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
         <is>
           <t>The subsequent protonation pathway of *CHCO, which forms a variable SDI in a tautomeric form, may play a decisive role in dictating the selectivity between C hydrocarbons (mainly C H ) and C 2 2 4 2 oxygenates (mainly EtOH), as revealed by density functional theory (DFT) calculations10,15-17.</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
+          <t>These variable SDI configurations can be broadly categorized based on the coordination of the</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
+      <c r="N133" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -5406,27 +9032,55 @@
           <t>S0133</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
+      <c r="D134" t="n">
+        <v>6</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>The results show good agreement with the formationratewith≤20%O inthegasfeed(Fig.1).Asthe*OH 2 observed Raman band of 706cm −1 in the in situ SERS expericoverageincreasesbeyond3/9,boththeactivationbarrierandthe ments, which supports the representativeness of the computafree energy change for *CO dimerization increase substantially, tional model employed in this work.</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
         <is>
           <t>Due to the limitations of which is likely due to the repulsive interaction with the excess DFT calculations, other characters such as band width and *OH groups nearby. intensity, cannot be accurately predicted and thus are not For*COhydrogenationto*CHO,bothactivationbarrierand discussed. free energy change decrease substantially when *OH coverage Boththeactivationbarrierandthefreeenergychangefor*CO increases from 1/9 to 4/9 (Fig. 5b).</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Notably, these decreases are dimerization decrease as the *OH coverage increases from 0 to much more significant than those in *CO dimerization, which 3/9butreboundwithfurtherincreasein*OHcoverage(Fig.5a). agreeswiththesignificantanodicshiftofmethaneonsetpotential Boththeinitialstateandtransitionstatebecomelessstableasthe in the presence of the concurrent ORR (Fig. 2).</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr">
+      <c r="L134" t="inlineStr">
         <is>
           <t>P2:*CHO</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr">
+      <c r="M134" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
+      <c r="N134" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5448,19 +9102,43 @@
           <t>S0134</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
+      <c r="D135" t="n">
+        <v>19</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>This 2 results in increasing the CO binding strength on the surface Mo-atoms of MoP-Im (section S18, 2 Supplementary Materials).</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
         <is>
           <t>To gain more insight about a higher C-C coupling and ethanol production rates of MoP-Im, we further investigated the differences between three Raman peaks centered at 290, 380, and 2160 cm-1 which are correlated to the restricted rotation of adsorbed *CO (P1), Mo-CO stretching (P2), and *C-O stretching (P3), respectively.[30,43,44] It is worth noting that as a 19</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5482,27 +9160,51 @@
           <t>S0135</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr">
+      <c r="D136" t="n">
+        <v>8</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>CO molecules interact with two exposed Cu atoms, result suggested the rate-determining steps (RDS) altered when 2 respectively, forming coadsorbed (*OCHO+*OCHO) (State 3). thepotentialatdecreasedto−1.2Vvs.RHE,combiningtheFTIR One adsorbed *OCHO was firstly reduced to form *CH +* results in Fig. 4d.</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
         <is>
           <t>To further analysis why RDS changed during 3 OCHO (State 9), and then the other *OCHO was reduced to the reaction, the different charge density for Cu -CuN (with/ 2 3 construct*CH +*OCH (State12),thatwentthroughtheC–C without CH * ) and Cu -CuN (with/without CH * ) was 3 2 3 3 3 3 Fig.5DFTcalculationsofCO RRactivity.aReactionprogressofCO toCH CH OHontheCu –CuN at0Vand−0.501Vappliedpotential.The* 2 2 3 2 2 3 showedthereactionsite.Thestatewiththehighestenergybarrier(0.501eV)is8→9.Allstatesinvolvingthetransferofthe(H++e−)pairwere electrochemicalreactionstates,exceptforthe12→13state(CH *+OCH *→OCH CH *),whichwastheC–Cbondformationandnotinfluencedby 3 2 2 3 appliedpotential.bLocalstructuresoftheactivesiteandintermediatestate.Theballsinbrown,blue,red,grayandwhiterepresentCu,N,O,C,andH atoms,respectively. 8 NATURECOMMUNICATIONS| (2022) 13:1322 |https://doi.org/10.1038/s41467-022-29035-8|www.nature.com/naturecommunications</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr">
+      <c r="L136" t="inlineStr">
         <is>
           <t>P5:*OCHO; P5:OCHO</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr">
+      <c r="M136" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
+      <c r="N136" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5524,19 +9226,47 @@
           <t>S0136</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr">
+      <c r="D137" t="n">
+        <v>9</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>It wouldextendtothesingle-atomicsite,oxidecompositestructure, Quasi-insituXPSandAES.Quasi-insituX-rayphotoelectronspectroscopywas conductedofcatalystsdrop-castedoncarbonpaperassameasmentionedin and metal-support effect.</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
         <is>
           <t>These catalysts have great potential to Electrodessection.BeforetesttheelectrolytesshouldbeCO-saturatedtoremove exhibit novel catalytic properties such as more efficient catalytic thedissolvedoxygeninthesolution.Sampleswerecondition 2 edatdifferent performance and higher selectivity compared to the single atom potentialfor30minasoneconditioningstep.Afterthatthesampleswasmovedto catalysts and oxide catalysts. theXPSvacuumchamberwithoutextraexposedtotheair.Thatwouldavoidthe airtoinfluencethecatalyststokeeptheauthenticstateundertheCORRprocess. 2 XPS(ESCALAB250X)wasmeasuredatAnalyticalInstrumentationCenter, Methods ShanghaiTechUniversity.Itwasusedtocharacterizethechemicalbonding PreparationofCu/N x Candthecomparisonsamples.Typically,100mgcopper characteroftheobtainedcatalystsusingamonochromaticof1486.6eV(AlKα phthalocyanineand1.0gdicyandiamidewerecontinuouslymixedinethanoland source).AllXPSspectrawerecorrectedbyC1speakwiththebindingenergyat entirelydried.Subsequently,thedriedmixturewaspyrolyzedfor2hintheN 284.6eV.Allofthereagentswereusedwithoutfurtherpurification. 2 atmosphereatdifferenttemperaturetoobtainaseriesofCu/NCsampleswith x differentnitrogencontent(x=0.14,0.11,0.02,correspondingpyrolysistemperatureat800°C,900°C,1000°C,respectively.xismasscontentratioofnitrogento Freeze-quenchXAS.TheCu/N 0.14 Cwaselectrodepositedonacarbonpaper carbon).Collectobtainedblackpowderafterpyrolysisanddirectlyusedforfurther electrode,whichwasanintegralpartoftheXASsampleholder.TheCu/N 0.14 Cwas characterizationsandcatalyticperformancetest.Cu/Cwaspreparedwithcopper equilibratedpotentiostaticallyfor20minat−1.1Vvs.RHE.TheCu/N 0.14 C chlorideandtrimesicacid.Thepyrolysistemperaturewas800°Candother electrodewasrapidlyfrozenbyimmersioninliquidnitrogen.Thechemical synthesisconditionswerethesameasabove. reactionisextremelyslowatlowtemperatureenvironmentandthechemicalstate ofthecatalystwaswellpreservedforXAFSdatacollectionperiods.X-ray absorptionspectraattheCuK-edgewerecollectedatbeamlineBL14W1ofthe Characterization.TEMimageswerecarriedoutbytheJEOLJEM-2100FmicroSSRFusingaLytledetectorwiththeNifilter.Themeasurementswereperformedat scope(200kV).AFMwasobtainedonSPM-960AFM.Typically,smallamountof 18Kusingacryostat(ARS).Theexcitationenergies(scanrange8779–9779eV) samplewasultrasonicallydispersedintheaqueoussolution.ForAFMmeasurewereselectedbyaSi(111)double-crystalmonochromator. ment,10μLofthecompletelydispersedsolutionwascarefullydroppedonaflat micasheet,andthenplaceditinafumehoodtoairdry.ForTEM,10μLofthe dispersedsolutionpreparedabovewasdroppedonacoppermeshwithcarbon supportfilm.EDSelementalmappingandHAADF-STEMwerecharacterizedbya Computationalmethods.DFTcalculationswereperformedwithintheframeof plane-wave-baseddensityfunctionaltheory(DFT)byVASPpackage.ThegenJEOLARM-200microscope(200kV)withaprobesphericalaberrationcorrector. eralizedgradientapproximation(GGA)inthePerdew−Burke−Ernzerhof(PBE) X-raypowderdiffraction(XRD)spectrawereobservedbyRigakuTTR-IIIXRDof CuKαradiation(λ=1.5418Å).XPSspectrawereacquiredonaPerkinElmer formalismwasadoptedtotreattheelectronexchangeandcorrelationenergy.The cut-offenergywassettobe500eV.Forstructuraloptimization,3×3×2k-points PhysicsPHI5300spectrometer57. mesheswithatheoriginalMonkhorst-Packschemewasusedandtheconvergence ofenergyandforcewere10−6eVand0.01eVÅ−1,respectively.6×6×4k-points Electrochemicalmeasurements.Electrochemicalmeasurementswereaccommesheswereusedforstaticcalculations.A20Åvacuumlayerinthez-axis plishedinagas-tightH-typecellatCHI760Eelectrochemicalworkstation directionwasaddedtoavoidtheinterfereofthelayerimagecouplingcausedbythe (ShanghaiChenhua,China).Forpreparationoftheworkingelectrode,2mgofthe periodicboundaryconditions59.Formoredetails,pleaseseeSupplementary catalystwasdissolvedin500μlsolution(including10μlNafionsolution(5wt%) Figs.20, 28, 29, 31andSupplementaryDatafile1–13.</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
+          <t>NATURECOMMUNICATIONS| (2022) 13:1322 |https://doi.org/10.1038/s41467-022-29035-8|www.nature.com/naturecommunications 9</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
+      <c r="N137" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5558,19 +9288,47 @@
           <t>S0137</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
+      <c r="D138" t="n">
+        <v>6</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>This correlation between the amount of dehydration to generate a shared intermediate, * HCCOH3,14. 2 4 modified Ag and FEs for CO and EtOH was observed also with The selectivity between C H and EtOH, is significantly 2 4 other applied currents (Supplementary Fig. 22).</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
         <is>
           <t>Common to Cudependent on the relative stabilities of the next-intermediates * based catalysts, the coverage of CO on Cu surface is conducive for EtOH and C H pathways branched from HCCOH on Cu 2 4 to C–C coupling to impact EtOH and C H generation sites3,14,40.</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
+          <t>Cu with a relatively low coordinated surface and 2 4 concurrently24.</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
+      <c r="N138" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5592,19 +9350,47 @@
           <t>S0138</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
+      <c r="D139" t="n">
+        <v>7</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Thus, intermediate 6, which contains a Sn-C-C-O quaternary ring, is obtained.</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
         <is>
           <t>As reduction proceeds, with exergonicity of 0.99 eV, the Sn-C bond breaks upon further PCET, then forms the *CH CHOH 3 intermediate (7), followed by PCET and O-C bond cleavage (with a free energy barrier of 0.87 eV), and nally releases CH CH OH from the active site.</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
+          <t>Owing to the exibility of the bond between the active O 3 2 Page 7/14</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
+      <c r="N139" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5626,19 +9412,47 @@
           <t>S0139</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr">
+      <c r="D140" t="n">
+        <v>3</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Cu-composedelectrodeinpreviousstudies39–41.However,thecatalyst AccordingtotheSEMimages,XRDprofilesandOH−electroadsorption inthisstudycontributestotheimprovedC product,whichisascri2+ measurement, the morphology and dominant exposed facets of Cu bedtothenewreductionpathwaysofCO RRafterwettabilitymod2 catalyst are not significantly changed (Supplementary Figs. 18–20). ification.Thus,thechemicalstructureormorphologychangingafter XPSanalysisbeforeandaftertheelectrolysisrevealsimilarCu/Sratios thiol-modified is not the reason for improved CO RR selectivity of 2 onthecatalystsurface(SupplementaryFig.21).TheHRTEMdisplays ethyleneandethanol. the presence of the alkanethiol layer on the Cu catalyst after the reactionduetothehighelectrochemicalstabilityofthehydrophobic Effectofcontrollablewettabilityon*COcoverageviaCO mass 2 layer(SupplementaryFig.22).Thehydrophobic-treatedelectrodecan transport maintainalargercontactangleafterelectrolysis,whichascribestothe ItisknownthatthemasstransportofCO (localCO concentration) 2 2 optimized wettabilityofthecatalystlayerthatimprovestheCO RR can affect the coverage of *CO (a precursor of *CO), *CO, and *H, 2 2 stability (Supplementary Fig. 23).</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
         <is>
           <t>In this regard, the exposed facet, which affects the reaction pathways toward ethylene and ethanol morphologyandhydrophobicityoftheCucatalystandthethiollayer further5,20,42.Ourdata(Fig.2)alsomayimplythatthekinetic-controlled after electrolysisare relatively stableunder experimental condition, *CO/*H ratio can be controlled by tuning the local CO /H O ratio 2 2 whichisinaccordancewiththepreviousreport27,34.Additionally,the throughchangingthewettabilityofthecatalyst.Tocircumventthis electrochemicallyactivesurfacearea(ECSA)alsodropsrapidlyafter issue,computationalfluiddynamic(CFD)simulationswereemployed hydrophobic treatment (Supplementary Fig. 24), although the toinvestigatethemasstransportofCO andH Ointhecatalystlayers 2 2 Brunauer–Emmett–Teller specific surface area (S ) is almost relatedtokinetic-controlled*COand*H.Themodelswithandwithout BET unchanged(SupplementaryFig.26),consistentwithpreviousresult27. the alkanethiol modification layer were established to quantity CO 2 Therefore,thelowerECSAandcurrentdensitywiththeformationof alongthecatalystsurface(Fig.3a).Thedifferenceingasdiffusionwas thealkanethiollayercanbeattributedtothereducedcontactwiththe verifiedbysimulatingCO concentration.Theavailabilityofthegas 2 aqueouselectrolyte(Fig.2f,SupplementaryFig.24,25).Thevariation reactant significantly varied at the gas–electrolyte interface after of charge resistance (R ), mass transport resistance (W), and intermodification.Comparingwiththeunmodified-hydrophilicCucatalyst, ct facial electrochemical double-layer capacitance (C) after alkanethiol thegasdiffusiondistanceofthealkanethiol-modifiedlayerisincreased modification in electrochemical impedance spectroscopy (EIS) duetotheimprovedgasdiffusion. 156° 160 131° 112° 120 95° 80 40 0 Cu-4CCu-7CCu-12CCu-18C )°( elgna tcatnoC S 2p Cu-12C 43° Cu 175 170 165 160 Cu ).u.a( ytisnetnI Cu 2p Cu+/Cu0 Cu+/Cu0 Cu-12C Cu2+ Cu 970 960 950 940 930 Binding energy (eV) ).u.a( ytisnetnI Cu(200) Cu(220) Cu 30 40 50 60 70 80 Cu2+ Binding energy (eV) ).u.a( ytisnetnI Article https://doi.org/10.1038/s41467-023-39351-2 a b c Cu(111) Electrolyte Modified layer Alkanethiol Cu Product Product S CO 2 Cu-12C 10 nm Cu 2θ (°) d e f Fig.1|Characterizationofthewettability-tunablemodifiedCuelectrode.</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Cu–Sbonds.fTheaveragewaterdropletcontactangleofalkanethiol-treated aXRDpatternsofCuandCu-12CshowthatbothCucatalystswithorwithout Cuincreaseswiththeincreaseofthealkylchainlength.Theinsetsshow modificationtendtoexposeCu(111)facet.bHRTEMimageofCu-12C, photographsofwaterdroplets.Amodifiedlayerwithcontinuouslytunable revealinga2–3nmcontinuousandconformalalkanethiollayer.cIllustration wettability,aswellasahomogeneousstructure,wasobtained.Thea.u.stands showsCucatalystsviahydrophobictreatmentbyalkanethiol.dCu2pXPS forarbitraryunits.Errorbarsrepresentthestandarddeviationfromatleast spectra.eS2pXPSspectraofCuandCu-12C,demonstratingtheformationof threeindependentmeasurements.</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5660,19 +9474,47 @@
           <t>S0140</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
+      <c r="D141" t="n">
+        <v>1</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Copper-based materials are the most selective catalysts for elecAmong the CORR reaction intermediates7,8, *OCHCH is consid2 2 trochemically reducing CO to C products2.</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
         <is>
           <t>A myriad of studies have ered the last common precursor in the ethylene and ethanol routes, 2 2+ focused on understanding the C–C coupling mechanism, and although although experimental confirmation is still missing2,7.</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr"/>
-      <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>In fact, glyoxal some consensus has been reached, the dependence of these paths on and glycolaldehyde reduce to acetaldehyde, ethanol and ethylene the particular material history is yet to be confirmed5,6.</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5694,19 +9536,47 @@
           <t>S0141</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
+      <c r="D142" t="n">
+        <v>3</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Two new peaks at ∼1,390 cm−1 and ∼1,610 cm−1 appear, which are a potential switch from −0.36 V RHE to −0.96 V RHE (Supplementary Fig. 14). attributed to the symmetric and asymmetric stretching vibrations Concurrently, a broad band in the range of 2,830–2,990 cm−1 appeared, of carboxyl(ate) groups, respectively, based on control experiments which can be attributed to the stretching band of C–H (ref. 12). in Ar-saturated NaClO with 1 mM HCOOH solution (Supplementary 4 Fig. 13) and in Ar-saturated KHCO solution (Supplementary Fig. 11).</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
         <is>
           <t>Intermediates responsible for CO RR to ethylene 3 2 At −0.56 V , peaks of CO adsorbed on Cu are detected, with and ethanol RHE vibrational features at ∼280 cm−1, 355–360 cm−1 and 1,970–2,110 cm−1 To confirm the assignment of the vibrational modes detected expericorresponding to the restricted rotation of adsorbed CO (P1), Cu–CO mentally, we reverted to DFT (PBE-D233) through the Vienna Ab initio stretching (P2) and C–O stretching, respectively.</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Consistent with our Simulation Package34,35.</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5728,27 +9598,55 @@
           <t>S0142</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr">
+      <c r="D143" t="n">
+        <v>7</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AgCuNW.dCalculatedGibbsfreeenergydiagramsforCORRtoethanoland 1 2 AgCuNWcandonateelectronstoitsneighboringCuatoms,moving to0.63eV,revealingpreferredproductionof*COviathe*COOHroute 1 the d-band center of Cu from −2.142 to −2.132eV.</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
         <is>
           <t>Meanwhile, the overAgCuNW.Theincreased*COcoverageshallincreasetheprobatomicallydispersedAgatombecomespositivelycharged,matching ability of *CO-*CO coupling to form *COCO intermediate, directing wellwiththeXPSandXASresults.</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr">
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>CO reduction to produce ethylene over AgCu NW (Supplementary 2 Operando Ramanmeasurements observed in-situ generation of Figs.61,62).</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr">
+      <c r="L143" t="inlineStr">
         <is>
           <t>P1:*COCO; P1:COCO</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr">
+      <c r="M143" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
+      <c r="N143" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5770,27 +9668,55 @@
           <t>S0143</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr">
+      <c r="D144" t="n">
+        <v>18</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>In contrast, CuS mainly shows the *CO bridge atop peak, with minimal evidence of *CO in the same potential region (Supplementary Fig. 58). bridge Previous studies indicate that protonation of *CO on the Cu surface is more energetically bridge favorable than protonation of *CO 38,42.</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
         <is>
           <t>The simultaneous presence of *CO and *COH (or *CHO) atop following *CO protonation can trigger asymmetric C-C coupling on Co -Sub-CuS.</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr">
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>The bridge 0.050 appearance of *CHO intermediates at 1259 cm-1 in the in-situ FTIR spectra of Co -Sub-CuS 0.050 further supports this mechanism42.</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
         <is>
           <t>P2;P3</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr">
+      <c r="L144" t="inlineStr">
         <is>
           <t>P2:*CHO; P3:*COH</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr">
+      <c r="M144" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
+      <c r="N144" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5812,27 +9738,55 @@
           <t>S0144</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr">
+      <c r="D145" t="n">
+        <v>19</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Theoretical calculations of the A FTIR spectra of *OCCOH intermediates adsorbed on the surface of Co -Sub-CuS showed a 0.050 C=O stretching at 1151 cm-1, and a C-OH stretching at 1629 cm-1, which correspond to the experimental values of 1621 cm-1 and 1132 cm-1, respectively (Fig. 3e and Supplementary Fig. 61).</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
         <is>
           <t>A peak at 1540 cm-1, indicative of *OCCO species, was detected on CuS and Co -Sur-CuS, a 0.050 key intermediate in traditional C-C symmetric coupling using surface-adsorbed *CO42,49,50.</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr">
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Stronger bands at 1335 cm-1 and 1117 cm-1 were detected on Co -Sub-CuS, which are 0.050 attributed to *OC H 38,49,51-53, a key intermediate in EtOH production (Fig. 3a).</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr">
+      <c r="L145" t="inlineStr">
         <is>
           <t>P1:*OCCO; P1:OCCO</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr">
+      <c r="M145" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
+      <c r="N145" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5854,27 +9808,51 @@
           <t>S0145</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr">
+      <c r="D146" t="n">
+        <v>6</v>
+      </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr">
         <is>
           <t>ARTICLE NATURECOMMUNICATIONS|https://doi.org/10.1038/s41467-020-17690-8 a b c d e f Fig.4Computationalmodel.Representativestructuresof*COdimerizationatinitialstates(a),transitionstates(b),andfinalstates(c).Representative structuresof*COhydrogenationatinitialstates(d),transitionstates(e),andfinalstates(f). modes of *OH are compared with the Raman band observed ThisisconsistentwiththeobservedenhancementofC 2+product experimentally.</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr">
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>The results show good agreement with the formationratewith≤20%O inthegasfeed(Fig.1).Asthe*OH 2 observed Raman band of 706cm −1 in the in situ SERS expericoverageincreasesbeyond3/9,boththeactivationbarrierandthe ments, which supports the representativeness of the computafree energy change for *CO dimerization increase substantially, tional model employed in this work.</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr">
+      <c r="L146" t="inlineStr">
         <is>
           <t>P1:*CO dimerization; P1:CO dimerization</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr">
+      <c r="M146" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
+      <c r="N146" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5896,27 +9874,55 @@
           <t>S0146</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr">
+      <c r="D147" t="n">
+        <v>6</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>ARTICLE NATURECOMMUNICATIONS|https://doi.org/10.1038/s41467-020-17690-8 a b c d e f Fig.4Computationalmodel.Representativestructuresof*COdimerizationatinitialstates(a),transitionstates(b),andfinalstates(c).Representative structuresof*COhydrogenationatinitialstates(d),transitionstates(e),andfinalstates(f). modes of *OH are compared with the Raman band observed ThisisconsistentwiththeobservedenhancementofC 2+product experimentally.</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
         <is>
           <t>The results show good agreement with the formationratewith≤20%O inthegasfeed(Fig.1).Asthe*OH 2 observed Raman band of 706cm −1 in the in situ SERS expericoverageincreasesbeyond3/9,boththeactivationbarrierandthe ments, which supports the representativeness of the computafree energy change for *CO dimerization increase substantially, tional model employed in this work.</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr">
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Due to the limitations of which is likely due to the repulsive interaction with the excess DFT calculations, other characters such as band width and *OH groups nearby. intensity, cannot be accurately predicted and thus are not For*COhydrogenationto*CHO,bothactivationbarrierand discussed. free energy change decrease substantially when *OH coverage Boththeactivationbarrierandthefreeenergychangefor*CO increases from 1/9 to 4/9 (Fig. 5b).</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr">
+      <c r="L147" t="inlineStr">
         <is>
           <t>P1:*CO dimerization; P1:CO dimerization</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr">
+      <c r="M147" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
+      <c r="N147" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5938,27 +9944,55 @@
           <t>S0147</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr">
+      <c r="D148" t="n">
+        <v>6</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Overall our ex situ and operando emphasizingthattheoriginoftheimprovedselectivityforC 2+is characterizations of the modified bimetallic catalyst establish an not primarily due to the surface properties of the Cu electrodes obvious correlation between the electron-withdrawing ability of but rather the electron-withdrawing nature of the aromatic the functional groups and the oxidation state of Cu, which heterocycles as evidenced by our operando X-ray absorption translate into a larger concentration of adsorbed *CO on the spectroscopy measurements (Supplementary Figs. 6, 24 and 25). electrode surface and ultimately a higher probability for *CO to Itiswell-knownthattheformationofmulticarbonproductsin dimerize.</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
         <is>
           <t>CO RRproceedsviatheformationofthe*COintermediate,and 2 its subsequent dimerization in CO=CO or *CO–COH intermediates57–59.</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr">
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>To gain insight into the C–C coupling CO 2 RR using a membrane electrode-assembly (MEA) flow mechanismonfunctionalizedandpristineAg–CuduringCO RR, electrolyzer.</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr">
+      <c r="L148" t="inlineStr">
         <is>
           <t>P3:CO-COH; P3:CO–COH; P3:COH intermediate</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr">
+      <c r="M148" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
+      <c r="N148" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5980,19 +10014,47 @@
           <t>S0148</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr">
+      <c r="D149" t="n">
+        <v>2</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Highlights • High energy efficiency electrochemical conversion of CO to ethanol enabled by 2 employing MoP nanoparticles covered by an imidazolium-functionalized ionomer (Im). • The Im reduces mass transport limitations of the reaction and fine-tunes the catalytic properties of the surface-active sites.</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
         <is>
           <t>It also boosts CO /water ratio of the catalyst 2 layer that suppresses competing hydrogen evolution reaction. • In-situ Raman spectroscopy experiments reveal that the imidazolium layer increases the number of CO molecules near the catalyst surface and stabilizes the formation of 2 the *CO – and *CO intermediates on the Mo surface atoms for the ethanol formation. 2 • The first principle computational calculations are consistent with *CO - being strongly 2 bound to the Mo surface sites in presence of Im. 1.</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Introduction The US economy accounts for the release of a large amount of carbon dioxide (CO ) into the 2 atmosphere, causing severe environmental impacts.[1] However, CO can be directly converted 2 to value-added products via an electrochemical process driven by renewable energy that also provides a promising path to carbon-neutral manufacturing of chemicals and fuels at the gigaton scale.[2,3] While recent studies have mainly focused on the development of catalysts to effectively produce multi-carbon (C +) products, it is also important to improve CO diffusion 2 2 (mass transport) to the catalyst surface where CO is adsorbed and then converted to *CO - 2 2 intermediates that are identified to be thermodynamically uphill steps in many catalytic systems leading to a high overpotential and therefore, a low energy efficiency of the electrocatalytic CO 2 reduction reaction (eCO RR).[4,5] This requires the discovery of a novel catalytic system that 2 2</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -6014,27 +10076,55 @@
           <t>S0149</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr">
+      <c r="D150" t="n">
+        <v>8</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Fig.38).TheprotonationonCtoform*OCHCOH,followedbysubAlltheconstructedmodelsarelistedinSupplementaryFig.34. sequenthydrogenation,canbewellsupportedbythereactioninterAftergeometryoptimization,thestructureofHex-2Cu-Obendstoa mediatesdetectedbyATR-SEIRAS,especiallythestretchingoftheC–C curvedshape,coincidingwiththemolecularstructuredeterminedby coupling intermediate—*OCCOH and the C HOH precursor— 2 5 X-raycrystallography23,24.ThehybridstructureofCuclusterandpar- *OCH CH around1436and1360cm−1,respectively(Fig.4c),whichin 2 3 tially reduced Hex-2Cu-O is represented by a nine Cu atom cluster turnqualitativelyvalidatestheproposedethanolpathway(Fig.5d).</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
         <is>
           <t>(Cu )immobilizedontheCu-reduction-inducedvacancyonHex-2CuOurexperimentsobserveaselectivityincreaseforethylenepro9 O,anddenotedasR-Hex-2Cu-O.ThecurvedstructureofHex-2Cu-O duction starting from –1.3V on Hex-2Cu-O (Supplementary Fig. 7), formsaconfinedspacebetweentheCu clusterandtheadjacentsingle whichisrationalizedbycalculationssuggestingthattheaccelerated 9 Cucenter,whichare~3.84Åapart(SupplementaryFig.34).Thismodel reactionkinetics is led by the decreased activationbarrier with the isreasonableconsideringthesimilarsizeoftheCuclustertothatofthe changeofelectrodepotential.Figure5eshowsthatat0VvsRHEthe hexaphyrinmolecule(Fig.3d).Furthermore,toincludetheimpactof formation of *HOCCOH is kinetically unfavored on R-Hex-2Cu-O/G carbon-basedconductingagentKetjenBlack(KB)intheexperiment,a with an activation energy barrier of 1.51eV (MEP shown in Supple5×5×1 graphene substrate was introduced to support the hybrid mentary Fig. 39).</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr">
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>When applying a bias of –1.3V, the formation of structure (R-Hex-2Cu-O/G), which was used for all reaction *HOCCOHbecomesthermodynamicallydownhill(ΔE=–0.87eV)with mechanismstudy. aloweractivationenergybarrierof0.72eV,leadingtoanacceptable WefirstscrutinizedthekeyreactionintermediatesforC–Ccoureactionrateatroomtemperature46.Ourcalculationalsoconfirms*CO plingonR-Hex-2Cu-O/G,includingtwoCu-adsorbed*CObeforecoutrimerization to form n-propanol is facilitated by the spatialplingandthe*OCCOHdirectlyaftercoupling.Formostoftheactive confinementeffectonR-Hex-2Cu-O/G(SupplementaryFig.36b).The sitesexplored,alinearrelationshipexistsbetweenthetwoadsorption C pathwaytowardn-propanolisshowninFig.5candSupplementary 3 strengths(i.e.,ΔG andΔG )asshowninFig.5aandSuppleFig.40;theU is–0.98V,similartothatforethanolproduction, 2*CO *OCCOH limiting mentary Fig. 35.</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr">
+      <c r="L150" t="inlineStr">
         <is>
           <t>P1:OCCO</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr">
+      <c r="M150" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
+      <c r="N150" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -6056,19 +10146,43 @@
           <t>S0150</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr">
+      <c r="D151" t="n">
+        <v>4</v>
+      </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr">
         <is>
           <t>ARTICLE NATURECOMMUNICATIONS|https://doi.org/10.1038/s41467-022-29140-8 Fig.2Freeenergydiagrams(FEDs)ofCORonCu(100)atU =−0.73V(pH7).aTSstructuresofCHCO-H(TS1),CHC-HO(TS2),andOCCH-H RHE (TS3)protonation.FEDsshowingbthemajorCHCOHpathwaytowardsethylene(red)andethane(yellow),ctheminorCHCOHpathwaytowards ethylene(red)andacetylene(brown),dtheOCHCHpathwaytowardsethanol(blue)andacetaldehyde(navy),andetheCH COpathwaytowardsacetic 2 acid(green)andanintermediate(blue)leadingtotheothertwoC Oxyproducts.Thecoloredsquaresinbanddhighlightregionswherekeycompeting 2 reactionstepsappearfrombranchingpathwaysasillustratedinFig.1:fCHCHOHformationfromCHCOH*(purple),possiblyleadingtoC Oxysand 2 gethyleneformationfromOCHCH *(purple)asproposedbyCalle-Vallejoetal.26andbasedonlyonthethermodynamicstabilitiesofsurfacespecies. 2 ImportantTSstructures,CHCOH-H(TS4)andCHC-HOH(TS5)protonationareshowninf,andOCH-HCH (TS6),CH CHO-H(TS8),andOCHCH -H 2 2 2 (TS9)protonation,aswellasC–OscissionofOCH CH *(TS7)areshowning.Electrochemicalprotonationstepsareshownassolidlineswhilechemical 2 2 processesareshownasdashedlines.AllenergiesintheFEDsarereferencedtoCO(g),H (g),andH Obasedonthecomputationalhydrogenelectrode 2 2 (CHE)model.Thevaluesinparenthesesinb–grepresenttheΔG atU =−0.73V(pH7).SourcedataareprovidedasaSourceDatafile. a RHE via surface hydrogenation35.</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr">
         <is>
+          <t>Since the C–O bond breaks easily absence of C HC products, acetylene and ethane, observed 2 through CHCOH-H protonation, the CHCOH pathway is conexperimentally may be attributed to the slower H-CCH protonasequently identified to exclusively produce C HCs.</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
+      <c r="N151" t="inlineStr">
         <is>
           <t>no</t>
         </is>
